--- a/IG/AI Native-生成AI_IG.xlsx
+++ b/IG/AI Native-生成AI_IG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02858889-D414-44B0-9B89-977B6FCA6C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C62B856-6F4C-4298-AC72-947CEE83D98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール（1日）" sheetId="33" r:id="rId1"/>
@@ -20,8 +20,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（1日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$101</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$99</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="206">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -150,10 +150,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>アンケート</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>使用教材</t>
     <rPh sb="0" eb="2">
       <t>シヨウ</t>
@@ -365,10 +361,6 @@
     <rPh sb="6" eb="7">
       <t>テン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>・アンケートの実施</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2231,11 +2223,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">・共通1
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>ハンズオン編:ChatGPT</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -2432,7 +2419,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2592,14 +2579,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <b/>
-      <sz val="8"/>
+      <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -2859,7 +2840,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3022,9 +3003,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3064,9 +3042,6 @@
     <xf numFmtId="20" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -3082,176 +3057,170 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3625,15 +3594,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="98" t="str">
+      <c r="B2" s="94" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3646,10 +3615,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="100"/>
+      <c r="B4" s="95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="96"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3657,18 +3626,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="101"/>
-      <c r="C5" s="102"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="98"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="99"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="27"/>
@@ -3684,19 +3653,19 @@
       <c r="B10" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="90" t="s">
+      <c r="C10" s="84" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="42"/>
-      <c r="B11" s="72">
+      <c r="B11" s="70">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="87" t="str">
+      <c r="C11" s="81" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -3706,16 +3675,16 @@
       <c r="A12" s="40">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="84"/>
-      <c r="C12" s="88"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="82"/>
       <c r="G12" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="41"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="89"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="83"/>
       <c r="F13" s="26"/>
       <c r="H13" s="6"/>
     </row>
@@ -3724,20 +3693,20 @@
       <c r="B14" s="40">
         <v>0.4375</v>
       </c>
-      <c r="C14" s="87" t="str">
+      <c r="C14" s="81" t="str">
         <f>master!B4</f>
         <v>導入編</v>
       </c>
-      <c r="F14" s="97"/>
+      <c r="F14" s="93"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="42"/>
-      <c r="B15" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="88"/>
-      <c r="F15" s="97"/>
+      <c r="B15" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="82"/>
+      <c r="F15" s="93"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -3745,8 +3714,8 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="B16" s="44"/>
-      <c r="C16" s="89"/>
-      <c r="F16" s="97"/>
+      <c r="C16" s="83"/>
+      <c r="F16" s="93"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
@@ -3754,18 +3723,18 @@
       <c r="B17" s="43">
         <v>0.46875</v>
       </c>
-      <c r="C17" s="87" t="str">
+      <c r="C17" s="81" t="str">
         <f>master!B15</f>
         <v>復習編</v>
       </c>
-      <c r="F17" s="97"/>
+      <c r="F17" s="93"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="41"/>
       <c r="B18" s="44"/>
-      <c r="C18" s="89"/>
-      <c r="F18" s="97"/>
+      <c r="C18" s="83"/>
+      <c r="F18" s="93"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3773,32 +3742,32 @@
       <c r="B19" s="45">
         <v>0.48958333333333331</v>
       </c>
-      <c r="C19" s="86" t="str">
+      <c r="C19" s="80" t="str">
         <f>master!B24</f>
         <v>AI-Native研修の目的</v>
       </c>
-      <c r="F19" s="97"/>
+      <c r="F19" s="93"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="69">
+      <c r="A20" s="67">
         <v>0.5</v>
       </c>
-      <c r="B20" s="69">
+      <c r="B20" s="67">
         <v>0.5</v>
       </c>
-      <c r="C20" s="87" t="str">
+      <c r="C20" s="81" t="str">
         <f>master!B29</f>
         <v>キャリア編</v>
       </c>
-      <c r="F20" s="97"/>
+      <c r="F20" s="93"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="61"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="89"/>
-      <c r="F21" s="97"/>
+      <c r="A21" s="60"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="83"/>
+      <c r="F21" s="93"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3806,7 +3775,7 @@
       <c r="B22" s="41">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="91" t="s">
+      <c r="C22" s="85" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="25"/>
@@ -3816,9 +3785,9 @@
     <row r="23" spans="1:8">
       <c r="A23" s="42"/>
       <c r="B23" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="92"/>
+        <v>30</v>
+      </c>
+      <c r="C23" s="86"/>
       <c r="F23" s="25"/>
       <c r="G23" s="10"/>
       <c r="H23" s="6"/>
@@ -3828,9 +3797,9 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="B24" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="92"/>
+        <v>30</v>
+      </c>
+      <c r="C24" s="86"/>
       <c r="F24" s="25"/>
       <c r="G24" s="10"/>
       <c r="H24" s="6"/>
@@ -3838,9 +3807,9 @@
     <row r="25" spans="1:8">
       <c r="A25" s="41"/>
       <c r="B25" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="93"/>
+        <v>30</v>
+      </c>
+      <c r="C25" s="87"/>
       <c r="F25" s="25"/>
       <c r="G25" s="10"/>
       <c r="H25" s="6"/>
@@ -3850,8 +3819,8 @@
       <c r="B26" s="45">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="89"/>
-      <c r="F26" s="97"/>
+      <c r="C26" s="83"/>
+      <c r="F26" s="93"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -3860,11 +3829,11 @@
       <c r="B27" s="43">
         <v>0.57291666666666663</v>
       </c>
-      <c r="C27" s="87" t="str">
+      <c r="C27" s="81" t="str">
         <f>master!B43</f>
         <v>NTTデータの強み編</v>
       </c>
-      <c r="F27" s="97"/>
+      <c r="F27" s="93"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3873,8 +3842,8 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="B28" s="44"/>
-      <c r="C28" s="89"/>
-      <c r="F28" s="97"/>
+      <c r="C28" s="83"/>
+      <c r="F28" s="93"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -3882,74 +3851,74 @@
       <c r="B29" s="43">
         <v>0.59375</v>
       </c>
-      <c r="C29" s="71" t="str">
+      <c r="C29" s="69" t="str">
         <f>master!B52</f>
         <v>ハンズオン編:ChatGPT</v>
       </c>
-      <c r="D29" s="60"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="97"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="93"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="41"/>
       <c r="B30" s="45"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="97"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="93"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="42"/>
       <c r="B31" s="45"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="60"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="59"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="97"/>
+      <c r="F31" s="93"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="69">
+      <c r="A32" s="67">
         <v>0.625</v>
       </c>
       <c r="B32" s="45"/>
-      <c r="C32" s="64"/>
-      <c r="D32" s="60"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="59"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="97"/>
+      <c r="F32" s="93"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="61"/>
+      <c r="A33" s="60"/>
       <c r="B33" s="44"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="97"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="93"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="61"/>
+      <c r="A34" s="60"/>
       <c r="B34" s="43">
         <v>0.60416666666666663</v>
       </c>
-      <c r="C34" s="71" t="str">
+      <c r="C34" s="69" t="str">
         <f>master!B60</f>
         <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
       </c>
-      <c r="D34" s="60"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="97"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="93"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="42"/>
       <c r="B35" s="45"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="97"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="93"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3957,37 +3926,37 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="B36" s="45"/>
-      <c r="C36" s="64"/>
-      <c r="D36" s="60"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="59"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="97"/>
+      <c r="F36" s="93"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="41"/>
       <c r="B37" s="45"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="60"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="59"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="97"/>
+      <c r="F37" s="93"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="41"/>
       <c r="B38" s="45"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="60"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="59"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="97"/>
+      <c r="F38" s="93"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="41"/>
       <c r="B39" s="44"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="60"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="59"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="97"/>
+      <c r="F39" s="93"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3997,45 +3966,45 @@
       <c r="B40" s="43">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C40" s="64" t="s">
-        <v>200</v>
-      </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="97"/>
+      <c r="C40" s="63" t="s">
+        <v>197</v>
+      </c>
+      <c r="D40" s="59"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="93"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="41"/>
       <c r="B41" s="45"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="97"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="93"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="45"/>
       <c r="B42" s="44"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="97"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="93"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
       <c r="A43" s="44"/>
-      <c r="B43" s="96">
+      <c r="B43" s="90">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="95" t="s">
-        <v>198</v>
-      </c>
-      <c r="D43" s="61"/>
-      <c r="E43" s="59"/>
+      <c r="C43" s="89" t="s">
+        <v>195</v>
+      </c>
+      <c r="D43" s="60"/>
+      <c r="E43" s="58"/>
       <c r="F43" s="25"/>
       <c r="G43" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.6" thickBot="1">
@@ -4064,7 +4033,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:L14"/>
+  <dimension ref="A2:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -4083,7 +4052,7 @@
   <sheetData>
     <row r="2" spans="1:12" s="34" customFormat="1" ht="36.75" customHeight="1">
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="35"/>
@@ -4107,10 +4076,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="109" t="s">
+      <c r="B4" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="109"/>
+      <c r="C4" s="105"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4121,16 +4090,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="110"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4140,38 +4109,38 @@
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="36"/>
-      <c r="D7" s="111" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="111"/>
+      <c r="D7" s="107" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="107"/>
       <c r="F7" s="36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="47"/>
       <c r="F8" s="39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -4186,46 +4155,46 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="105"/>
-      <c r="C11" s="105" t="s">
+      <c r="B11" s="101"/>
+      <c r="C11" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="105" t="s">
+      <c r="D11" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="112" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="104" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104" t="s">
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="108" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="100" t="s">
         <v>33</v>
+      </c>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100" t="s">
+        <v>32</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="105"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="113"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="109"/>
       <c r="I12" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J12" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="105"/>
+      <c r="K12" s="101"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
@@ -4234,53 +4203,28 @@
       <c r="C13" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="106" t="s">
-        <v>193</v>
-      </c>
-      <c r="E13" s="107"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="66" t="s">
-        <v>194</v>
+      <c r="D13" s="102" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" s="103"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="65" t="s">
+        <v>192</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="67">
+        <v>29</v>
+      </c>
+      <c r="J13" s="66">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K13" s="20"/>
       <c r="L13" s="10"/>
     </row>
-    <row r="14" spans="1:12" ht="25.2">
-      <c r="A14" s="10"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="106" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="107"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="83" t="s">
-        <v>195</v>
-      </c>
-      <c r="H14" s="20"/>
-      <c r="I14" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="68">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K14" s="20"/>
-      <c r="L14" s="10"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="D7:E7"/>
@@ -4302,7 +4246,7 @@
           <x14:formula1>
             <xm:f>master!$C$48:$C$50</xm:f>
           </x14:formula1>
-          <xm:sqref>H13:H14</xm:sqref>
+          <xm:sqref>H13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4312,7 +4256,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N102"/>
+  <dimension ref="A2:N100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -4334,7 +4278,7 @@
   <sheetData>
     <row r="2" spans="1:14" ht="36.75" customHeight="1">
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -4362,12 +4306,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="109" t="s">
+      <c r="B4" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4378,30 +4322,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
       <c r="L5" s="32"/>
       <c r="M5" s="33"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="124"/>
       <c r="L6" s="32"/>
       <c r="M6" s="33"/>
     </row>
@@ -4416,20 +4360,20 @@
     </row>
     <row r="8" spans="1:14">
       <c r="B8" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>17</v>
-      </c>
       <c r="D8" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" s="36"/>
       <c r="F8" s="36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" s="36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" s="51"/>
       <c r="J8" s="6"/>
@@ -4440,210 +4384,235 @@
     </row>
     <row r="9" spans="1:14">
       <c r="B9" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>36</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:14">
-      <c r="B10" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="B11" s="24"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="22"/>
-      <c r="H11" s="10"/>
+    <row r="11" spans="1:14" ht="24" customHeight="1">
+      <c r="A11" s="10"/>
+      <c r="B11" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="100" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="122" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="123"/>
+      <c r="K11" s="100" t="s">
+        <v>34</v>
+      </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="13" spans="1:14" ht="24" customHeight="1">
+    <row r="12" spans="1:14">
+      <c r="A12" s="10"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="101"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" ht="75.599999999999994">
       <c r="A13" s="10"/>
-      <c r="B13" s="105" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="105" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="105" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="104" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="114" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="115"/>
-      <c r="K13" s="104" t="s">
-        <v>35</v>
-      </c>
+      <c r="B13" s="110" t="str">
+        <f>master!B3</f>
+        <v>自己紹介</v>
+      </c>
+      <c r="C13" s="54" t="str">
+        <f>master!C3</f>
+        <v>ー</v>
+      </c>
+      <c r="D13" s="118" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="119"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K13" s="46"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" ht="88.2">
       <c r="A14" s="10"/>
-      <c r="B14" s="105"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="105"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="115" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="116"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="H14" s="73"/>
+      <c r="I14" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="75">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K14" s="76"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" ht="75.599999999999994">
+    <row r="15" spans="1:14" ht="138.6">
       <c r="A15" s="10"/>
-      <c r="B15" s="124" t="str">
-        <f>master!B3</f>
-        <v>自己紹介</v>
-      </c>
-      <c r="C15" s="55" t="str">
-        <f>master!C3</f>
-        <v>ー</v>
-      </c>
-      <c r="D15" s="117" t="s">
-        <v>190</v>
-      </c>
-      <c r="E15" s="118"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="55" t="s">
-        <v>123</v>
+      <c r="B15" s="121" t="str">
+        <f>master!B4</f>
+        <v>導入編</v>
+      </c>
+      <c r="C15" s="54" t="str">
+        <f>master!C4</f>
+        <v>あなたはもう生成ＡＩを使っていますか？</v>
+      </c>
+      <c r="D15" s="118" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="119"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="54" t="s">
+        <v>122</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="50">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K15" s="46"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="88.2">
-      <c r="A16" s="10"/>
-      <c r="B16" s="125"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="120" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" s="121"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="77" t="s">
-        <v>191</v>
-      </c>
-      <c r="H16" s="78"/>
-      <c r="I16" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K16" s="81"/>
+    <row r="16" spans="1:14" ht="75.599999999999994">
+      <c r="A16" s="11"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="54" t="str">
+        <f>master!C5</f>
+        <v>FYI：システム開発SaaS　「GEAR.indigo」</v>
+      </c>
+      <c r="D16" s="118" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="119"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="50">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K16" s="46"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="138.6">
-      <c r="A17" s="10"/>
-      <c r="B17" s="123" t="str">
-        <f>master!B4</f>
-        <v>導入編</v>
-      </c>
-      <c r="C17" s="55" t="str">
-        <f>master!C4</f>
-        <v>あなたはもう生成ＡＩを使っていますか？</v>
-      </c>
-      <c r="D17" s="117" t="s">
+    <row r="17" spans="1:14" ht="37.799999999999997">
+      <c r="A17" s="11"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="54" t="str">
+        <f>master!C6</f>
+        <v>FYI：GEAR.indigo　「業務要件一覧」</v>
+      </c>
+      <c r="D17" s="118" t="s">
         <v>158</v>
       </c>
-      <c r="E17" s="118"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="55" t="s">
+      <c r="E17" s="119"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="54" t="s">
         <v>124</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" s="50">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K17" s="46"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="75.599999999999994">
+    <row r="18" spans="1:14" ht="37.799999999999997">
       <c r="A18" s="11"/>
-      <c r="B18" s="123"/>
-      <c r="C18" s="55" t="str">
-        <f>master!C5</f>
-        <v>FYI：システム開発SaaS　「GEAR.indigo」</v>
-      </c>
-      <c r="D18" s="117" t="s">
+      <c r="B18" s="121"/>
+      <c r="C18" s="54" t="str">
+        <f>master!C7</f>
+        <v>FYI：GEAR.indigo　「システム化業務フロー」</v>
+      </c>
+      <c r="D18" s="118" t="s">
         <v>159</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="55" t="s">
-        <v>128</v>
+      <c r="E18" s="119"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J18" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K18" s="46"/>
       <c r="L18" s="6"/>
@@ -4652,22 +4621,22 @@
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="55" t="str">
-        <f>master!C6</f>
-        <v>FYI：GEAR.indigo　「業務要件一覧」</v>
-      </c>
-      <c r="D19" s="117" t="s">
+      <c r="B19" s="121"/>
+      <c r="C19" s="54" t="str">
+        <f>master!C8</f>
+        <v>FYI：GEAR.indigo　「テーブル定義書」</v>
+      </c>
+      <c r="D19" s="118" t="s">
         <v>160</v>
       </c>
-      <c r="E19" s="118"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="55" t="s">
-        <v>126</v>
+      <c r="E19" s="119"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J19" s="50">
         <v>6.9444444444444447E-4</v>
@@ -4679,22 +4648,22 @@
     </row>
     <row r="20" spans="1:14" ht="37.799999999999997">
       <c r="A20" s="11"/>
-      <c r="B20" s="123"/>
-      <c r="C20" s="55" t="str">
-        <f>master!C7</f>
-        <v>FYI：GEAR.indigo　「システム化業務フロー」</v>
-      </c>
-      <c r="D20" s="117" t="s">
+      <c r="B20" s="121"/>
+      <c r="C20" s="54" t="str">
+        <f>master!C9</f>
+        <v>FYI：GEAR.indigo　「画面定義書」</v>
+      </c>
+      <c r="D20" s="118" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="118"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="55" t="s">
-        <v>126</v>
+      <c r="E20" s="119"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J20" s="50">
         <v>6.9444444444444447E-4</v>
@@ -4704,132 +4673,132 @@
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="37.799999999999997">
+    <row r="21" spans="1:14" ht="50.4">
       <c r="A21" s="11"/>
-      <c r="B21" s="123"/>
-      <c r="C21" s="55" t="str">
-        <f>master!C8</f>
-        <v>FYI：GEAR.indigo　「テーブル定義書」</v>
-      </c>
-      <c r="D21" s="117" t="s">
-        <v>162</v>
-      </c>
-      <c r="E21" s="118"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="55" t="s">
-        <v>126</v>
+      <c r="B21" s="121"/>
+      <c r="C21" s="54" t="str">
+        <f>master!C10</f>
+        <v>GEAR.indigo が （いずれ）見せてくれるもの</v>
+      </c>
+      <c r="D21" s="118" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="119"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J21" s="50">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K21" s="46"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="37.799999999999997">
+    <row r="22" spans="1:14" ht="25.2">
       <c r="A22" s="11"/>
-      <c r="B22" s="123"/>
-      <c r="C22" s="55" t="str">
-        <f>master!C9</f>
-        <v>FYI：GEAR.indigo　「画面定義書」</v>
-      </c>
-      <c r="D22" s="117" t="s">
-        <v>163</v>
-      </c>
-      <c r="E22" s="118"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="55" t="s">
-        <v>126</v>
+      <c r="B22" s="121"/>
+      <c r="C22" s="54" t="str">
+        <f>master!C11</f>
+        <v>あなたはどちらになりたいですか？</v>
+      </c>
+      <c r="D22" s="118" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="119"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="54" t="s">
+        <v>132</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J22" s="50">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K22" s="46"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="50.4">
+    <row r="23" spans="1:14" ht="37.799999999999997">
       <c r="A23" s="11"/>
-      <c r="B23" s="123"/>
-      <c r="C23" s="55" t="str">
-        <f>master!C10</f>
-        <v>GEAR.indigo が （いずれ）見せてくれるもの</v>
-      </c>
-      <c r="D23" s="117" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" s="118"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="55" t="s">
-        <v>127</v>
+      <c r="B23" s="121"/>
+      <c r="C23" s="54" t="str">
+        <f>master!C12</f>
+        <v>いま、生成AIができること　（システム開発関連）</v>
+      </c>
+      <c r="D23" s="118" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J23" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K23" s="46"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="25.2">
+    <row r="24" spans="1:14" ht="214.2">
       <c r="A24" s="11"/>
-      <c r="B24" s="123"/>
-      <c r="C24" s="55" t="str">
-        <f>master!C11</f>
-        <v>あなたはどちらになりたいですか？</v>
-      </c>
-      <c r="D24" s="117" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="118"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="55" t="s">
-        <v>134</v>
+      <c r="B24" s="121"/>
+      <c r="C24" s="54" t="str">
+        <f>master!C13</f>
+        <v>いま、生成ＡＩができないこと</v>
+      </c>
+      <c r="D24" s="118" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="119"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="54" t="s">
+        <v>185</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J24" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K24" s="46"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="37.799999999999997">
+    <row r="25" spans="1:14" ht="226.8">
       <c r="A25" s="11"/>
-      <c r="B25" s="123"/>
-      <c r="C25" s="55" t="str">
-        <f>master!C12</f>
-        <v>いま、生成AIができること　（システム開発関連）</v>
-      </c>
-      <c r="D25" s="117" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="118"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="55" t="s">
-        <v>126</v>
+      <c r="B25" s="121"/>
+      <c r="C25" s="54" t="str">
+        <f>master!C14</f>
+        <v>生成ＡＩを使う心得８条</v>
+      </c>
+      <c r="D25" s="118" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="119"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="54" t="s">
+        <v>136</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J25" s="50">
         <v>3.472222222222222E-3</v>
@@ -4839,54 +4808,59 @@
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="214.2">
+    <row r="26" spans="1:14" ht="15" customHeight="1">
       <c r="A26" s="11"/>
-      <c r="B26" s="123"/>
-      <c r="C26" s="55" t="str">
-        <f>master!C13</f>
-        <v>いま、生成ＡＩができないこと</v>
-      </c>
-      <c r="D26" s="117" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" s="118"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="55" t="s">
-        <v>187</v>
+      <c r="B26" s="121" t="str">
+        <f>master!B15</f>
+        <v>復習編</v>
+      </c>
+      <c r="C26" s="54" t="str">
+        <f>master!C15</f>
+        <v>NTTDATAが目指す方向性</v>
+      </c>
+      <c r="D26" s="118" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" s="119"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J26" s="50">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K26" s="46"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K26" s="46" t="s">
+        <v>138</v>
+      </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="226.8">
+    <row r="27" spans="1:14" ht="15" customHeight="1">
       <c r="A27" s="11"/>
-      <c r="B27" s="123"/>
-      <c r="C27" s="55" t="str">
-        <f>master!C14</f>
-        <v>生成ＡＩを使う心得８条</v>
-      </c>
-      <c r="D27" s="117" t="s">
+      <c r="B27" s="121"/>
+      <c r="C27" s="54" t="str">
+        <f>master!C16</f>
+        <v>NTTデータ新入社員向け生成AI基礎講座</v>
+      </c>
+      <c r="D27" s="118" t="s">
         <v>139</v>
       </c>
-      <c r="E27" s="118"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="55" t="s">
-        <v>138</v>
+      <c r="E27" s="119"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J27" s="50">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K27" s="46"/>
       <c r="L27" s="6"/>
@@ -4895,57 +4869,52 @@
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
       <c r="A28" s="11"/>
-      <c r="B28" s="123" t="str">
-        <f>master!B15</f>
-        <v>復習編</v>
-      </c>
-      <c r="C28" s="55" t="str">
-        <f>master!C15</f>
-        <v>NTTDATAが目指す方向性</v>
-      </c>
-      <c r="D28" s="117" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" s="118"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="55" t="s">
-        <v>122</v>
+      <c r="B28" s="121"/>
+      <c r="C28" s="54" t="str">
+        <f>master!C17</f>
+        <v>プロンプト設計の基本</v>
+      </c>
+      <c r="D28" s="118" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="119"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" s="50">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K28" s="46" t="s">
-        <v>140</v>
-      </c>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K28" s="46"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1">
+    <row r="29" spans="1:14" ht="75.599999999999994">
       <c r="A29" s="11"/>
-      <c r="B29" s="123"/>
-      <c r="C29" s="55" t="str">
-        <f>master!C16</f>
-        <v>NTTデータ新入社員向け生成AI基礎講座</v>
-      </c>
-      <c r="D29" s="117" t="s">
-        <v>141</v>
-      </c>
-      <c r="E29" s="118"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="55" t="s">
-        <v>122</v>
+      <c r="B29" s="121"/>
+      <c r="C29" s="54" t="str">
+        <f>master!C18</f>
+        <v>プロンプト設計の基本を踏まえた構造型プロンプト</v>
+      </c>
+      <c r="D29" s="118" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" s="119"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="54" t="s">
+        <v>126</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J29" s="50">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K29" s="46"/>
       <c r="L29" s="6"/>
@@ -4954,264 +4923,264 @@
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="11"/>
-      <c r="B30" s="123"/>
-      <c r="C30" s="55" t="str">
-        <f>master!C17</f>
-        <v>プロンプト設計の基本</v>
-      </c>
-      <c r="D30" s="117" t="s">
-        <v>154</v>
-      </c>
-      <c r="E30" s="118"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="55" t="s">
-        <v>122</v>
+      <c r="B30" s="121"/>
+      <c r="C30" s="54" t="str">
+        <f>master!C19</f>
+        <v>本セクションで学ぶこと</v>
+      </c>
+      <c r="D30" s="118"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J30" s="50">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K30" s="46"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="75.599999999999994">
+    <row r="31" spans="1:14" ht="50.4">
       <c r="A31" s="11"/>
-      <c r="B31" s="123"/>
-      <c r="C31" s="55" t="str">
-        <f>master!C18</f>
-        <v>プロンプト設計の基本を踏まえた構造型プロンプト</v>
-      </c>
-      <c r="D31" s="117" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" s="118"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="55" t="s">
-        <v>128</v>
+      <c r="B31" s="121"/>
+      <c r="C31" s="54" t="str">
+        <f>master!C20</f>
+        <v>エージェントAIとは何か？</v>
+      </c>
+      <c r="D31" s="118" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="119"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J31" s="50">
-        <v>3.472222222222222E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K31" s="46"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1">
+    <row r="32" spans="1:14" ht="25.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="123"/>
-      <c r="C32" s="55" t="str">
-        <f>master!C19</f>
-        <v>本セクションで学ぶこと</v>
-      </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="55" t="s">
-        <v>122</v>
+      <c r="B32" s="121"/>
+      <c r="C32" s="54" t="str">
+        <f>master!C21</f>
+        <v>エージェントの処理</v>
+      </c>
+      <c r="D32" s="118" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="119"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="54" t="s">
+        <v>132</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J32" s="50">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K32" s="46"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" ht="50.4">
+    <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="55" t="str">
-        <f>master!C20</f>
-        <v>エージェントAIとは何か？</v>
-      </c>
-      <c r="D33" s="117" t="s">
-        <v>164</v>
-      </c>
-      <c r="E33" s="118"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="55" t="s">
-        <v>127</v>
+      <c r="B33" s="121"/>
+      <c r="C33" s="54" t="str">
+        <f>master!C22</f>
+        <v>AIエージェントのアーキテクチャ</v>
+      </c>
+      <c r="D33" s="118" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="119"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J33" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K33" s="46"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14" ht="25.2">
+    <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="123"/>
-      <c r="C34" s="55" t="str">
-        <f>master!C21</f>
-        <v>エージェントの処理</v>
-      </c>
-      <c r="D34" s="117" t="s">
-        <v>156</v>
-      </c>
-      <c r="E34" s="118"/>
-      <c r="F34" s="119"/>
-      <c r="G34" s="55" t="s">
-        <v>134</v>
+      <c r="B34" s="121"/>
+      <c r="C34" s="54" t="str">
+        <f>master!C23</f>
+        <v>AIの強みを生かすポイント</v>
+      </c>
+      <c r="D34" s="118" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="119"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J34" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K34" s="46"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" ht="37.799999999999997">
+    <row r="35" spans="1:14" ht="15" customHeight="1">
       <c r="A35" s="11"/>
-      <c r="B35" s="123"/>
-      <c r="C35" s="55" t="str">
-        <f>master!C22</f>
-        <v>AIエージェントのアーキテクチャ</v>
-      </c>
-      <c r="D35" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" s="118"/>
-      <c r="F35" s="119"/>
-      <c r="G35" s="55" t="s">
-        <v>126</v>
+      <c r="B35" s="121" t="str">
+        <f>master!B24</f>
+        <v>AI-Native研修の目的</v>
+      </c>
+      <c r="C35" s="54" t="str">
+        <f>master!C24</f>
+        <v>1.研修概要</v>
+      </c>
+      <c r="D35" s="118"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="52" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="J35" s="50">
-        <v>3.472222222222222E-3</v>
+        <v>0</v>
       </c>
       <c r="K35" s="46"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="37.799999999999997">
+    <row r="36" spans="1:14" ht="15" customHeight="1">
       <c r="A36" s="11"/>
-      <c r="B36" s="123"/>
-      <c r="C36" s="55" t="str">
-        <f>master!C23</f>
-        <v>AIの強みを生かすポイント</v>
-      </c>
-      <c r="D36" s="117" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" s="118"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="55" t="s">
-        <v>126</v>
+      <c r="B36" s="121"/>
+      <c r="C36" s="54" t="str">
+        <f>master!C25</f>
+        <v>2-1　背景目的</v>
+      </c>
+      <c r="D36" s="118" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" s="119"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J36" s="50">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K36" s="46"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="15" customHeight="1">
+    <row r="37" spans="1:14" ht="113.4">
       <c r="A37" s="11"/>
-      <c r="B37" s="123" t="str">
-        <f>master!B24</f>
-        <v>AI-Native研修の目的</v>
-      </c>
-      <c r="C37" s="55" t="str">
-        <f>master!C24</f>
-        <v>1.研修概要</v>
-      </c>
-      <c r="D37" s="117"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="55" t="s">
-        <v>122</v>
+      <c r="B37" s="121"/>
+      <c r="C37" s="54" t="str">
+        <f>master!C26</f>
+        <v>2-3　研修のゴールと獲得可能な経験</v>
+      </c>
+      <c r="D37" s="118" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" s="119"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="54" t="s">
+        <v>127</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="52" t="s">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="J37" s="50">
-        <v>0</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K37" s="46"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:14" ht="15" customHeight="1">
+    <row r="38" spans="1:14" ht="25.2">
       <c r="A38" s="11"/>
-      <c r="B38" s="123"/>
-      <c r="C38" s="55" t="str">
-        <f>master!C25</f>
-        <v>2-1　背景目的</v>
-      </c>
-      <c r="D38" s="117" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" s="118"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="55" t="s">
-        <v>122</v>
+      <c r="B38" s="121"/>
+      <c r="C38" s="54" t="str">
+        <f>master!C27</f>
+        <v>AIエージェントを用いたシステム開発タスクの実行の大まかな流れ</v>
+      </c>
+      <c r="D38" s="118" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" s="119"/>
+      <c r="F38" s="120"/>
+      <c r="G38" s="54" t="s">
+        <v>132</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J38" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K38" s="46"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="113.4">
+    <row r="39" spans="1:14" ht="25.2">
       <c r="A39" s="11"/>
-      <c r="B39" s="123"/>
-      <c r="C39" s="55" t="str">
-        <f>master!C26</f>
-        <v>2-3　研修のゴールと獲得可能な経験</v>
-      </c>
-      <c r="D39" s="117" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" s="118"/>
-      <c r="F39" s="119"/>
-      <c r="G39" s="55" t="s">
-        <v>129</v>
+      <c r="B39" s="121"/>
+      <c r="C39" s="54" t="str">
+        <f>master!C28</f>
+        <v>学ぶ範囲</v>
+      </c>
+      <c r="D39" s="118" t="s">
+        <v>164</v>
+      </c>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="54" t="s">
+        <v>132</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J39" s="50">
         <v>2.0833333333333333E-3</v>
@@ -5221,395 +5190,393 @@
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="25.2">
+    <row r="40" spans="1:14" ht="50.4">
       <c r="A40" s="11"/>
-      <c r="B40" s="123"/>
-      <c r="C40" s="55" t="str">
-        <f>master!C27</f>
-        <v>AIエージェントを用いたシステム開発タスクの実行の大まかな流れ</v>
-      </c>
-      <c r="D40" s="117" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" s="118"/>
-      <c r="F40" s="119"/>
-      <c r="G40" s="55" t="s">
-        <v>134</v>
+      <c r="B40" s="121" t="str">
+        <f>master!B29</f>
+        <v>キャリア編</v>
+      </c>
+      <c r="C40" s="54" t="str">
+        <f>master!C29</f>
+        <v>おまけ：新人の仕事はどうなるか？ これまで</v>
+      </c>
+      <c r="D40" s="118" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" s="119"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J40" s="50">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K40" s="46"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K40" s="46" t="s">
+        <v>201</v>
+      </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="25.2">
+    <row r="41" spans="1:14" ht="63">
       <c r="A41" s="11"/>
-      <c r="B41" s="123"/>
-      <c r="C41" s="55" t="str">
-        <f>master!C28</f>
-        <v>学ぶ範囲</v>
-      </c>
-      <c r="D41" s="117" t="s">
-        <v>166</v>
-      </c>
-      <c r="E41" s="118"/>
-      <c r="F41" s="119"/>
-      <c r="G41" s="55" t="s">
-        <v>134</v>
+      <c r="B41" s="121"/>
+      <c r="C41" s="54" t="str">
+        <f>master!C30</f>
+        <v>おまけ：生成AI before/after</v>
+      </c>
+      <c r="D41" s="118" t="s">
+        <v>167</v>
+      </c>
+      <c r="E41" s="119"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="54" t="s">
+        <v>123</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J41" s="50">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K41" s="46"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K41" s="46" t="s">
+        <v>201</v>
+      </c>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" ht="50.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="123" t="str">
-        <f>master!B29</f>
-        <v>キャリア編</v>
-      </c>
-      <c r="C42" s="55" t="str">
-        <f>master!C29</f>
-        <v>おまけ：新人の仕事はどうなるか？ これまで</v>
-      </c>
-      <c r="D42" s="117" t="s">
-        <v>168</v>
-      </c>
-      <c r="E42" s="118"/>
-      <c r="F42" s="119"/>
-      <c r="G42" s="55" t="s">
-        <v>127</v>
+      <c r="B42" s="121"/>
+      <c r="C42" s="54" t="str">
+        <f>master!C31</f>
+        <v>おまけ：新人の仕事はどうなるか？　これから</v>
+      </c>
+      <c r="D42" s="118" t="s">
+        <v>165</v>
+      </c>
+      <c r="E42" s="119"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J42" s="50">
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" ht="63">
+    <row r="43" spans="1:14" ht="100.8">
       <c r="A43" s="11"/>
-      <c r="B43" s="123"/>
-      <c r="C43" s="55" t="str">
-        <f>master!C30</f>
-        <v>おまけ：生成AI before/after</v>
-      </c>
-      <c r="D43" s="117" t="s">
-        <v>169</v>
-      </c>
-      <c r="E43" s="118"/>
-      <c r="F43" s="119"/>
-      <c r="G43" s="55" t="s">
-        <v>125</v>
+      <c r="B43" s="121"/>
+      <c r="C43" s="54" t="str">
+        <f>master!C32</f>
+        <v>代表的な若手の仕事</v>
+      </c>
+      <c r="D43" s="118" t="s">
+        <v>168</v>
+      </c>
+      <c r="E43" s="119"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="54" t="s">
+        <v>144</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J43" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K43" s="46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="50.4">
+    <row r="44" spans="1:14" ht="88.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="123"/>
-      <c r="C44" s="55" t="str">
-        <f>master!C31</f>
-        <v>おまけ：新人の仕事はどうなるか？　これから</v>
-      </c>
-      <c r="D44" s="117" t="s">
-        <v>167</v>
-      </c>
-      <c r="E44" s="118"/>
-      <c r="F44" s="119"/>
-      <c r="G44" s="55" t="s">
-        <v>127</v>
+      <c r="B44" s="121"/>
+      <c r="C44" s="54" t="str">
+        <f>master!C33</f>
+        <v>そもそも</v>
+      </c>
+      <c r="D44" s="118" t="s">
+        <v>172</v>
+      </c>
+      <c r="E44" s="119"/>
+      <c r="F44" s="120"/>
+      <c r="G44" s="54" t="s">
+        <v>130</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J44" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K44" s="46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="100.8">
+    <row r="45" spans="1:14" ht="37.799999999999997">
       <c r="A45" s="11"/>
-      <c r="B45" s="123"/>
-      <c r="C45" s="55" t="str">
-        <f>master!C32</f>
-        <v>代表的な若手の仕事</v>
-      </c>
-      <c r="D45" s="117" t="s">
-        <v>170</v>
-      </c>
-      <c r="E45" s="118"/>
-      <c r="F45" s="119"/>
-      <c r="G45" s="55" t="s">
-        <v>146</v>
+      <c r="B45" s="121"/>
+      <c r="C45" s="54" t="str">
+        <f>master!C34</f>
+        <v>2040年の就業構造推計（改定版）の概要</v>
+      </c>
+      <c r="D45" s="118" t="s">
+        <v>169</v>
+      </c>
+      <c r="E45" s="119"/>
+      <c r="F45" s="120"/>
+      <c r="G45" s="54" t="s">
+        <v>124</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J45" s="50">
         <v>2.0833333333333333E-3</v>
       </c>
       <c r="K45" s="46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="1:14" ht="88.2">
+    <row r="46" spans="1:14" ht="50.4">
       <c r="A46" s="11"/>
-      <c r="B46" s="123"/>
-      <c r="C46" s="55" t="str">
-        <f>master!C33</f>
-        <v>そもそも</v>
-      </c>
-      <c r="D46" s="117" t="s">
-        <v>174</v>
-      </c>
-      <c r="E46" s="118"/>
-      <c r="F46" s="119"/>
-      <c r="G46" s="55" t="s">
-        <v>132</v>
+      <c r="B46" s="121"/>
+      <c r="C46" s="54" t="str">
+        <f>master!C35</f>
+        <v>全国版就業構造推計（改定版）・職業間ミスマッチ</v>
+      </c>
+      <c r="D46" s="118" t="s">
+        <v>170</v>
+      </c>
+      <c r="E46" s="119"/>
+      <c r="F46" s="120"/>
+      <c r="G46" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J46" s="50">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K46" s="46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:14" ht="37.799999999999997">
+    <row r="47" spans="1:14" ht="50.4">
       <c r="A47" s="11"/>
-      <c r="B47" s="123"/>
-      <c r="C47" s="55" t="str">
-        <f>master!C34</f>
-        <v>2040年の就業構造推計（改定版）の概要</v>
-      </c>
-      <c r="D47" s="117" t="s">
+      <c r="B47" s="121"/>
+      <c r="C47" s="54" t="str">
+        <f>master!C36</f>
+        <v>（参考）将来の産業構造は・・・</v>
+      </c>
+      <c r="D47" s="118" t="s">
         <v>171</v>
       </c>
-      <c r="E47" s="118"/>
-      <c r="F47" s="119"/>
-      <c r="G47" s="55" t="s">
-        <v>126</v>
+      <c r="E47" s="119"/>
+      <c r="F47" s="120"/>
+      <c r="G47" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J47" s="50">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K47" s="46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="50.4">
+    <row r="48" spans="1:14" ht="75.599999999999994">
       <c r="A48" s="11"/>
-      <c r="B48" s="123"/>
-      <c r="C48" s="55" t="str">
-        <f>master!C35</f>
-        <v>全国版就業構造推計（改定版）・職業間ミスマッチ</v>
-      </c>
-      <c r="D48" s="117" t="s">
-        <v>172</v>
-      </c>
-      <c r="E48" s="118"/>
-      <c r="F48" s="119"/>
-      <c r="G48" s="55" t="s">
-        <v>127</v>
+      <c r="B48" s="121"/>
+      <c r="C48" s="54" t="str">
+        <f>master!C37</f>
+        <v>ヒント１：生成ＡＩと原理原則</v>
+      </c>
+      <c r="D48" s="118" t="s">
+        <v>143</v>
+      </c>
+      <c r="E48" s="119"/>
+      <c r="F48" s="120"/>
+      <c r="G48" s="54" t="s">
+        <v>126</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J48" s="50">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K48" s="46" t="s">
-        <v>204</v>
-      </c>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K48" s="46"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="123"/>
-      <c r="C49" s="55" t="str">
-        <f>master!C36</f>
-        <v>（参考）将来の産業構造は・・・</v>
-      </c>
-      <c r="D49" s="117" t="s">
-        <v>173</v>
-      </c>
-      <c r="E49" s="118"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="55" t="s">
-        <v>127</v>
+      <c r="B49" s="121"/>
+      <c r="C49" s="54" t="str">
+        <f>master!C38</f>
+        <v>ヒント2：プロンプトによる生成AIの挙動の違い</v>
+      </c>
+      <c r="D49" s="118" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="119"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J49" s="50">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K49" s="46" t="s">
-        <v>204</v>
-      </c>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K49" s="46"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="75.599999999999994">
+    <row r="50" spans="1:14" ht="189">
       <c r="A50" s="11"/>
-      <c r="B50" s="123"/>
-      <c r="C50" s="55" t="str">
-        <f>master!C37</f>
-        <v>ヒント１：生成ＡＩと原理原則</v>
-      </c>
-      <c r="D50" s="117" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" s="118"/>
-      <c r="F50" s="119"/>
-      <c r="G50" s="55" t="s">
-        <v>128</v>
+      <c r="B50" s="121"/>
+      <c r="C50" s="54" t="str">
+        <f>master!C39</f>
+        <v>ヒント３：それでも生成AIを積極的に使うしかない</v>
+      </c>
+      <c r="D50" s="118" t="s">
+        <v>203</v>
+      </c>
+      <c r="E50" s="119"/>
+      <c r="F50" s="120"/>
+      <c r="G50" s="54" t="s">
+        <v>134</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J50" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K50" s="46"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14" ht="50.4">
+    <row r="51" spans="1:14">
       <c r="A51" s="11"/>
-      <c r="B51" s="123"/>
-      <c r="C51" s="55" t="str">
-        <f>master!C38</f>
-        <v>ヒント2：プロンプトによる生成AIの挙動の違い</v>
-      </c>
-      <c r="D51" s="117" t="s">
-        <v>205</v>
-      </c>
-      <c r="E51" s="118"/>
-      <c r="F51" s="119"/>
-      <c r="G51" s="55" t="s">
-        <v>127</v>
+      <c r="B51" s="121"/>
+      <c r="C51" s="54" t="str">
+        <f>master!C40</f>
+        <v>1. 研修概要</v>
+      </c>
+      <c r="D51" s="118"/>
+      <c r="E51" s="119"/>
+      <c r="F51" s="120"/>
+      <c r="G51" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="52" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="J51" s="50">
-        <v>1.3888888888888889E-3</v>
+        <v>0</v>
       </c>
       <c r="K51" s="46"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" ht="189">
+    <row r="52" spans="1:14" ht="15" customHeight="1">
       <c r="A52" s="11"/>
-      <c r="B52" s="123"/>
-      <c r="C52" s="55" t="str">
-        <f>master!C39</f>
-        <v>ヒント３：それでも生成AIを積極的に使うしかない</v>
-      </c>
-      <c r="D52" s="117" t="s">
-        <v>206</v>
-      </c>
-      <c r="E52" s="118"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="55" t="s">
-        <v>136</v>
+      <c r="B52" s="121"/>
+      <c r="C52" s="54" t="str">
+        <f>master!C41</f>
+        <v>デジタルブートキャンプの目的</v>
+      </c>
+      <c r="D52" s="118"/>
+      <c r="E52" s="119"/>
+      <c r="F52" s="120"/>
+      <c r="G52" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J52" s="50">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K52" s="46"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="123"/>
-      <c r="C53" s="55" t="str">
-        <f>master!C40</f>
-        <v>1. 研修概要</v>
-      </c>
-      <c r="D53" s="117"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="55" t="s">
-        <v>122</v>
+      <c r="B53" s="121"/>
+      <c r="C53" s="54" t="str">
+        <f>master!C42</f>
+        <v>まとめ</v>
+      </c>
+      <c r="D53" s="118" t="s">
+        <v>173</v>
+      </c>
+      <c r="E53" s="119"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="52" t="s">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="J53" s="50">
-        <v>0</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K53" s="46"/>
       <c r="L53" s="6"/>
@@ -5618,20 +5585,25 @@
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
       <c r="A54" s="11"/>
-      <c r="B54" s="123"/>
-      <c r="C54" s="55" t="str">
-        <f>master!C41</f>
-        <v>デジタルブートキャンプの目的</v>
-      </c>
-      <c r="D54" s="117"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="55" t="s">
-        <v>122</v>
+      <c r="B54" s="121" t="str">
+        <f>master!B43</f>
+        <v>NTTデータの強み編</v>
+      </c>
+      <c r="C54" s="54" t="str">
+        <f>master!C43</f>
+        <v>2025年の変動</v>
+      </c>
+      <c r="D54" s="118" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="119"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J54" s="50">
         <v>6.9444444444444447E-4</v>
@@ -5643,79 +5615,76 @@
     </row>
     <row r="55" spans="1:14" ht="50.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="123"/>
-      <c r="C55" s="55" t="str">
-        <f>master!C42</f>
-        <v>まとめ</v>
-      </c>
-      <c r="D55" s="117" t="s">
-        <v>175</v>
-      </c>
-      <c r="E55" s="118"/>
-      <c r="F55" s="119"/>
-      <c r="G55" s="55" t="s">
-        <v>127</v>
+      <c r="B55" s="121"/>
+      <c r="C55" s="54" t="str">
+        <f>master!C44</f>
+        <v>2025年の変動　AIエージェントの台頭</v>
+      </c>
+      <c r="D55" s="118" t="s">
+        <v>182</v>
+      </c>
+      <c r="E55" s="119"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J55" s="50">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K55" s="46"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:14" ht="15" customHeight="1">
+    <row r="56" spans="1:14" ht="50.4">
       <c r="A56" s="11"/>
-      <c r="B56" s="123" t="str">
-        <f>master!B43</f>
-        <v>NTTデータの強み編</v>
-      </c>
-      <c r="C56" s="55" t="str">
-        <f>master!C43</f>
-        <v>2025年の変動</v>
-      </c>
-      <c r="D56" s="117" t="s">
-        <v>148</v>
-      </c>
-      <c r="E56" s="118"/>
-      <c r="F56" s="119"/>
-      <c r="G56" s="55" t="s">
-        <v>122</v>
+      <c r="B56" s="121"/>
+      <c r="C56" s="54" t="str">
+        <f>master!C45</f>
+        <v>2025年の変動　Vibe Coding</v>
+      </c>
+      <c r="D56" s="118" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" s="119"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J56" s="50">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K56" s="46"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="50.4">
+    <row r="57" spans="1:14" ht="75.599999999999994">
       <c r="A57" s="11"/>
-      <c r="B57" s="123"/>
-      <c r="C57" s="55" t="str">
-        <f>master!C44</f>
-        <v>2025年の変動　AIエージェントの台頭</v>
-      </c>
-      <c r="D57" s="117" t="s">
-        <v>184</v>
-      </c>
-      <c r="E57" s="118"/>
-      <c r="F57" s="119"/>
-      <c r="G57" s="55" t="s">
-        <v>127</v>
+      <c r="B57" s="121"/>
+      <c r="C57" s="54" t="str">
+        <f>master!C46</f>
+        <v>2025年の変動　Spec Driven Development</v>
+      </c>
+      <c r="D57" s="118" t="s">
+        <v>179</v>
+      </c>
+      <c r="E57" s="119"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="54" t="s">
+        <v>126</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J57" s="50">
         <v>2.0833333333333333E-3</v>
@@ -5727,22 +5696,22 @@
     </row>
     <row r="58" spans="1:14" ht="50.4">
       <c r="A58" s="11"/>
-      <c r="B58" s="123"/>
-      <c r="C58" s="55" t="str">
-        <f>master!C45</f>
-        <v>2025年の変動　Vibe Coding</v>
-      </c>
-      <c r="D58" s="117" t="s">
-        <v>183</v>
-      </c>
-      <c r="E58" s="118"/>
-      <c r="F58" s="119"/>
-      <c r="G58" s="55" t="s">
-        <v>127</v>
+      <c r="B58" s="121"/>
+      <c r="C58" s="54" t="str">
+        <f>master!C47</f>
+        <v>2025年の変動　ハーネスエンジニアリング</v>
+      </c>
+      <c r="D58" s="118" t="s">
+        <v>180</v>
+      </c>
+      <c r="E58" s="119"/>
+      <c r="F58" s="120"/>
+      <c r="G58" s="54" t="s">
+        <v>125</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J58" s="50">
         <v>2.0833333333333333E-3</v>
@@ -5754,22 +5723,22 @@
     </row>
     <row r="59" spans="1:14" ht="75.599999999999994">
       <c r="A59" s="11"/>
-      <c r="B59" s="123"/>
-      <c r="C59" s="55" t="str">
-        <f>master!C46</f>
-        <v>2025年の変動　Spec Driven Development</v>
-      </c>
-      <c r="D59" s="117" t="s">
-        <v>181</v>
-      </c>
-      <c r="E59" s="118"/>
-      <c r="F59" s="119"/>
-      <c r="G59" s="55" t="s">
-        <v>128</v>
+      <c r="B59" s="121"/>
+      <c r="C59" s="54" t="str">
+        <f>master!C48</f>
+        <v>2025年の変動　動向まとめ</v>
+      </c>
+      <c r="D59" s="118" t="s">
+        <v>183</v>
+      </c>
+      <c r="E59" s="119"/>
+      <c r="F59" s="120"/>
+      <c r="G59" s="54" t="s">
+        <v>126</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J59" s="50">
         <v>2.0833333333333333E-3</v>
@@ -5779,24 +5748,24 @@
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:14" ht="50.4">
+    <row r="60" spans="1:14" ht="113.4">
       <c r="A60" s="11"/>
-      <c r="B60" s="123"/>
-      <c r="C60" s="55" t="str">
-        <f>master!C47</f>
-        <v>2025年の変動　ハーネスエンジニアリング</v>
-      </c>
-      <c r="D60" s="117" t="s">
-        <v>182</v>
-      </c>
-      <c r="E60" s="118"/>
-      <c r="F60" s="119"/>
-      <c r="G60" s="55" t="s">
+      <c r="B60" s="121"/>
+      <c r="C60" s="54" t="str">
+        <f>master!C49</f>
+        <v>2026年 ソフトウェア開発における課題とNTTDグループの強み</v>
+      </c>
+      <c r="D60" s="118" t="s">
+        <v>186</v>
+      </c>
+      <c r="E60" s="119"/>
+      <c r="F60" s="120"/>
+      <c r="G60" s="54" t="s">
         <v>127</v>
       </c>
       <c r="H60" s="12"/>
       <c r="I60" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J60" s="50">
         <v>2.0833333333333333E-3</v>
@@ -5806,1139 +5775,1068 @@
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:14" ht="75.599999999999994">
+    <row r="61" spans="1:14" ht="25.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="123"/>
-      <c r="C61" s="55" t="str">
-        <f>master!C48</f>
-        <v>2025年の変動　動向まとめ</v>
-      </c>
-      <c r="D61" s="117" t="s">
-        <v>185</v>
-      </c>
-      <c r="E61" s="118"/>
-      <c r="F61" s="119"/>
-      <c r="G61" s="55" t="s">
-        <v>128</v>
+      <c r="B61" s="121"/>
+      <c r="C61" s="54" t="str">
+        <f>master!C50</f>
+        <v>2025年の変動</v>
+      </c>
+      <c r="D61" s="118" t="s">
+        <v>187</v>
+      </c>
+      <c r="E61" s="119"/>
+      <c r="F61" s="120"/>
+      <c r="G61" s="54" t="s">
+        <v>132</v>
       </c>
       <c r="H61" s="12"/>
       <c r="I61" s="52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J61" s="50">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K61" s="46"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:14" ht="113.4">
+    <row r="62" spans="1:14" ht="15" customHeight="1">
       <c r="A62" s="11"/>
-      <c r="B62" s="123"/>
-      <c r="C62" s="55" t="str">
-        <f>master!C49</f>
-        <v>2026年 ソフトウェア開発における課題とNTTDグループの強み</v>
-      </c>
-      <c r="D62" s="117" t="s">
-        <v>188</v>
-      </c>
-      <c r="E62" s="118"/>
-      <c r="F62" s="119"/>
-      <c r="G62" s="55" t="s">
-        <v>129</v>
+      <c r="B62" s="77" t="str">
+        <f>master!B51</f>
+        <v>デジタルソサエティ事業部取組紹介</v>
+      </c>
+      <c r="C62" s="54" t="str">
+        <f>master!C51</f>
+        <v>ー</v>
+      </c>
+      <c r="D62" s="118"/>
+      <c r="E62" s="119"/>
+      <c r="F62" s="120"/>
+      <c r="G62" s="54" t="s">
+        <v>120</v>
       </c>
       <c r="H62" s="12"/>
       <c r="I62" s="52" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="J62" s="50">
-        <v>2.0833333333333333E-3</v>
+        <v>0</v>
       </c>
       <c r="K62" s="46"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:14" ht="25.2">
+    <row r="63" spans="1:14" ht="50.4" customHeight="1">
       <c r="A63" s="11"/>
-      <c r="B63" s="123"/>
-      <c r="C63" s="55" t="str">
-        <f>master!C50</f>
-        <v>2025年の変動</v>
-      </c>
-      <c r="D63" s="117" t="s">
-        <v>189</v>
-      </c>
-      <c r="E63" s="118"/>
-      <c r="F63" s="119"/>
-      <c r="G63" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="H63" s="12"/>
-      <c r="I63" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="J63" s="50">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K63" s="46"/>
+      <c r="B63" s="112" t="str">
+        <f>master!B52</f>
+        <v>ハンズオン編:ChatGPT</v>
+      </c>
+      <c r="C63" s="72" t="str">
+        <f>master!C52</f>
+        <v>生成ＡＩハンズオン</v>
+      </c>
+      <c r="D63" s="115"/>
+      <c r="E63" s="116"/>
+      <c r="F63" s="117"/>
+      <c r="G63" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="H63" s="73"/>
+      <c r="I63" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K63" s="76"/>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:14" ht="15" customHeight="1">
+    <row r="64" spans="1:14">
       <c r="A64" s="11"/>
-      <c r="B64" s="82" t="str">
-        <f>master!B51</f>
-        <v>デジタルソサエティ事業部取組紹介</v>
-      </c>
-      <c r="C64" s="55" t="str">
-        <f>master!C51</f>
-        <v>ー</v>
-      </c>
-      <c r="D64" s="117"/>
-      <c r="E64" s="118"/>
-      <c r="F64" s="119"/>
-      <c r="G64" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="H64" s="12"/>
-      <c r="I64" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="J64" s="50">
-        <v>0</v>
-      </c>
-      <c r="K64" s="46"/>
+      <c r="B64" s="113"/>
+      <c r="C64" s="72" t="str">
+        <f>master!C53</f>
+        <v>ChatGPTの使い方（一般チャット）</v>
+      </c>
+      <c r="D64" s="115"/>
+      <c r="E64" s="116"/>
+      <c r="F64" s="117"/>
+      <c r="G64" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="H64" s="73"/>
+      <c r="I64" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K64" s="76"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:14" ht="50.4" customHeight="1">
+    <row r="65" spans="1:14" ht="50.4">
       <c r="A65" s="11"/>
-      <c r="B65" s="126" t="str">
-        <f>master!B52</f>
-        <v>ハンズオン編:ChatGPT</v>
-      </c>
-      <c r="C65" s="77" t="str">
-        <f>master!C52</f>
-        <v>生成ＡＩハンズオン</v>
-      </c>
-      <c r="D65" s="120"/>
-      <c r="E65" s="121"/>
-      <c r="F65" s="122"/>
-      <c r="G65" s="77" t="s">
-        <v>127</v>
-      </c>
-      <c r="H65" s="78"/>
-      <c r="I65" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K65" s="81"/>
+      <c r="B65" s="113"/>
+      <c r="C65" s="72" t="str">
+        <f>master!C54</f>
+        <v>プロンプトを入れてみる</v>
+      </c>
+      <c r="D65" s="115" t="s">
+        <v>178</v>
+      </c>
+      <c r="E65" s="116"/>
+      <c r="F65" s="117"/>
+      <c r="G65" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="H65" s="73"/>
+      <c r="I65" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" s="75">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K65" s="76"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" ht="63">
       <c r="A66" s="11"/>
-      <c r="B66" s="127"/>
-      <c r="C66" s="77" t="str">
-        <f>master!C53</f>
-        <v>ChatGPTの使い方（一般チャット）</v>
-      </c>
-      <c r="D66" s="120"/>
-      <c r="E66" s="121"/>
-      <c r="F66" s="122"/>
-      <c r="G66" s="77" t="s">
-        <v>122</v>
-      </c>
-      <c r="H66" s="78"/>
-      <c r="I66" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J66" s="80">
+      <c r="B66" s="113"/>
+      <c r="C66" s="72" t="str">
+        <f>master!C55</f>
+        <v>ハンズオン例</v>
+      </c>
+      <c r="D66" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="E66" s="116"/>
+      <c r="F66" s="117"/>
+      <c r="G66" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="H66" s="73"/>
+      <c r="I66" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J66" s="75">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K66" s="81"/>
+      <c r="K66" s="76"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:14" ht="50.4">
+    <row r="67" spans="1:14" ht="126">
       <c r="A67" s="11"/>
-      <c r="B67" s="127"/>
-      <c r="C67" s="77" t="str">
-        <f>master!C54</f>
-        <v>プロンプトを入れてみる</v>
-      </c>
-      <c r="D67" s="120" t="s">
-        <v>180</v>
-      </c>
-      <c r="E67" s="121"/>
-      <c r="F67" s="122"/>
-      <c r="G67" s="77" t="s">
-        <v>127</v>
-      </c>
-      <c r="H67" s="78"/>
-      <c r="I67" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" s="80">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K67" s="81"/>
+      <c r="B67" s="113"/>
+      <c r="C67" s="72" t="str">
+        <f>master!C56</f>
+        <v>例１：【レポート作成】　佐々木社長の調査を行う</v>
+      </c>
+      <c r="D67" s="115" t="s">
+        <v>174</v>
+      </c>
+      <c r="E67" s="116"/>
+      <c r="F67" s="117"/>
+      <c r="G67" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="H67" s="73"/>
+      <c r="I67" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" s="75">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K67" s="76"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:14" ht="63">
+    <row r="68" spans="1:14" ht="126" customHeight="1">
       <c r="A68" s="11"/>
-      <c r="B68" s="127"/>
-      <c r="C68" s="77" t="str">
-        <f>master!C55</f>
-        <v>ハンズオン例</v>
-      </c>
-      <c r="D68" s="120" t="s">
-        <v>150</v>
-      </c>
-      <c r="E68" s="121"/>
-      <c r="F68" s="122"/>
-      <c r="G68" s="77" t="s">
-        <v>125</v>
-      </c>
-      <c r="H68" s="78"/>
-      <c r="I68" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J68" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K68" s="81"/>
+      <c r="B68" s="113"/>
+      <c r="C68" s="72" t="str">
+        <f>master!C57</f>
+        <v>例２：顧客提案向けの企画書を作りたい</v>
+      </c>
+      <c r="D68" s="115" t="s">
+        <v>174</v>
+      </c>
+      <c r="E68" s="116"/>
+      <c r="F68" s="117"/>
+      <c r="G68" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="H68" s="73"/>
+      <c r="I68" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J68" s="75">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K68" s="76"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:14" ht="126">
+    <row r="69" spans="1:14" ht="126" customHeight="1">
       <c r="A69" s="11"/>
-      <c r="B69" s="127"/>
-      <c r="C69" s="77" t="str">
-        <f>master!C56</f>
-        <v>例１：【レポート作成】　佐々木社長の調査を行う</v>
-      </c>
-      <c r="D69" s="120" t="s">
-        <v>176</v>
-      </c>
-      <c r="E69" s="121"/>
-      <c r="F69" s="122"/>
-      <c r="G69" s="77" t="s">
-        <v>130</v>
-      </c>
-      <c r="H69" s="78"/>
-      <c r="I69" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J69" s="80">
+      <c r="B69" s="113"/>
+      <c r="C69" s="72" t="str">
+        <f>master!C58</f>
+        <v>例３：１００本ノックを作ってみる</v>
+      </c>
+      <c r="D69" s="115" t="s">
+        <v>174</v>
+      </c>
+      <c r="E69" s="116"/>
+      <c r="F69" s="117"/>
+      <c r="G69" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="H69" s="73"/>
+      <c r="I69" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" s="75">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K69" s="81"/>
+      <c r="K69" s="76"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
-    <row r="70" spans="1:14" ht="126" customHeight="1">
+    <row r="70" spans="1:14">
       <c r="A70" s="11"/>
-      <c r="B70" s="127"/>
-      <c r="C70" s="77" t="str">
-        <f>master!C57</f>
-        <v>例２：顧客提案向けの企画書を作りたい</v>
-      </c>
-      <c r="D70" s="120" t="s">
-        <v>176</v>
-      </c>
-      <c r="E70" s="121"/>
-      <c r="F70" s="122"/>
-      <c r="G70" s="77" t="s">
-        <v>130</v>
-      </c>
-      <c r="H70" s="78"/>
-      <c r="I70" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J70" s="80">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K70" s="81"/>
+      <c r="B70" s="114"/>
+      <c r="C70" s="72" t="str">
+        <f>master!C59</f>
+        <v>ChatGPT まとめ</v>
+      </c>
+      <c r="D70" s="115"/>
+      <c r="E70" s="116"/>
+      <c r="F70" s="117"/>
+      <c r="G70" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="H70" s="73"/>
+      <c r="I70" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J70" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K70" s="76"/>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
-    <row r="71" spans="1:14" ht="126" customHeight="1">
+    <row r="71" spans="1:14" ht="15" customHeight="1">
       <c r="A71" s="11"/>
-      <c r="B71" s="127"/>
-      <c r="C71" s="77" t="str">
-        <f>master!C58</f>
-        <v>例３：１００本ノックを作ってみる</v>
-      </c>
-      <c r="D71" s="120" t="s">
-        <v>176</v>
-      </c>
-      <c r="E71" s="121"/>
-      <c r="F71" s="122"/>
-      <c r="G71" s="77" t="s">
-        <v>130</v>
-      </c>
-      <c r="H71" s="78"/>
-      <c r="I71" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J71" s="80">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K71" s="81"/>
+      <c r="B71" s="112" t="str">
+        <f>master!B60</f>
+        <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
+      </c>
+      <c r="C71" s="72" t="str">
+        <f>master!C60</f>
+        <v>生成ＡＩハンズオン</v>
+      </c>
+      <c r="D71" s="115"/>
+      <c r="E71" s="116"/>
+      <c r="F71" s="117"/>
+      <c r="G71" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="H71" s="73"/>
+      <c r="I71" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K71" s="76"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" ht="25.2">
       <c r="A72" s="11"/>
-      <c r="B72" s="128"/>
-      <c r="C72" s="77" t="str">
-        <f>master!C59</f>
-        <v>ChatGPT まとめ</v>
-      </c>
-      <c r="D72" s="120"/>
-      <c r="E72" s="121"/>
-      <c r="F72" s="122"/>
-      <c r="G72" s="77" t="s">
-        <v>122</v>
-      </c>
-      <c r="H72" s="78"/>
-      <c r="I72" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J72" s="80">
+      <c r="B72" s="113"/>
+      <c r="C72" s="72" t="str">
+        <f>master!C61</f>
+        <v>Visual Studio Code を開く</v>
+      </c>
+      <c r="D72" s="115" t="s">
+        <v>175</v>
+      </c>
+      <c r="E72" s="116"/>
+      <c r="F72" s="117"/>
+      <c r="G72" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H72" s="73"/>
+      <c r="I72" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" s="75">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K72" s="81"/>
+      <c r="K72" s="76"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
-    <row r="73" spans="1:14" ht="15" customHeight="1">
+    <row r="73" spans="1:14" ht="37.799999999999997">
       <c r="A73" s="11"/>
-      <c r="B73" s="126" t="str">
-        <f>master!B60</f>
-        <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
-      </c>
-      <c r="C73" s="77" t="str">
-        <f>master!C60</f>
-        <v>生成ＡＩハンズオン</v>
-      </c>
-      <c r="D73" s="120"/>
-      <c r="E73" s="121"/>
-      <c r="F73" s="122"/>
-      <c r="G73" s="77" t="s">
-        <v>122</v>
-      </c>
-      <c r="H73" s="78"/>
-      <c r="I73" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J73" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K73" s="81"/>
+      <c r="B73" s="113"/>
+      <c r="C73" s="72" t="str">
+        <f>master!C62</f>
+        <v>コード補完機能</v>
+      </c>
+      <c r="D73" s="115" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" s="116"/>
+      <c r="F73" s="117"/>
+      <c r="G73" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H73" s="73"/>
+      <c r="I73" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" s="75">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K73" s="76"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
-    <row r="74" spans="1:14" ht="25.2">
+    <row r="74" spans="1:14" ht="100.8">
       <c r="A74" s="11"/>
-      <c r="B74" s="127"/>
-      <c r="C74" s="77" t="str">
-        <f>master!C61</f>
-        <v>Visual Studio Code を開く</v>
-      </c>
-      <c r="D74" s="120" t="s">
+      <c r="B74" s="113"/>
+      <c r="C74" s="72" t="str">
+        <f>master!C63</f>
+        <v>チャット機能</v>
+      </c>
+      <c r="D74" s="115" t="s">
         <v>177</v>
       </c>
-      <c r="E74" s="121"/>
-      <c r="F74" s="122"/>
-      <c r="G74" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H74" s="78"/>
-      <c r="I74" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J74" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K74" s="81"/>
+      <c r="E74" s="116"/>
+      <c r="F74" s="117"/>
+      <c r="G74" s="72" t="s">
+        <v>144</v>
+      </c>
+      <c r="H74" s="73"/>
+      <c r="I74" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" s="75">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K74" s="76"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
-    <row r="75" spans="1:14" ht="37.799999999999997">
+    <row r="75" spans="1:14" ht="15" customHeight="1">
       <c r="A75" s="11"/>
-      <c r="B75" s="127"/>
-      <c r="C75" s="77" t="str">
-        <f>master!C62</f>
-        <v>コード補完機能</v>
-      </c>
-      <c r="D75" s="120" t="s">
-        <v>178</v>
-      </c>
-      <c r="E75" s="121"/>
-      <c r="F75" s="122"/>
-      <c r="G75" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="H75" s="78"/>
-      <c r="I75" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J75" s="80">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K75" s="81"/>
+      <c r="B75" s="113"/>
+      <c r="C75" s="72" t="str">
+        <f>master!C64</f>
+        <v>ChatGPT で 簡単なアプリやゲームを作ってみましょう</v>
+      </c>
+      <c r="D75" s="115"/>
+      <c r="E75" s="116"/>
+      <c r="F75" s="117"/>
+      <c r="G75" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="H75" s="73"/>
+      <c r="I75" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J75" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K75" s="76"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:14" ht="100.8">
+    <row r="76" spans="1:14" ht="25.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="127"/>
-      <c r="C76" s="77" t="str">
-        <f>master!C63</f>
-        <v>チャット機能</v>
-      </c>
-      <c r="D76" s="120" t="s">
-        <v>179</v>
-      </c>
-      <c r="E76" s="121"/>
-      <c r="F76" s="122"/>
-      <c r="G76" s="77" t="s">
-        <v>146</v>
-      </c>
-      <c r="H76" s="78"/>
-      <c r="I76" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J76" s="80">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K76" s="81"/>
+      <c r="B76" s="113"/>
+      <c r="C76" s="72" t="str">
+        <f>master!C65</f>
+        <v>例１　高級志向テトリス</v>
+      </c>
+      <c r="D76" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E76" s="116"/>
+      <c r="F76" s="117"/>
+      <c r="G76" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H76" s="73"/>
+      <c r="I76" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K76" s="76"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:14" ht="15" customHeight="1">
+    <row r="77" spans="1:14" ht="25.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="127"/>
-      <c r="C77" s="77" t="str">
-        <f>master!C64</f>
-        <v>ChatGPT で 簡単なアプリやゲームを作ってみましょう</v>
-      </c>
-      <c r="D77" s="120"/>
-      <c r="E77" s="121"/>
-      <c r="F77" s="122"/>
-      <c r="G77" s="77" t="s">
-        <v>122</v>
-      </c>
-      <c r="H77" s="78"/>
-      <c r="I77" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J77" s="80">
+      <c r="B77" s="113"/>
+      <c r="C77" s="72" t="str">
+        <f>master!C66</f>
+        <v>例）わくわく！にっぽんダーツの旅</v>
+      </c>
+      <c r="D77" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E77" s="116"/>
+      <c r="F77" s="117"/>
+      <c r="G77" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H77" s="73"/>
+      <c r="I77" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J77" s="75">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K77" s="81"/>
+      <c r="K77" s="76"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
     <row r="78" spans="1:14" ht="25.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="127"/>
-      <c r="C78" s="77" t="str">
-        <f>master!C65</f>
-        <v>例１　高級志向テトリス</v>
-      </c>
-      <c r="D78" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E78" s="121"/>
-      <c r="F78" s="122"/>
-      <c r="G78" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H78" s="78"/>
-      <c r="I78" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J78" s="80">
+      <c r="B78" s="113"/>
+      <c r="C78" s="72" t="str">
+        <f>master!C67</f>
+        <v>例）タスク管理ツール</v>
+      </c>
+      <c r="D78" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E78" s="116"/>
+      <c r="F78" s="117"/>
+      <c r="G78" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H78" s="73"/>
+      <c r="I78" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" s="75">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K78" s="81"/>
+      <c r="K78" s="76"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:14" ht="25.2">
+    <row r="79" spans="1:14" ht="126">
       <c r="A79" s="11"/>
-      <c r="B79" s="127"/>
-      <c r="C79" s="77" t="str">
-        <f>master!C66</f>
-        <v>例）わくわく！にっぽんダーツの旅</v>
-      </c>
-      <c r="D79" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E79" s="121"/>
-      <c r="F79" s="122"/>
-      <c r="G79" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H79" s="78"/>
-      <c r="I79" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J79" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K79" s="81"/>
+      <c r="B79" s="113"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="115" t="s">
+        <v>150</v>
+      </c>
+      <c r="E79" s="116"/>
+      <c r="F79" s="117"/>
+      <c r="G79" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="H79" s="73"/>
+      <c r="I79" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" s="75">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K79" s="76"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
     </row>
-    <row r="80" spans="1:14" ht="25.2">
+    <row r="80" spans="1:14" ht="63">
       <c r="A80" s="11"/>
-      <c r="B80" s="127"/>
-      <c r="C80" s="77" t="str">
-        <f>master!C67</f>
-        <v>例）タスク管理ツール</v>
-      </c>
-      <c r="D80" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E80" s="121"/>
-      <c r="F80" s="122"/>
-      <c r="G80" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H80" s="78"/>
-      <c r="I80" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J80" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K80" s="81"/>
+      <c r="B80" s="113"/>
+      <c r="C80" s="72" t="str">
+        <f>master!C68</f>
+        <v>ディレクトリ作成とファイル配置</v>
+      </c>
+      <c r="D80" s="115" t="s">
+        <v>151</v>
+      </c>
+      <c r="E80" s="116"/>
+      <c r="F80" s="117"/>
+      <c r="G80" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="H80" s="73"/>
+      <c r="I80" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" s="75">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K80" s="76"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
-    <row r="81" spans="1:14" ht="126">
+    <row r="81" spans="1:14" ht="25.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="127"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="120" t="s">
-        <v>152</v>
-      </c>
-      <c r="E81" s="121"/>
-      <c r="F81" s="122"/>
-      <c r="G81" s="77" t="s">
-        <v>130</v>
-      </c>
-      <c r="H81" s="78"/>
-      <c r="I81" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J81" s="80">
-        <v>1.0416666666666666E-2</v>
-      </c>
-      <c r="K81" s="81"/>
+      <c r="B81" s="113"/>
+      <c r="C81" s="72" t="str">
+        <f>master!C69</f>
+        <v>チャット機能：Aｓｋ</v>
+      </c>
+      <c r="D81" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E81" s="116"/>
+      <c r="F81" s="117"/>
+      <c r="G81" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H81" s="73"/>
+      <c r="I81" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J81" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K81" s="76"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
       <c r="N81" s="6"/>
     </row>
-    <row r="82" spans="1:14" ht="63">
+    <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="127"/>
-      <c r="C82" s="77" t="str">
-        <f>master!C68</f>
-        <v>ディレクトリ作成とファイル配置</v>
-      </c>
-      <c r="D82" s="120" t="s">
-        <v>153</v>
-      </c>
-      <c r="E82" s="121"/>
-      <c r="F82" s="122"/>
-      <c r="G82" s="77" t="s">
+      <c r="B82" s="113"/>
+      <c r="C82" s="72" t="str">
+        <f>master!C70</f>
+        <v>Askモードについて</v>
+      </c>
+      <c r="D82" s="115" t="s">
+        <v>184</v>
+      </c>
+      <c r="E82" s="116"/>
+      <c r="F82" s="117"/>
+      <c r="G82" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="H82" s="78"/>
-      <c r="I82" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J82" s="80">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K82" s="81"/>
+      <c r="H82" s="73"/>
+      <c r="I82" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" s="75">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K82" s="76"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
     </row>
     <row r="83" spans="1:14" ht="25.2">
       <c r="A83" s="11"/>
-      <c r="B83" s="127"/>
-      <c r="C83" s="77" t="str">
-        <f>master!C69</f>
-        <v>チャット機能：Aｓｋ</v>
-      </c>
-      <c r="D83" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E83" s="121"/>
-      <c r="F83" s="122"/>
-      <c r="G83" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H83" s="78"/>
-      <c r="I83" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J83" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K83" s="81"/>
+      <c r="B83" s="113"/>
+      <c r="C83" s="91" t="str">
+        <f>master!C71</f>
+        <v>実行例</v>
+      </c>
+      <c r="D83" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E83" s="116"/>
+      <c r="F83" s="117"/>
+      <c r="G83" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H83" s="73"/>
+      <c r="I83" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" s="75">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K83" s="76"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
-    <row r="84" spans="1:14" ht="50.4">
+    <row r="84" spans="1:14" ht="37.799999999999997">
       <c r="A84" s="11"/>
-      <c r="B84" s="127"/>
-      <c r="C84" s="77" t="str">
-        <f>master!C70</f>
-        <v>Askモードについて</v>
-      </c>
-      <c r="D84" s="120" t="s">
-        <v>186</v>
-      </c>
-      <c r="E84" s="121"/>
-      <c r="F84" s="122"/>
-      <c r="G84" s="77" t="s">
-        <v>127</v>
-      </c>
-      <c r="H84" s="78"/>
-      <c r="I84" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J84" s="80">
-        <v>1.0416666666666666E-2</v>
-      </c>
-      <c r="K84" s="81"/>
+      <c r="B84" s="113"/>
+      <c r="C84" s="92"/>
+      <c r="D84" s="115" t="s">
+        <v>204</v>
+      </c>
+      <c r="E84" s="116"/>
+      <c r="F84" s="117"/>
+      <c r="G84" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H84" s="73"/>
+      <c r="I84" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" s="75">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="K84" s="76"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
     </row>
     <row r="85" spans="1:14" ht="25.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="127"/>
-      <c r="C85" s="129" t="str">
-        <f>master!C71</f>
-        <v>実行例</v>
-      </c>
-      <c r="D85" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E85" s="121"/>
-      <c r="F85" s="122"/>
-      <c r="G85" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H85" s="78"/>
-      <c r="I85" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J85" s="80">
+      <c r="B85" s="113"/>
+      <c r="C85" s="72" t="str">
+        <f>master!C72</f>
+        <v>Askモードまとめ</v>
+      </c>
+      <c r="D85" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E85" s="116"/>
+      <c r="F85" s="117"/>
+      <c r="G85" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H85" s="73"/>
+      <c r="I85" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" s="75">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K85" s="81"/>
+      <c r="K85" s="76"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
-    <row r="86" spans="1:14" ht="37.799999999999997">
+    <row r="86" spans="1:14" ht="25.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="127"/>
-      <c r="C86" s="130"/>
-      <c r="D86" s="120" t="s">
-        <v>207</v>
-      </c>
-      <c r="E86" s="121"/>
-      <c r="F86" s="122"/>
-      <c r="G86" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="H86" s="78"/>
-      <c r="I86" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J86" s="80">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K86" s="81"/>
+      <c r="B86" s="113"/>
+      <c r="C86" s="72" t="str">
+        <f>master!C73</f>
+        <v>チャット機能：Agent</v>
+      </c>
+      <c r="D86" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E86" s="116"/>
+      <c r="F86" s="117"/>
+      <c r="G86" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H86" s="73"/>
+      <c r="I86" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" s="75">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K86" s="76"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
       <c r="N86" s="6"/>
     </row>
     <row r="87" spans="1:14" ht="25.2">
       <c r="A87" s="11"/>
-      <c r="B87" s="127"/>
-      <c r="C87" s="77" t="str">
-        <f>master!C72</f>
-        <v>Askモードまとめ</v>
-      </c>
-      <c r="D87" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E87" s="121"/>
-      <c r="F87" s="122"/>
-      <c r="G87" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H87" s="78"/>
-      <c r="I87" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J87" s="80">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K87" s="81"/>
+      <c r="B87" s="113"/>
+      <c r="C87" s="72" t="str">
+        <f>master!C74</f>
+        <v>Agentモード</v>
+      </c>
+      <c r="D87" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E87" s="116"/>
+      <c r="F87" s="117"/>
+      <c r="G87" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H87" s="73"/>
+      <c r="I87" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="75">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K87" s="76"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
       <c r="N87" s="6"/>
     </row>
-    <row r="88" spans="1:14" ht="25.2">
+    <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="127"/>
-      <c r="C88" s="77" t="str">
-        <f>master!C73</f>
-        <v>チャット機能：Agent</v>
-      </c>
-      <c r="D88" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E88" s="121"/>
-      <c r="F88" s="122"/>
-      <c r="G88" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H88" s="78"/>
-      <c r="I88" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J88" s="80">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K88" s="81"/>
+      <c r="B88" s="113"/>
+      <c r="C88" s="72" t="str">
+        <f>master!C75</f>
+        <v>実行例</v>
+      </c>
+      <c r="D88" s="115" t="s">
+        <v>184</v>
+      </c>
+      <c r="E88" s="116"/>
+      <c r="F88" s="117"/>
+      <c r="G88" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H88" s="73"/>
+      <c r="I88" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" s="75">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K88" s="76"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
-    <row r="89" spans="1:14" ht="25.2">
+    <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="127"/>
-      <c r="C89" s="77" t="str">
-        <f>master!C74</f>
-        <v>Agentモード</v>
-      </c>
-      <c r="D89" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E89" s="121"/>
-      <c r="F89" s="122"/>
-      <c r="G89" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H89" s="78"/>
-      <c r="I89" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J89" s="80">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K89" s="81"/>
+      <c r="B89" s="113"/>
+      <c r="C89" s="72" t="str">
+        <f>master!C76</f>
+        <v>READMEの内容を確認しましょう</v>
+      </c>
+      <c r="D89" s="115" t="s">
+        <v>184</v>
+      </c>
+      <c r="E89" s="116"/>
+      <c r="F89" s="117"/>
+      <c r="G89" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H89" s="73"/>
+      <c r="I89" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" s="75">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K89" s="76"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
     <row r="90" spans="1:14" ht="37.799999999999997">
       <c r="A90" s="11"/>
-      <c r="B90" s="127"/>
-      <c r="C90" s="77" t="str">
-        <f>master!C75</f>
-        <v>実行例</v>
-      </c>
-      <c r="D90" s="120" t="s">
-        <v>186</v>
-      </c>
-      <c r="E90" s="121"/>
-      <c r="F90" s="122"/>
-      <c r="G90" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="H90" s="78"/>
-      <c r="I90" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J90" s="80">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K90" s="81"/>
+      <c r="B90" s="113"/>
+      <c r="C90" s="91" t="str">
+        <f>master!C77</f>
+        <v>Changeログを作ってみましょう</v>
+      </c>
+      <c r="D90" s="115" t="s">
+        <v>184</v>
+      </c>
+      <c r="E90" s="116"/>
+      <c r="F90" s="117"/>
+      <c r="G90" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H90" s="73"/>
+      <c r="I90" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K90" s="76"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" ht="37.799999999999997">
       <c r="A91" s="11"/>
-      <c r="B91" s="127"/>
-      <c r="C91" s="77" t="str">
-        <f>master!C76</f>
-        <v>READMEの内容を確認しましょう</v>
-      </c>
-      <c r="D91" s="120" t="s">
-        <v>186</v>
-      </c>
-      <c r="E91" s="121"/>
-      <c r="F91" s="122"/>
-      <c r="G91" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="H91" s="78"/>
-      <c r="I91" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J91" s="80">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K91" s="81"/>
+      <c r="B91" s="113"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="115" t="s">
+        <v>200</v>
+      </c>
+      <c r="E91" s="116"/>
+      <c r="F91" s="117"/>
+      <c r="G91" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H91" s="73"/>
+      <c r="I91" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" s="75">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K91" s="76"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:14" ht="37.799999999999997">
+    <row r="92" spans="1:14" ht="25.2">
       <c r="A92" s="11"/>
-      <c r="B92" s="127"/>
-      <c r="C92" s="129" t="str">
-        <f>master!C77</f>
-        <v>Changeログを作ってみましょう</v>
-      </c>
-      <c r="D92" s="120" t="s">
-        <v>186</v>
-      </c>
-      <c r="E92" s="121"/>
-      <c r="F92" s="122"/>
-      <c r="G92" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="H92" s="78"/>
-      <c r="I92" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J92" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K92" s="81"/>
+      <c r="B92" s="113"/>
+      <c r="C92" s="72" t="str">
+        <f>master!C78</f>
+        <v>チャット機能：Plan</v>
+      </c>
+      <c r="D92" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E92" s="116"/>
+      <c r="F92" s="117"/>
+      <c r="G92" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H92" s="73"/>
+      <c r="I92" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" s="75">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K92" s="76"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
     <row r="93" spans="1:14" ht="37.799999999999997">
       <c r="A93" s="11"/>
-      <c r="B93" s="127"/>
-      <c r="C93" s="130"/>
-      <c r="D93" s="120" t="s">
-        <v>203</v>
-      </c>
-      <c r="E93" s="121"/>
-      <c r="F93" s="122"/>
-      <c r="G93" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="H93" s="78"/>
-      <c r="I93" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J93" s="80">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K93" s="81"/>
+      <c r="B93" s="113"/>
+      <c r="C93" s="72" t="str">
+        <f>master!C79</f>
+        <v>Planモードで機能追加してみましょう</v>
+      </c>
+      <c r="D93" s="115" t="s">
+        <v>184</v>
+      </c>
+      <c r="E93" s="116"/>
+      <c r="F93" s="117"/>
+      <c r="G93" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H93" s="73"/>
+      <c r="I93" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" s="75">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K93" s="76"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
     </row>
     <row r="94" spans="1:14" ht="25.2">
       <c r="A94" s="11"/>
-      <c r="B94" s="127"/>
-      <c r="C94" s="77" t="str">
-        <f>master!C78</f>
-        <v>チャット機能：Plan</v>
-      </c>
-      <c r="D94" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E94" s="121"/>
-      <c r="F94" s="122"/>
-      <c r="G94" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H94" s="78"/>
-      <c r="I94" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J94" s="80">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K94" s="81"/>
+      <c r="B94" s="113"/>
+      <c r="C94" s="72" t="str">
+        <f>master!C80</f>
+        <v>実行例</v>
+      </c>
+      <c r="D94" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E94" s="116"/>
+      <c r="F94" s="117"/>
+      <c r="G94" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H94" s="73"/>
+      <c r="I94" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J94" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K94" s="76"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
-    <row r="95" spans="1:14" ht="37.799999999999997">
+    <row r="95" spans="1:14" ht="25.2">
       <c r="A95" s="11"/>
-      <c r="B95" s="127"/>
-      <c r="C95" s="77" t="str">
-        <f>master!C79</f>
-        <v>Planモードで機能追加してみましょう</v>
-      </c>
-      <c r="D95" s="120" t="s">
-        <v>186</v>
-      </c>
-      <c r="E95" s="121"/>
-      <c r="F95" s="122"/>
-      <c r="G95" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="H95" s="78"/>
-      <c r="I95" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J95" s="80">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K95" s="81"/>
+      <c r="B95" s="113"/>
+      <c r="C95" s="91" t="str">
+        <f>master!C81</f>
+        <v>実行結果</v>
+      </c>
+      <c r="D95" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E95" s="116"/>
+      <c r="F95" s="117"/>
+      <c r="G95" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H95" s="73"/>
+      <c r="I95" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" s="75">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K95" s="76"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
-    <row r="96" spans="1:14" ht="25.2">
+    <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="127"/>
-      <c r="C96" s="77" t="str">
-        <f>master!C80</f>
-        <v>実行例</v>
-      </c>
-      <c r="D96" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E96" s="121"/>
-      <c r="F96" s="122"/>
-      <c r="G96" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H96" s="78"/>
-      <c r="I96" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J96" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K96" s="81"/>
+      <c r="B96" s="113"/>
+      <c r="C96" s="92"/>
+      <c r="D96" s="115" t="s">
+        <v>200</v>
+      </c>
+      <c r="E96" s="116"/>
+      <c r="F96" s="117"/>
+      <c r="G96" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="H96" s="73"/>
+      <c r="I96" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J96" s="75">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K96" s="76"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
       <c r="N96" s="6"/>
     </row>
     <row r="97" spans="1:14" ht="25.2">
       <c r="A97" s="11"/>
-      <c r="B97" s="127"/>
-      <c r="C97" s="129" t="str">
-        <f>master!C81</f>
-        <v>実行結果</v>
-      </c>
-      <c r="D97" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E97" s="121"/>
-      <c r="F97" s="122"/>
-      <c r="G97" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H97" s="78"/>
-      <c r="I97" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J97" s="80">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K97" s="81"/>
+      <c r="B97" s="113"/>
+      <c r="C97" s="72" t="str">
+        <f>master!C82</f>
+        <v>Planモード＆Agentモードまとめ</v>
+      </c>
+      <c r="D97" s="115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E97" s="116"/>
+      <c r="F97" s="117"/>
+      <c r="G97" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H97" s="73"/>
+      <c r="I97" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J97" s="75">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K97" s="76"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
-    <row r="98" spans="1:14" ht="37.799999999999997">
+    <row r="98" spans="1:14" ht="113.4">
       <c r="A98" s="11"/>
-      <c r="B98" s="127"/>
-      <c r="C98" s="130"/>
-      <c r="D98" s="120" t="s">
-        <v>203</v>
-      </c>
-      <c r="E98" s="121"/>
-      <c r="F98" s="122"/>
-      <c r="G98" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="H98" s="78"/>
-      <c r="I98" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J98" s="80">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K98" s="81"/>
+      <c r="B98" s="88" t="str">
+        <f>master!B83</f>
+        <v>プレゼン</v>
+      </c>
+      <c r="C98" s="72" t="str">
+        <f>master!C83</f>
+        <v>開発したゲームやアプリをプレゼン</v>
+      </c>
+      <c r="D98" s="115" t="s">
+        <v>199</v>
+      </c>
+      <c r="E98" s="116"/>
+      <c r="F98" s="117"/>
+      <c r="G98" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="H98" s="73"/>
+      <c r="I98" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J98" s="75">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K98" s="76" t="s">
+        <v>196</v>
+      </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
     </row>
-    <row r="99" spans="1:14" ht="25.2">
-      <c r="A99" s="11"/>
-      <c r="B99" s="127"/>
-      <c r="C99" s="77" t="str">
-        <f>master!C82</f>
-        <v>Planモード＆Agentモードまとめ</v>
-      </c>
-      <c r="D99" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="E99" s="121"/>
-      <c r="F99" s="122"/>
-      <c r="G99" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="H99" s="78"/>
-      <c r="I99" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J99" s="80">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K99" s="81"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="6"/>
-      <c r="N99" s="6"/>
-    </row>
-    <row r="100" spans="1:14" ht="113.4">
-      <c r="A100" s="11"/>
-      <c r="B100" s="94" t="str">
-        <f>master!B83</f>
-        <v>プレゼン</v>
-      </c>
-      <c r="C100" s="77" t="str">
-        <f>master!C83</f>
-        <v>開発したゲームやアプリをプレゼン</v>
-      </c>
-      <c r="D100" s="120" t="s">
-        <v>202</v>
-      </c>
-      <c r="E100" s="121"/>
-      <c r="F100" s="122"/>
-      <c r="G100" s="77" t="s">
-        <v>129</v>
-      </c>
-      <c r="H100" s="78"/>
-      <c r="I100" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J100" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K100" s="81" t="s">
-        <v>199</v>
-      </c>
-      <c r="L100" s="6"/>
-      <c r="M100" s="6"/>
-      <c r="N100" s="6"/>
-    </row>
-    <row r="101" spans="1:14" ht="15" customHeight="1">
-      <c r="J101" s="49"/>
-    </row>
-    <row r="102" spans="1:14" ht="15" customHeight="1"/>
+    <row r="99" spans="1:14" ht="15" customHeight="1">
+      <c r="J99" s="49"/>
+    </row>
+    <row r="100" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B65:B72"/>
-    <mergeCell ref="B73:B99"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B15:B25"/>
+    <mergeCell ref="B26:B34"/>
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="D46:F46"/>
     <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B56:B63"/>
-    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="B40:B53"/>
+    <mergeCell ref="B54:B61"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="D34:F34"/>
     <mergeCell ref="D35:F35"/>
@@ -6949,42 +6847,59 @@
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
     <mergeCell ref="D58:F58"/>
     <mergeCell ref="D59:F59"/>
-    <mergeCell ref="B17:B27"/>
-    <mergeCell ref="B28:B36"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="B63:B70"/>
+    <mergeCell ref="B71:B97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6997,7 +6912,7 @@
           <x14:formula1>
             <xm:f>master!$C$48:$C$50</xm:f>
           </x14:formula1>
-          <xm:sqref>H15:H100</xm:sqref>
+          <xm:sqref>H13:H98</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7008,460 +6923,460 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:C83"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="9.6"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="40.109375" style="75" customWidth="1"/>
-    <col min="3" max="3" width="44" style="75" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="75"/>
+    <col min="1" max="1" width="4.6640625" style="125" customWidth="1"/>
+    <col min="2" max="2" width="40.109375" style="125" customWidth="1"/>
+    <col min="3" max="3" width="44" style="125" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3">
-      <c r="B1" s="75" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3">
-      <c r="B2" s="76" t="s">
+    <row r="1" spans="2:3" s="125" customFormat="1">
+      <c r="B1" s="125" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" s="125" customFormat="1">
+      <c r="B2" s="126" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="76" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3">
-      <c r="B3" s="75" t="s">
+    </row>
+    <row r="3" spans="2:3" s="125" customFormat="1">
+      <c r="B3" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="125" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" s="125" customFormat="1">
+      <c r="B4" s="125" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="125" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" s="125" customFormat="1">
+      <c r="C5" s="125" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" s="125" customFormat="1">
+      <c r="C6" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="75" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3">
-      <c r="B4" s="75" t="s">
+    </row>
+    <row r="7" spans="2:3" s="125" customFormat="1">
+      <c r="C7" s="125" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" s="125" customFormat="1">
+      <c r="C8" s="125" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" s="125" customFormat="1">
+      <c r="C9" s="125" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" s="125" customFormat="1">
+      <c r="C10" s="125" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" s="125" customFormat="1">
+      <c r="C11" s="125" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" s="125" customFormat="1">
+      <c r="C12" s="125" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" s="125" customFormat="1">
+      <c r="C13" s="125" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" s="125" customFormat="1">
+      <c r="C14" s="125" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" s="125" customFormat="1">
+      <c r="B15" s="125" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="125" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" s="125" customFormat="1">
+      <c r="C16" s="125" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" s="125" customFormat="1">
+      <c r="C17" s="125" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" s="125" customFormat="1">
+      <c r="C18" s="125" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" s="125" customFormat="1">
+      <c r="C19" s="125" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" s="125" customFormat="1">
+      <c r="C20" s="125" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" s="125" customFormat="1">
+      <c r="C21" s="125" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" s="125" customFormat="1">
+      <c r="C22" s="125" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" s="125" customFormat="1">
+      <c r="C23" s="125" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" s="125" customFormat="1">
+      <c r="B24" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="75" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3">
-      <c r="C5" s="75" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="C6" s="75" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="C7" s="75" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="C8" s="75" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="C9" s="75" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="C10" s="75" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="C11" s="75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="C12" s="75" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3">
-      <c r="C13" s="75" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3">
-      <c r="C14" s="75" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3">
-      <c r="B15" s="75" t="s">
+      <c r="C24" s="125" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" s="125" customFormat="1">
+      <c r="C25" s="125" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" s="125" customFormat="1">
+      <c r="C26" s="125" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" s="125" customFormat="1">
+      <c r="C27" s="125" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" s="125" customFormat="1">
+      <c r="C28" s="125" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" s="125" customFormat="1">
+      <c r="B29" s="125" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="75" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3">
-      <c r="C16" s="75" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="C17" s="75" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="C18" s="75" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3">
-      <c r="C19" s="75" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="C20" s="75" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="C21" s="75" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="C22" s="75" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="C23" s="75" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="75" t="s">
+      <c r="C29" s="125" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" s="125" customFormat="1">
+      <c r="C30" s="125" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" s="125" customFormat="1">
+      <c r="C31" s="125" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" s="125" customFormat="1">
+      <c r="C32" s="125" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" s="125" customFormat="1">
+      <c r="C33" s="125" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" s="125" customFormat="1">
+      <c r="C34" s="125" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" s="125" customFormat="1">
+      <c r="C35" s="125" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" s="125" customFormat="1">
+      <c r="C36" s="125" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" s="125" customFormat="1">
+      <c r="C37" s="125" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" s="125" customFormat="1">
+      <c r="C38" s="125" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" s="125" customFormat="1">
+      <c r="C39" s="125" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" s="125" customFormat="1">
+      <c r="C40" s="125" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" s="125" customFormat="1">
+      <c r="C41" s="125" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" s="125" customFormat="1">
+      <c r="C42" s="125" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" s="125" customFormat="1">
+      <c r="B43" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="75" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3">
-      <c r="C25" s="75" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="C26" s="75" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3">
-      <c r="C27" s="75" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="C28" s="75" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3">
-      <c r="B29" s="75" t="s">
+      <c r="C43" s="125" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" s="125" customFormat="1">
+      <c r="C44" s="125" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" s="125" customFormat="1">
+      <c r="C45" s="125" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" s="125" customFormat="1">
+      <c r="C46" s="125" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" s="125" customFormat="1">
+      <c r="C47" s="125" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" s="125" customFormat="1">
+      <c r="C48" s="125" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" s="125" customFormat="1">
+      <c r="C49" s="125" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" s="125" customFormat="1">
+      <c r="C50" s="125" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" s="125" customFormat="1">
+      <c r="B51" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="75" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3">
-      <c r="C30" s="75" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3">
-      <c r="C31" s="75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3">
-      <c r="C32" s="75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3">
-      <c r="C33" s="75" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3">
-      <c r="C34" s="75" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3">
-      <c r="C35" s="75" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3">
-      <c r="C36" s="75" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3">
-      <c r="C37" s="75" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3">
-      <c r="C38" s="75" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3">
-      <c r="C39" s="75" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3">
-      <c r="C40" s="75" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3">
-      <c r="C41" s="75" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3">
-      <c r="C42" s="75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3">
-      <c r="B43" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="75" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3">
-      <c r="C44" s="75" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3">
-      <c r="C45" s="75" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3">
-      <c r="C46" s="75" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3">
-      <c r="C47" s="75" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3">
-      <c r="C48" s="75" t="s">
+      <c r="C51" s="125" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" s="125" customFormat="1">
+      <c r="B52" s="125" t="s">
+        <v>193</v>
+      </c>
+      <c r="C52" s="125" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="2:3">
-      <c r="C49" s="75" t="s">
+    <row r="53" spans="2:3" s="125" customFormat="1">
+      <c r="C53" s="125" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="50" spans="2:3">
-      <c r="C50" s="75" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3">
-      <c r="B51" s="75" t="s">
-        <v>45</v>
-      </c>
-      <c r="C51" s="75" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3">
-      <c r="B52" s="75" t="s">
-        <v>196</v>
-      </c>
-      <c r="C52" s="75" t="s">
+    <row r="54" spans="2:3" s="125" customFormat="1">
+      <c r="C54" s="125" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="2:3">
-      <c r="C53" s="75" t="s">
+    <row r="55" spans="2:3" s="125" customFormat="1">
+      <c r="C55" s="125" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="2:3">
-      <c r="C54" s="75" t="s">
+    <row r="56" spans="2:3" s="125" customFormat="1">
+      <c r="C56" s="125" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="55" spans="2:3">
-      <c r="C55" s="75" t="s">
+    <row r="57" spans="2:3" s="125" customFormat="1">
+      <c r="C57" s="125" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="2:3">
-      <c r="C56" s="75" t="s">
+    <row r="58" spans="2:3" s="125" customFormat="1">
+      <c r="C58" s="125" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="2:3">
-      <c r="C57" s="75" t="s">
+    <row r="59" spans="2:3" s="125" customFormat="1">
+      <c r="C59" s="125" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" s="125" customFormat="1">
+      <c r="B60" s="125" t="s">
+        <v>194</v>
+      </c>
+      <c r="C60" s="125" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" s="125" customFormat="1">
+      <c r="C61" s="125" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="2:3">
-      <c r="C58" s="75" t="s">
+    <row r="62" spans="2:3" s="125" customFormat="1">
+      <c r="C62" s="125" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="59" spans="2:3">
-      <c r="C59" s="75" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3">
-      <c r="B60" s="75" t="s">
-        <v>197</v>
-      </c>
-      <c r="C60" s="75" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3">
-      <c r="C61" s="75" t="s">
+    <row r="63" spans="2:3" s="125" customFormat="1">
+      <c r="C63" s="125" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="2:3">
-      <c r="C62" s="75" t="s">
+    <row r="64" spans="2:3" s="125" customFormat="1">
+      <c r="C64" s="125" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="63" spans="2:3">
-      <c r="C63" s="75" t="s">
+    <row r="65" spans="3:3" s="125" customFormat="1">
+      <c r="C65" s="125" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="64" spans="2:3">
-      <c r="C64" s="75" t="s">
+    <row r="66" spans="3:3" s="125" customFormat="1">
+      <c r="C66" s="125" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="65" spans="3:3">
-      <c r="C65" s="75" t="s">
+    <row r="67" spans="3:3" s="125" customFormat="1">
+      <c r="C67" s="125" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="66" spans="3:3">
-      <c r="C66" s="75" t="s">
+    <row r="68" spans="3:3" s="125" customFormat="1">
+      <c r="C68" s="125" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="3:3">
-      <c r="C67" s="75" t="s">
+    <row r="69" spans="3:3" s="125" customFormat="1">
+      <c r="C69" s="125" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" s="125" customFormat="1">
+      <c r="C70" s="125" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="3:3">
-      <c r="C68" s="75" t="s">
+    <row r="71" spans="3:3" s="125" customFormat="1">
+      <c r="C71" s="125" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="69" spans="3:3">
-      <c r="C69" s="75" t="s">
+    <row r="72" spans="3:3" s="125" customFormat="1">
+      <c r="C72" s="125" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" s="125" customFormat="1">
+      <c r="C73" s="125" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" s="125" customFormat="1">
+      <c r="C74" s="125" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3" s="125" customFormat="1">
+      <c r="C75" s="125" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3" s="125" customFormat="1">
+      <c r="C76" s="125" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" spans="3:3" s="125" customFormat="1">
+      <c r="C77" s="125" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3" s="125" customFormat="1">
+      <c r="C78" s="125" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3" s="125" customFormat="1">
+      <c r="C79" s="125" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="70" spans="3:3">
-      <c r="C70" s="75" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="71" spans="3:3">
-      <c r="C71" s="75" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="72" spans="3:3">
-      <c r="C72" s="75" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="73" spans="3:3">
-      <c r="C73" s="75" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="74" spans="3:3">
-      <c r="C74" s="75" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="75" spans="3:3">
-      <c r="C75" s="75" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="76" spans="3:3">
-      <c r="C76" s="75" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="77" spans="3:3">
-      <c r="C77" s="75" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="78" spans="3:3">
-      <c r="C78" s="75" t="s">
+    <row r="80" spans="3:3" s="125" customFormat="1">
+      <c r="C80" s="125" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" s="125" customFormat="1">
+      <c r="C81" s="125" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="79" spans="3:3">
-      <c r="C79" s="75" t="s">
+    <row r="82" spans="2:3" s="125" customFormat="1">
+      <c r="C82" s="125" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="80" spans="3:3">
-      <c r="C80" s="75" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3">
-      <c r="C81" s="75" t="s">
+    <row r="83" spans="2:3" s="125" customFormat="1">
+      <c r="B83" s="125" t="s">
+        <v>198</v>
+      </c>
+      <c r="C83" s="125" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3">
-      <c r="C82" s="75" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3">
-      <c r="B83" s="75" t="s">
-        <v>201</v>
-      </c>
-      <c r="C83" s="75" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/IG/AI Native-生成AI_IG.xlsx
+++ b/IG/AI Native-生成AI_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C62B856-6F4C-4298-AC72-947CEE83D98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3885BB11-D456-4EE6-BE89-123685B6F428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="206">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -1039,26 +1039,6 @@
   <si>
     <t xml:space="preserve">・AI-01
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>そのまま読んでいただいても良いです。
-・業務知識や社内ルールは最初から知らない
-　→ 必要な情報を与える必要がある。
-・システム全体の整合性維持は苦手
-　→ 大規模開発では人によるレビューが必要。
-・背景や暗黙知を理解していない
-　→ 前提条件を明示する必要がある。
-・自律的に組織の標準を学習し続けるわけではない
-　→ ルールや指示を継続的に与える必要がある。
-・意思決定や責任は負えない
-　→ 最終判断は人が行う。</t>
-    <rPh sb="4" eb="5">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ヨ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1091,29 +1071,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>受講生は動画で一度見たことがある。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>忘れてしまった人はもう一度見るように伝える。</t>
-    <rPh sb="0" eb="1">
-      <t>ワス</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ツタ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>左：概念的なPDCAの話
 右：AgenticAIにおけるPDCAの話</t>
     <rPh sb="0" eb="1">
@@ -1508,29 +1465,6 @@
 AgenticAIとは、「目標を与えると、自ら計画を立て、必要な作業を実行しながら目的達成を目指すAI」のこと
 ※目標達成のためにPDCAを繰り返す。</t>
     <rPh sb="10" eb="12">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>実施対象は以下であることを説明する。
-＜研修ゴール＞
-・ 生成AI（ChatGPT / GitHub Copilot）を活用し、要件定義～設計～実装～テストまでの開発プロセスを一通り実行できる
-・ プロンプトの選択・修正・改善を通じて、成果物の品質を向上させるサイクルを実践できる
-＜獲得可能な経験＞
-・ ChatGPT を用いた 「調査・整理」、「叩き台資料作成」、「モックアプリ開発」、「企画・提案書骨子作成」、「成果物RV」の経験
-・ GitHub Copilot を用いた AIエージェント への作業指示および上述の成果物作成・修正・RVの経験
-・ GitHub Copilot を用いる際の 各種ハーネスエンジニアリング に向けたAI動作環境の改善経験</t>
-    <rPh sb="0" eb="2">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
       <t>セツメイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
@@ -1657,26 +1591,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">以下の仕事は教育も兼任していた。
-■ 議事録作成
-■ 進捗取りまとめ
-生成AIによって作業は効率化されるが、その作業を通じて得られていた若手の学習機会や成長機会も同時に失われる可能性がある。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※受講生にとって攻撃的な内容なので柔らかい表現で説明する。</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>2040年の業種と学歴の需要と供給のミスマッチの図です。
 需要と供給のミスマッチをの詳細を説明する。</t>
     <rPh sb="4" eb="5">
@@ -1759,32 +1673,6 @@
     </rPh>
     <rPh sb="27" eb="29">
       <t>ワリアイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">以下を説明する。
-■ 人手不足：AIが若手の比較対象・代替候補になっている
-■ 生成ＡＩ活用の矛盾：AIを活用するために必要な能力を、AI活用によって身につけにくくなる
-生成AIによって若手の代替が進む一方で、生成AIを正しく活用・評価できる人材を育成する機会も失われつつある。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※受講生にとって攻撃的な内容なので柔らかい表現で説明する。</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>セツメイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1888,41 +1776,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">以下の概要を説明する。
-▮モード
-・Ask
-・Agent
-・Plan
-▮コマンド
-個々の内容は説明せずに、概要を説明する。
-</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ガイヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ココ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>ガイヨウ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>プロンプト集を説明する。
 ・構造化
 ・マークダウン</t>
@@ -1934,23 +1787,6 @@
     </rPh>
     <rPh sb="14" eb="17">
       <t>コウゾウカ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>全体を説明する。
-Spec-Driven Developmentとは、「まず仕様（Specification）を明確に定義し、その仕様を中心に設計・実装・テストを進める開発手法」のこと
-「仕様駆動開発」という言葉だけでは意味が曖昧なので、導入時には何を仕様と呼び、どのように開発を進めるのかを明確にする必要がある。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>全体を説明する。
-ハーネスエンジニアリングとは、「AIエージェントの性能を最大限に引き出すために、ツール連携、知識ベース、プロンプト、ワークフローなどの実行環境を設計・改善する考え方・手法」のこと</t>
-    <rPh sb="0" eb="2">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>セツメイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2045,11 +1881,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">・AI-01
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>全体を説明する。
 非決定性とは「品質や内容が毎回完全には保証されないこと」であり、AI時代は「間違えないこと」ではなく「間違いを早く発見できる仕組み」を重視する必要がある。
 成果物を100%信じない
@@ -2412,6 +2243,178 @@
   </si>
   <si>
     <t>AI Native-生成AI</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※受講生は動画で一度見たことがある。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-01
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>実施対象は以下であることを説明する。
+■研修ゴール
+・ 生成AI（ChatGPT / GitHub Copilot）を活用し、要件定義～設計～実装～テストまでの開発プロセスを一通り実行できる
+・ プロンプトの選択・修正・改善を通じて、成果物の品質を向上させるサイクルを実践できる
+■獲得可能な経験
+・ ChatGPTを用いた 「調査・整理」、「叩き台資料作成」、「モックアプリ開発」、「企画・提案書骨子作成」、「成果物RV」の経験
+・ GitHub Copilotを用いたAIエージェントへの作業指示および上述の成果物作成・修正・RVの経験
+・ GitHub Copilotを用いる際の各種ハーネスエンジニアリングに向けたAI動作環境の改善経験</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下の仕事は教育も兼任していた。
+・議事録作成
+・進捗取りまとめ
+生成AIによって作業は効率化されるが、その作業を通じて得られていた若手の学習機会や成長機会も同時に失われる可能性がある。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※受講生にとって攻撃的な内容なので柔らかい表現で説明する。</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下を説明する。
+・人手不足：AIが若手の比較対象・代替候補になっている
+・生成AI活用の矛盾：AIを活用するために必要な能力を、AI活用によって身につけにくくなる
+生成AIによって若手の代替が進む一方で、生成AIを正しく活用・評価できる人材を育成する機会も失われつつある。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※受講生にとって攻撃的な内容なので柔らかい表現で説明する。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>全体を説明する。
+Spec-Driven Developmentとは、「まず仕様（Specification）を明確に定義し、その仕様を中心に設計・実装・テストを進める開発手法」のこと。
+「仕様駆動開発」という言葉だけでは意味が曖昧なので、導入時には何を仕様と呼び、どのように開発を進めるのかを明確にする必要がある。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>全体を説明する。
+ハーネスエンジニアリングとは、「AIエージェントの性能を最大限に引き出すために、ツール連携、知識ベース、プロンプト、ワークフローなどの実行環境を設計・改善する考え方・手法」のこと。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下の概要を説明する。
+▮モード
+・Ask
+・Agent
+・Plan
+▮コマンド
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※個々の内容は説明せずに、概要を説明する。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ココ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・業務知識や社内ルールは最初から知らない　→ 必要な情報を与える必要がある。
+・システム全体の整合性維持は苦手　→ 大規模開発では人によるレビューが必要。
+・背景や暗黙知を理解していない　→ 前提条件を明示する必要がある。
+・自律的に組織の標準を学習し続けるわけではない　→ ルールや指示を継続的に与える必要がある。
+・意思決定や責任は負えない　→ 最終判断は人が行う。
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>受講生に「忘れてしまった人はもう一度見るように！」と伝える。</t>
+    <rPh sb="0" eb="3">
+      <t>ジュコウセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ワス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツタ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -2840,7 +2843,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3120,6 +3123,9 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3171,6 +3177,36 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -3185,42 +3221,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3594,15 +3594,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="94" t="str">
+      <c r="B2" s="95" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="96"/>
+      <c r="C4" s="97"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3626,18 +3626,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="99" t="s">
+      <c r="B7" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="99"/>
+      <c r="C7" s="100"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="27"/>
@@ -3697,7 +3697,7 @@
         <f>master!B4</f>
         <v>導入編</v>
       </c>
-      <c r="F14" s="93"/>
+      <c r="F14" s="94"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
@@ -3706,7 +3706,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="82"/>
-      <c r="F15" s="93"/>
+      <c r="F15" s="94"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B16" s="44"/>
       <c r="C16" s="83"/>
-      <c r="F16" s="93"/>
+      <c r="F16" s="94"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
@@ -3727,14 +3727,14 @@
         <f>master!B15</f>
         <v>復習編</v>
       </c>
-      <c r="F17" s="93"/>
+      <c r="F17" s="94"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="41"/>
       <c r="B18" s="44"/>
       <c r="C18" s="83"/>
-      <c r="F18" s="93"/>
+      <c r="F18" s="94"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3746,7 +3746,7 @@
         <f>master!B24</f>
         <v>AI-Native研修の目的</v>
       </c>
-      <c r="F19" s="93"/>
+      <c r="F19" s="94"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
@@ -3760,14 +3760,14 @@
         <f>master!B29</f>
         <v>キャリア編</v>
       </c>
-      <c r="F20" s="93"/>
+      <c r="F20" s="94"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="60"/>
       <c r="B21" s="62"/>
       <c r="C21" s="83"/>
-      <c r="F21" s="93"/>
+      <c r="F21" s="94"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3820,7 +3820,7 @@
         <v>0.5625</v>
       </c>
       <c r="C26" s="83"/>
-      <c r="F26" s="93"/>
+      <c r="F26" s="94"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -3833,7 +3833,7 @@
         <f>master!B43</f>
         <v>NTTデータの強み編</v>
       </c>
-      <c r="F27" s="93"/>
+      <c r="F27" s="94"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B28" s="44"/>
       <c r="C28" s="83"/>
-      <c r="F28" s="93"/>
+      <c r="F28" s="94"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D29" s="59"/>
       <c r="E29" s="56"/>
-      <c r="F29" s="93"/>
+      <c r="F29" s="94"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -3866,7 +3866,7 @@
       <c r="C30" s="63"/>
       <c r="D30" s="59"/>
       <c r="E30" s="56"/>
-      <c r="F30" s="93"/>
+      <c r="F30" s="94"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
@@ -3875,7 +3875,7 @@
       <c r="C31" s="63"/>
       <c r="D31" s="59"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="93"/>
+      <c r="F31" s="94"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
@@ -3886,7 +3886,7 @@
       <c r="C32" s="63"/>
       <c r="D32" s="59"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="93"/>
+      <c r="F32" s="94"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
@@ -3895,7 +3895,7 @@
       <c r="C33" s="63"/>
       <c r="D33" s="59"/>
       <c r="E33" s="56"/>
-      <c r="F33" s="93"/>
+      <c r="F33" s="94"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="56"/>
-      <c r="F34" s="93"/>
+      <c r="F34" s="94"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
@@ -3918,7 +3918,7 @@
       <c r="C35" s="63"/>
       <c r="D35" s="59"/>
       <c r="E35" s="56"/>
-      <c r="F35" s="93"/>
+      <c r="F35" s="94"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3929,7 +3929,7 @@
       <c r="C36" s="63"/>
       <c r="D36" s="59"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="93"/>
+      <c r="F36" s="94"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
@@ -3938,7 +3938,7 @@
       <c r="C37" s="63"/>
       <c r="D37" s="59"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="93"/>
+      <c r="F37" s="94"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
@@ -3947,7 +3947,7 @@
       <c r="C38" s="63"/>
       <c r="D38" s="59"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="93"/>
+      <c r="F38" s="94"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
@@ -3956,7 +3956,7 @@
       <c r="C39" s="68"/>
       <c r="D39" s="59"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="93"/>
+      <c r="F39" s="94"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3967,11 +3967,11 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C40" s="63" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D40" s="59"/>
       <c r="E40" s="56"/>
-      <c r="F40" s="93"/>
+      <c r="F40" s="94"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -3980,7 +3980,7 @@
       <c r="C41" s="63"/>
       <c r="D41" s="61"/>
       <c r="E41" s="57"/>
-      <c r="F41" s="93"/>
+      <c r="F41" s="94"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
@@ -3989,7 +3989,7 @@
       <c r="C42" s="64"/>
       <c r="D42" s="59"/>
       <c r="E42" s="57"/>
-      <c r="F42" s="93"/>
+      <c r="F42" s="94"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
@@ -3998,7 +3998,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="C43" s="89" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D43" s="60"/>
       <c r="E43" s="58"/>
@@ -4076,10 +4076,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="105"/>
+      <c r="C4" s="106"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4090,16 +4090,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="106"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4112,10 +4112,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="36"/>
-      <c r="D7" s="107" t="s">
+      <c r="D7" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="107"/>
+      <c r="E7" s="108"/>
       <c r="F7" s="36" t="s">
         <v>10</v>
       </c>
@@ -4155,46 +4155,46 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101" t="s">
+      <c r="B11" s="102"/>
+      <c r="C11" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="101" t="s">
+      <c r="D11" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101" t="s">
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="108" t="s">
+      <c r="H11" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="100" t="s">
+      <c r="I11" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100" t="s">
+      <c r="J11" s="101"/>
+      <c r="K11" s="101" t="s">
         <v>32</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="109"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="110"/>
       <c r="I12" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J12" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="101"/>
+      <c r="K12" s="102"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
@@ -4203,13 +4203,13 @@
       <c r="C13" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="102" t="s">
-        <v>191</v>
-      </c>
-      <c r="E13" s="103"/>
-      <c r="F13" s="104"/>
+      <c r="D13" s="103" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="104"/>
+      <c r="F13" s="105"/>
       <c r="G13" s="65" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="53" t="s">
@@ -4306,12 +4306,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4322,30 +4322,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
       <c r="L5" s="32"/>
       <c r="M5" s="33"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="124"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
       <c r="L6" s="32"/>
       <c r="M6" s="33"/>
     </row>
@@ -4406,28 +4406,28 @@
     </row>
     <row r="11" spans="1:14" ht="24" customHeight="1">
       <c r="A11" s="10"/>
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="101" t="s">
+      <c r="D11" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101" t="s">
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="100" t="s">
+      <c r="H11" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="122" t="s">
+      <c r="I11" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="123"/>
-      <c r="K11" s="100" t="s">
+      <c r="J11" s="112"/>
+      <c r="K11" s="101" t="s">
         <v>34</v>
       </c>
       <c r="L11" s="6"/>
@@ -4436,27 +4436,27 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="10"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="100"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="101"/>
       <c r="I12" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J12" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="101"/>
+      <c r="K12" s="102"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" ht="75.599999999999994">
       <c r="A13" s="10"/>
-      <c r="B13" s="110" t="str">
+      <c r="B13" s="121" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
@@ -4464,11 +4464,11 @@
         <f>master!C3</f>
         <v>ー</v>
       </c>
-      <c r="D13" s="118" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13" s="119"/>
-      <c r="F13" s="120"/>
+      <c r="D13" s="114" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="115"/>
+      <c r="F13" s="116"/>
       <c r="G13" s="54" t="s">
         <v>121</v>
       </c>
@@ -4486,15 +4486,15 @@
     </row>
     <row r="14" spans="1:14" ht="88.2">
       <c r="A14" s="10"/>
-      <c r="B14" s="111"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="72"/>
-      <c r="D14" s="115" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="116"/>
-      <c r="F14" s="117"/>
+      <c r="D14" s="117" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" s="118"/>
+      <c r="F14" s="119"/>
       <c r="G14" s="72" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="H14" s="73"/>
       <c r="I14" s="74" t="s">
@@ -4510,7 +4510,7 @@
     </row>
     <row r="15" spans="1:14" ht="138.6">
       <c r="A15" s="10"/>
-      <c r="B15" s="121" t="str">
+      <c r="B15" s="120" t="str">
         <f>master!B4</f>
         <v>導入編</v>
       </c>
@@ -4518,11 +4518,11 @@
         <f>master!C4</f>
         <v>あなたはもう生成ＡＩを使っていますか？</v>
       </c>
-      <c r="D15" s="118" t="s">
-        <v>156</v>
-      </c>
-      <c r="E15" s="119"/>
-      <c r="F15" s="120"/>
+      <c r="D15" s="114" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="115"/>
+      <c r="F15" s="116"/>
       <c r="G15" s="54" t="s">
         <v>122</v>
       </c>
@@ -4540,16 +4540,16 @@
     </row>
     <row r="16" spans="1:14" ht="75.599999999999994">
       <c r="A16" s="11"/>
-      <c r="B16" s="121"/>
+      <c r="B16" s="120"/>
       <c r="C16" s="54" t="str">
         <f>master!C5</f>
         <v>FYI：システム開発SaaS　「GEAR.indigo」</v>
       </c>
-      <c r="D16" s="118" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="119"/>
-      <c r="F16" s="120"/>
+      <c r="D16" s="114" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="115"/>
+      <c r="F16" s="116"/>
       <c r="G16" s="54" t="s">
         <v>126</v>
       </c>
@@ -4567,16 +4567,16 @@
     </row>
     <row r="17" spans="1:14" ht="37.799999999999997">
       <c r="A17" s="11"/>
-      <c r="B17" s="121"/>
+      <c r="B17" s="120"/>
       <c r="C17" s="54" t="str">
         <f>master!C6</f>
         <v>FYI：GEAR.indigo　「業務要件一覧」</v>
       </c>
-      <c r="D17" s="118" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="119"/>
-      <c r="F17" s="120"/>
+      <c r="D17" s="114" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="115"/>
+      <c r="F17" s="116"/>
       <c r="G17" s="54" t="s">
         <v>124</v>
       </c>
@@ -4594,16 +4594,16 @@
     </row>
     <row r="18" spans="1:14" ht="37.799999999999997">
       <c r="A18" s="11"/>
-      <c r="B18" s="121"/>
+      <c r="B18" s="120"/>
       <c r="C18" s="54" t="str">
         <f>master!C7</f>
         <v>FYI：GEAR.indigo　「システム化業務フロー」</v>
       </c>
-      <c r="D18" s="118" t="s">
-        <v>159</v>
-      </c>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
+      <c r="D18" s="114" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" s="115"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="54" t="s">
         <v>124</v>
       </c>
@@ -4621,16 +4621,16 @@
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="121"/>
+      <c r="B19" s="120"/>
       <c r="C19" s="54" t="str">
         <f>master!C8</f>
         <v>FYI：GEAR.indigo　「テーブル定義書」</v>
       </c>
-      <c r="D19" s="118" t="s">
-        <v>160</v>
-      </c>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
+      <c r="D19" s="114" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="115"/>
+      <c r="F19" s="116"/>
       <c r="G19" s="54" t="s">
         <v>124</v>
       </c>
@@ -4648,16 +4648,16 @@
     </row>
     <row r="20" spans="1:14" ht="37.799999999999997">
       <c r="A20" s="11"/>
-      <c r="B20" s="121"/>
+      <c r="B20" s="120"/>
       <c r="C20" s="54" t="str">
         <f>master!C9</f>
         <v>FYI：GEAR.indigo　「画面定義書」</v>
       </c>
-      <c r="D20" s="118" t="s">
-        <v>161</v>
-      </c>
-      <c r="E20" s="119"/>
-      <c r="F20" s="120"/>
+      <c r="D20" s="114" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="115"/>
+      <c r="F20" s="116"/>
       <c r="G20" s="54" t="s">
         <v>124</v>
       </c>
@@ -4675,16 +4675,16 @@
     </row>
     <row r="21" spans="1:14" ht="50.4">
       <c r="A21" s="11"/>
-      <c r="B21" s="121"/>
+      <c r="B21" s="120"/>
       <c r="C21" s="54" t="str">
         <f>master!C10</f>
         <v>GEAR.indigo が （いずれ）見せてくれるもの</v>
       </c>
-      <c r="D21" s="118" t="s">
+      <c r="D21" s="114" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="119"/>
-      <c r="F21" s="120"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="116"/>
       <c r="G21" s="54" t="s">
         <v>125</v>
       </c>
@@ -4700,20 +4700,20 @@
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="25.2">
+    <row r="22" spans="1:14" ht="37.799999999999997">
       <c r="A22" s="11"/>
-      <c r="B22" s="121"/>
+      <c r="B22" s="120"/>
       <c r="C22" s="54" t="str">
         <f>master!C11</f>
         <v>あなたはどちらになりたいですか？</v>
       </c>
-      <c r="D22" s="118" t="s">
+      <c r="D22" s="114" t="s">
         <v>131</v>
       </c>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="54" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="52" t="s">
@@ -4729,16 +4729,16 @@
     </row>
     <row r="23" spans="1:14" ht="37.799999999999997">
       <c r="A23" s="11"/>
-      <c r="B23" s="121"/>
+      <c r="B23" s="120"/>
       <c r="C23" s="54" t="str">
         <f>master!C12</f>
         <v>いま、生成AIができること　（システム開発関連）</v>
       </c>
-      <c r="D23" s="118" t="s">
+      <c r="D23" s="114" t="s">
         <v>133</v>
       </c>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="116"/>
       <c r="G23" s="54" t="s">
         <v>124</v>
       </c>
@@ -4754,20 +4754,20 @@
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="214.2">
+    <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="121"/>
+      <c r="B24" s="120"/>
       <c r="C24" s="54" t="str">
         <f>master!C13</f>
         <v>いま、生成ＡＩができないこと</v>
       </c>
-      <c r="D24" s="118" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
+      <c r="D24" s="114" t="s">
+        <v>204</v>
+      </c>
+      <c r="E24" s="115"/>
+      <c r="F24" s="116"/>
       <c r="G24" s="54" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="52" t="s">
@@ -4783,18 +4783,18 @@
     </row>
     <row r="25" spans="1:14" ht="226.8">
       <c r="A25" s="11"/>
-      <c r="B25" s="121"/>
+      <c r="B25" s="120"/>
       <c r="C25" s="54" t="str">
         <f>master!C14</f>
         <v>生成ＡＩを使う心得８条</v>
       </c>
-      <c r="D25" s="118" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120"/>
+      <c r="D25" s="114" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="115"/>
+      <c r="F25" s="116"/>
       <c r="G25" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="52" t="s">
@@ -4808,9 +4808,9 @@
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1">
+    <row r="26" spans="1:14" ht="25.2">
       <c r="A26" s="11"/>
-      <c r="B26" s="121" t="str">
+      <c r="B26" s="120" t="str">
         <f>master!B15</f>
         <v>復習編</v>
       </c>
@@ -4818,13 +4818,13 @@
         <f>master!C15</f>
         <v>NTTDATAが目指す方向性</v>
       </c>
-      <c r="D26" s="118" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
+      <c r="D26" s="114" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="115"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="54" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="52" t="s">
@@ -4834,26 +4834,26 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K26" s="46" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1">
+    <row r="27" spans="1:14" ht="25.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="121"/>
+      <c r="B27" s="120"/>
       <c r="C27" s="54" t="str">
         <f>master!C16</f>
         <v>NTTデータ新入社員向け生成AI基礎講座</v>
       </c>
-      <c r="D27" s="118" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120"/>
+      <c r="D27" s="114" t="s">
+        <v>205</v>
+      </c>
+      <c r="E27" s="115"/>
+      <c r="F27" s="116"/>
       <c r="G27" s="54" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="52" t="s">
@@ -4862,25 +4862,27 @@
       <c r="J27" s="50">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K27" s="46"/>
+      <c r="K27" s="46" t="s">
+        <v>196</v>
+      </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1">
+    <row r="28" spans="1:14" ht="25.2">
       <c r="A28" s="11"/>
-      <c r="B28" s="121"/>
+      <c r="B28" s="120"/>
       <c r="C28" s="54" t="str">
         <f>master!C17</f>
         <v>プロンプト設計の基本</v>
       </c>
-      <c r="D28" s="118" t="s">
-        <v>152</v>
-      </c>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
+      <c r="D28" s="114" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" s="115"/>
+      <c r="F28" s="116"/>
       <c r="G28" s="54" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="52" t="s">
@@ -4896,16 +4898,16 @@
     </row>
     <row r="29" spans="1:14" ht="75.599999999999994">
       <c r="A29" s="11"/>
-      <c r="B29" s="121"/>
+      <c r="B29" s="120"/>
       <c r="C29" s="54" t="str">
         <f>master!C18</f>
         <v>プロンプト設計の基本を踏まえた構造型プロンプト</v>
       </c>
-      <c r="D29" s="118" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
+      <c r="D29" s="114" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="115"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="54" t="s">
         <v>126</v>
       </c>
@@ -4923,14 +4925,14 @@
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="11"/>
-      <c r="B30" s="121"/>
+      <c r="B30" s="120"/>
       <c r="C30" s="54" t="str">
         <f>master!C19</f>
         <v>本セクションで学ぶこと</v>
       </c>
-      <c r="D30" s="118"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="54" t="s">
         <v>120</v>
       </c>
@@ -4948,16 +4950,16 @@
     </row>
     <row r="31" spans="1:14" ht="50.4">
       <c r="A31" s="11"/>
-      <c r="B31" s="121"/>
+      <c r="B31" s="120"/>
       <c r="C31" s="54" t="str">
         <f>master!C20</f>
         <v>エージェントAIとは何か？</v>
       </c>
-      <c r="D31" s="118" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120"/>
+      <c r="D31" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" s="115"/>
+      <c r="F31" s="116"/>
       <c r="G31" s="54" t="s">
         <v>125</v>
       </c>
@@ -4975,16 +4977,16 @@
     </row>
     <row r="32" spans="1:14" ht="25.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="121"/>
+      <c r="B32" s="120"/>
       <c r="C32" s="54" t="str">
         <f>master!C21</f>
         <v>エージェントの処理</v>
       </c>
-      <c r="D32" s="118" t="s">
-        <v>154</v>
-      </c>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120"/>
+      <c r="D32" s="114" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="115"/>
+      <c r="F32" s="116"/>
       <c r="G32" s="54" t="s">
         <v>132</v>
       </c>
@@ -5002,16 +5004,16 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="121"/>
+      <c r="B33" s="120"/>
       <c r="C33" s="54" t="str">
         <f>master!C22</f>
         <v>AIエージェントのアーキテクチャ</v>
       </c>
-      <c r="D33" s="118" t="s">
-        <v>140</v>
-      </c>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
+      <c r="D33" s="114" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="115"/>
+      <c r="F33" s="116"/>
       <c r="G33" s="54" t="s">
         <v>124</v>
       </c>
@@ -5029,16 +5031,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="121"/>
+      <c r="B34" s="120"/>
       <c r="C34" s="54" t="str">
         <f>master!C23</f>
         <v>AIの強みを生かすポイント</v>
       </c>
-      <c r="D34" s="118" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="119"/>
-      <c r="F34" s="120"/>
+      <c r="D34" s="114" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="115"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="54" t="s">
         <v>124</v>
       </c>
@@ -5054,9 +5056,9 @@
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" ht="15" customHeight="1">
+    <row r="35" spans="1:14">
       <c r="A35" s="11"/>
-      <c r="B35" s="121" t="str">
+      <c r="B35" s="120" t="str">
         <f>master!B24</f>
         <v>AI-Native研修の目的</v>
       </c>
@@ -5064,15 +5066,15 @@
         <f>master!C24</f>
         <v>1.研修概要</v>
       </c>
-      <c r="D35" s="118"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="115"/>
+      <c r="F35" s="116"/>
       <c r="G35" s="54" t="s">
         <v>120</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="52" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J35" s="50">
         <v>0</v>
@@ -5082,20 +5084,20 @@
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="15" customHeight="1">
+    <row r="36" spans="1:14" ht="25.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="121"/>
+      <c r="B36" s="120"/>
       <c r="C36" s="54" t="str">
         <f>master!C25</f>
         <v>2-1　背景目的</v>
       </c>
-      <c r="D36" s="118" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" s="119"/>
-      <c r="F36" s="120"/>
+      <c r="D36" s="114" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="115"/>
+      <c r="F36" s="116"/>
       <c r="G36" s="54" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="52" t="s">
@@ -5109,20 +5111,20 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="113.4">
+    <row r="37" spans="1:14" ht="151.19999999999999">
       <c r="A37" s="11"/>
-      <c r="B37" s="121"/>
+      <c r="B37" s="120"/>
       <c r="C37" s="54" t="str">
         <f>master!C26</f>
         <v>2-3　研修のゴールと獲得可能な経験</v>
       </c>
-      <c r="D37" s="118" t="s">
-        <v>163</v>
-      </c>
-      <c r="E37" s="119"/>
-      <c r="F37" s="120"/>
+      <c r="D37" s="114" t="s">
+        <v>198</v>
+      </c>
+      <c r="E37" s="115"/>
+      <c r="F37" s="116"/>
       <c r="G37" s="54" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="52" t="s">
@@ -5136,20 +5138,20 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:14" ht="25.2">
+    <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="121"/>
+      <c r="B38" s="120"/>
       <c r="C38" s="54" t="str">
         <f>master!C27</f>
         <v>AIエージェントを用いたシステム開発タスクの実行の大まかな流れ</v>
       </c>
-      <c r="D38" s="118" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" s="119"/>
-      <c r="F38" s="120"/>
+      <c r="D38" s="114" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="54" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="52" t="s">
@@ -5163,20 +5165,20 @@
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="25.2">
+    <row r="39" spans="1:14" ht="37.799999999999997">
       <c r="A39" s="11"/>
-      <c r="B39" s="121"/>
+      <c r="B39" s="120"/>
       <c r="C39" s="54" t="str">
         <f>master!C28</f>
         <v>学ぶ範囲</v>
       </c>
-      <c r="D39" s="118" t="s">
-        <v>164</v>
-      </c>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
+      <c r="D39" s="114" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="115"/>
+      <c r="F39" s="116"/>
       <c r="G39" s="54" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="52" t="s">
@@ -5192,7 +5194,7 @@
     </row>
     <row r="40" spans="1:14" ht="50.4">
       <c r="A40" s="11"/>
-      <c r="B40" s="121" t="str">
+      <c r="B40" s="120" t="str">
         <f>master!B29</f>
         <v>キャリア編</v>
       </c>
@@ -5200,11 +5202,11 @@
         <f>master!C29</f>
         <v>おまけ：新人の仕事はどうなるか？ これまで</v>
       </c>
-      <c r="D40" s="118" t="s">
-        <v>166</v>
-      </c>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
+      <c r="D40" s="114" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" s="115"/>
+      <c r="F40" s="116"/>
       <c r="G40" s="54" t="s">
         <v>125</v>
       </c>
@@ -5216,7 +5218,7 @@
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="K40" s="46" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
@@ -5224,16 +5226,16 @@
     </row>
     <row r="41" spans="1:14" ht="63">
       <c r="A41" s="11"/>
-      <c r="B41" s="121"/>
+      <c r="B41" s="120"/>
       <c r="C41" s="54" t="str">
         <f>master!C30</f>
         <v>おまけ：生成AI before/after</v>
       </c>
-      <c r="D41" s="118" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" s="119"/>
-      <c r="F41" s="120"/>
+      <c r="D41" s="114" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" s="115"/>
+      <c r="F41" s="116"/>
       <c r="G41" s="54" t="s">
         <v>123</v>
       </c>
@@ -5245,7 +5247,7 @@
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="K41" s="46" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
@@ -5253,16 +5255,16 @@
     </row>
     <row r="42" spans="1:14" ht="50.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="121"/>
+      <c r="B42" s="120"/>
       <c r="C42" s="54" t="str">
         <f>master!C31</f>
         <v>おまけ：新人の仕事はどうなるか？　これから</v>
       </c>
-      <c r="D42" s="118" t="s">
-        <v>165</v>
-      </c>
-      <c r="E42" s="119"/>
-      <c r="F42" s="120"/>
+      <c r="D42" s="114" t="s">
+        <v>161</v>
+      </c>
+      <c r="E42" s="115"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="54" t="s">
         <v>125</v>
       </c>
@@ -5274,7 +5276,7 @@
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -5282,18 +5284,18 @@
     </row>
     <row r="43" spans="1:14" ht="100.8">
       <c r="A43" s="11"/>
-      <c r="B43" s="121"/>
+      <c r="B43" s="120"/>
       <c r="C43" s="54" t="str">
         <f>master!C32</f>
         <v>代表的な若手の仕事</v>
       </c>
-      <c r="D43" s="118" t="s">
-        <v>168</v>
-      </c>
-      <c r="E43" s="119"/>
-      <c r="F43" s="120"/>
+      <c r="D43" s="114" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="115"/>
+      <c r="F43" s="116"/>
       <c r="G43" s="54" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="52" t="s">
@@ -5303,7 +5305,7 @@
         <v>2.0833333333333333E-3</v>
       </c>
       <c r="K43" s="46" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -5311,16 +5313,16 @@
     </row>
     <row r="44" spans="1:14" ht="88.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="121"/>
+      <c r="B44" s="120"/>
       <c r="C44" s="54" t="str">
         <f>master!C33</f>
         <v>そもそも</v>
       </c>
-      <c r="D44" s="118" t="s">
-        <v>172</v>
-      </c>
-      <c r="E44" s="119"/>
-      <c r="F44" s="120"/>
+      <c r="D44" s="114" t="s">
+        <v>200</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="116"/>
       <c r="G44" s="54" t="s">
         <v>130</v>
       </c>
@@ -5332,7 +5334,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K44" s="46" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
@@ -5340,16 +5342,16 @@
     </row>
     <row r="45" spans="1:14" ht="37.799999999999997">
       <c r="A45" s="11"/>
-      <c r="B45" s="121"/>
+      <c r="B45" s="120"/>
       <c r="C45" s="54" t="str">
         <f>master!C34</f>
         <v>2040年の就業構造推計（改定版）の概要</v>
       </c>
-      <c r="D45" s="118" t="s">
-        <v>169</v>
-      </c>
-      <c r="E45" s="119"/>
-      <c r="F45" s="120"/>
+      <c r="D45" s="114" t="s">
+        <v>164</v>
+      </c>
+      <c r="E45" s="115"/>
+      <c r="F45" s="116"/>
       <c r="G45" s="54" t="s">
         <v>124</v>
       </c>
@@ -5361,7 +5363,7 @@
         <v>2.0833333333333333E-3</v>
       </c>
       <c r="K45" s="46" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
@@ -5369,16 +5371,16 @@
     </row>
     <row r="46" spans="1:14" ht="50.4">
       <c r="A46" s="11"/>
-      <c r="B46" s="121"/>
+      <c r="B46" s="120"/>
       <c r="C46" s="54" t="str">
         <f>master!C35</f>
         <v>全国版就業構造推計（改定版）・職業間ミスマッチ</v>
       </c>
-      <c r="D46" s="118" t="s">
-        <v>170</v>
-      </c>
-      <c r="E46" s="119"/>
-      <c r="F46" s="120"/>
+      <c r="D46" s="114" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="115"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="54" t="s">
         <v>125</v>
       </c>
@@ -5390,7 +5392,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K46" s="46" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -5398,16 +5400,16 @@
     </row>
     <row r="47" spans="1:14" ht="50.4">
       <c r="A47" s="11"/>
-      <c r="B47" s="121"/>
+      <c r="B47" s="120"/>
       <c r="C47" s="54" t="str">
         <f>master!C36</f>
         <v>（参考）将来の産業構造は・・・</v>
       </c>
-      <c r="D47" s="118" t="s">
-        <v>171</v>
-      </c>
-      <c r="E47" s="119"/>
-      <c r="F47" s="120"/>
+      <c r="D47" s="114" t="s">
+        <v>166</v>
+      </c>
+      <c r="E47" s="115"/>
+      <c r="F47" s="116"/>
       <c r="G47" s="54" t="s">
         <v>125</v>
       </c>
@@ -5419,26 +5421,26 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K47" s="46" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="75.599999999999994">
+    <row r="48" spans="1:14" ht="63">
       <c r="A48" s="11"/>
-      <c r="B48" s="121"/>
+      <c r="B48" s="120"/>
       <c r="C48" s="54" t="str">
         <f>master!C37</f>
         <v>ヒント１：生成ＡＩと原理原則</v>
       </c>
-      <c r="D48" s="118" t="s">
-        <v>143</v>
-      </c>
-      <c r="E48" s="119"/>
-      <c r="F48" s="120"/>
+      <c r="D48" s="114" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" s="115"/>
+      <c r="F48" s="116"/>
       <c r="G48" s="54" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="52" t="s">
@@ -5454,16 +5456,16 @@
     </row>
     <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="121"/>
+      <c r="B49" s="120"/>
       <c r="C49" s="54" t="str">
         <f>master!C38</f>
         <v>ヒント2：プロンプトによる生成AIの挙動の違い</v>
       </c>
-      <c r="D49" s="118" t="s">
-        <v>202</v>
-      </c>
-      <c r="E49" s="119"/>
-      <c r="F49" s="120"/>
+      <c r="D49" s="114" t="s">
+        <v>192</v>
+      </c>
+      <c r="E49" s="115"/>
+      <c r="F49" s="116"/>
       <c r="G49" s="54" t="s">
         <v>125</v>
       </c>
@@ -5481,16 +5483,16 @@
     </row>
     <row r="50" spans="1:14" ht="189">
       <c r="A50" s="11"/>
-      <c r="B50" s="121"/>
+      <c r="B50" s="120"/>
       <c r="C50" s="54" t="str">
         <f>master!C39</f>
         <v>ヒント３：それでも生成AIを積極的に使うしかない</v>
       </c>
-      <c r="D50" s="118" t="s">
-        <v>203</v>
-      </c>
-      <c r="E50" s="119"/>
-      <c r="F50" s="120"/>
+      <c r="D50" s="114" t="s">
+        <v>193</v>
+      </c>
+      <c r="E50" s="115"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="54" t="s">
         <v>134</v>
       </c>
@@ -5508,20 +5510,20 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="11"/>
-      <c r="B51" s="121"/>
+      <c r="B51" s="120"/>
       <c r="C51" s="54" t="str">
         <f>master!C40</f>
         <v>1. 研修概要</v>
       </c>
-      <c r="D51" s="118"/>
-      <c r="E51" s="119"/>
-      <c r="F51" s="120"/>
+      <c r="D51" s="114"/>
+      <c r="E51" s="115"/>
+      <c r="F51" s="116"/>
       <c r="G51" s="54" t="s">
         <v>120</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="52" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J51" s="50">
         <v>0</v>
@@ -5533,14 +5535,14 @@
     </row>
     <row r="52" spans="1:14" ht="15" customHeight="1">
       <c r="A52" s="11"/>
-      <c r="B52" s="121"/>
+      <c r="B52" s="120"/>
       <c r="C52" s="54" t="str">
         <f>master!C41</f>
         <v>デジタルブートキャンプの目的</v>
       </c>
-      <c r="D52" s="118"/>
-      <c r="E52" s="119"/>
-      <c r="F52" s="120"/>
+      <c r="D52" s="114"/>
+      <c r="E52" s="115"/>
+      <c r="F52" s="116"/>
       <c r="G52" s="54" t="s">
         <v>120</v>
       </c>
@@ -5558,16 +5560,16 @@
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="121"/>
+      <c r="B53" s="120"/>
       <c r="C53" s="54" t="str">
         <f>master!C42</f>
         <v>まとめ</v>
       </c>
-      <c r="D53" s="118" t="s">
-        <v>173</v>
-      </c>
-      <c r="E53" s="119"/>
-      <c r="F53" s="120"/>
+      <c r="D53" s="114" t="s">
+        <v>167</v>
+      </c>
+      <c r="E53" s="115"/>
+      <c r="F53" s="116"/>
       <c r="G53" s="54" t="s">
         <v>125</v>
       </c>
@@ -5583,9 +5585,9 @@
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:14" ht="15" customHeight="1">
+    <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="121" t="str">
+      <c r="B54" s="120" t="str">
         <f>master!B43</f>
         <v>NTTデータの強み編</v>
       </c>
@@ -5593,13 +5595,13 @@
         <f>master!C43</f>
         <v>2025年の変動</v>
       </c>
-      <c r="D54" s="118" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" s="119"/>
-      <c r="F54" s="120"/>
+      <c r="D54" s="114" t="s">
+        <v>143</v>
+      </c>
+      <c r="E54" s="115"/>
+      <c r="F54" s="116"/>
       <c r="G54" s="54" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="52" t="s">
@@ -5615,16 +5617,16 @@
     </row>
     <row r="55" spans="1:14" ht="50.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="121"/>
+      <c r="B55" s="120"/>
       <c r="C55" s="54" t="str">
         <f>master!C44</f>
         <v>2025年の変動　AIエージェントの台頭</v>
       </c>
-      <c r="D55" s="118" t="s">
-        <v>182</v>
-      </c>
-      <c r="E55" s="119"/>
-      <c r="F55" s="120"/>
+      <c r="D55" s="114" t="s">
+        <v>173</v>
+      </c>
+      <c r="E55" s="115"/>
+      <c r="F55" s="116"/>
       <c r="G55" s="54" t="s">
         <v>125</v>
       </c>
@@ -5642,16 +5644,16 @@
     </row>
     <row r="56" spans="1:14" ht="50.4">
       <c r="A56" s="11"/>
-      <c r="B56" s="121"/>
+      <c r="B56" s="120"/>
       <c r="C56" s="54" t="str">
         <f>master!C45</f>
         <v>2025年の変動　Vibe Coding</v>
       </c>
-      <c r="D56" s="118" t="s">
-        <v>181</v>
-      </c>
-      <c r="E56" s="119"/>
-      <c r="F56" s="120"/>
+      <c r="D56" s="114" t="s">
+        <v>172</v>
+      </c>
+      <c r="E56" s="115"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="54" t="s">
         <v>125</v>
       </c>
@@ -5667,20 +5669,20 @@
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="75.599999999999994">
+    <row r="57" spans="1:14" ht="88.2">
       <c r="A57" s="11"/>
-      <c r="B57" s="121"/>
+      <c r="B57" s="120"/>
       <c r="C57" s="54" t="str">
         <f>master!C46</f>
         <v>2025年の変動　Spec Driven Development</v>
       </c>
-      <c r="D57" s="118" t="s">
-        <v>179</v>
-      </c>
-      <c r="E57" s="119"/>
-      <c r="F57" s="120"/>
+      <c r="D57" s="114" t="s">
+        <v>201</v>
+      </c>
+      <c r="E57" s="115"/>
+      <c r="F57" s="116"/>
       <c r="G57" s="54" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="52" t="s">
@@ -5696,16 +5698,16 @@
     </row>
     <row r="58" spans="1:14" ht="50.4">
       <c r="A58" s="11"/>
-      <c r="B58" s="121"/>
+      <c r="B58" s="120"/>
       <c r="C58" s="54" t="str">
         <f>master!C47</f>
         <v>2025年の変動　ハーネスエンジニアリング</v>
       </c>
-      <c r="D58" s="118" t="s">
-        <v>180</v>
-      </c>
-      <c r="E58" s="119"/>
-      <c r="F58" s="120"/>
+      <c r="D58" s="114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E58" s="115"/>
+      <c r="F58" s="116"/>
       <c r="G58" s="54" t="s">
         <v>125</v>
       </c>
@@ -5723,16 +5725,16 @@
     </row>
     <row r="59" spans="1:14" ht="75.599999999999994">
       <c r="A59" s="11"/>
-      <c r="B59" s="121"/>
+      <c r="B59" s="120"/>
       <c r="C59" s="54" t="str">
         <f>master!C48</f>
         <v>2025年の変動　動向まとめ</v>
       </c>
-      <c r="D59" s="118" t="s">
-        <v>183</v>
-      </c>
-      <c r="E59" s="119"/>
-      <c r="F59" s="120"/>
+      <c r="D59" s="114" t="s">
+        <v>174</v>
+      </c>
+      <c r="E59" s="115"/>
+      <c r="F59" s="116"/>
       <c r="G59" s="54" t="s">
         <v>126</v>
       </c>
@@ -5750,16 +5752,16 @@
     </row>
     <row r="60" spans="1:14" ht="113.4">
       <c r="A60" s="11"/>
-      <c r="B60" s="121"/>
+      <c r="B60" s="120"/>
       <c r="C60" s="54" t="str">
         <f>master!C49</f>
         <v>2026年 ソフトウェア開発における課題とNTTDグループの強み</v>
       </c>
-      <c r="D60" s="118" t="s">
-        <v>186</v>
-      </c>
-      <c r="E60" s="119"/>
-      <c r="F60" s="120"/>
+      <c r="D60" s="114" t="s">
+        <v>176</v>
+      </c>
+      <c r="E60" s="115"/>
+      <c r="F60" s="116"/>
       <c r="G60" s="54" t="s">
         <v>127</v>
       </c>
@@ -5775,20 +5777,20 @@
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:14" ht="25.2">
+    <row r="61" spans="1:14" ht="37.799999999999997">
       <c r="A61" s="11"/>
-      <c r="B61" s="121"/>
+      <c r="B61" s="120"/>
       <c r="C61" s="54" t="str">
         <f>master!C50</f>
         <v>2025年の変動</v>
       </c>
-      <c r="D61" s="118" t="s">
-        <v>187</v>
-      </c>
-      <c r="E61" s="119"/>
-      <c r="F61" s="120"/>
+      <c r="D61" s="114" t="s">
+        <v>177</v>
+      </c>
+      <c r="E61" s="115"/>
+      <c r="F61" s="116"/>
       <c r="G61" s="54" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H61" s="12"/>
       <c r="I61" s="52" t="s">
@@ -5812,15 +5814,15 @@
         <f>master!C51</f>
         <v>ー</v>
       </c>
-      <c r="D62" s="118"/>
-      <c r="E62" s="119"/>
-      <c r="F62" s="120"/>
+      <c r="D62" s="114"/>
+      <c r="E62" s="115"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="54" t="s">
         <v>120</v>
       </c>
       <c r="H62" s="12"/>
       <c r="I62" s="52" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J62" s="50">
         <v>0</v>
@@ -5832,7 +5834,7 @@
     </row>
     <row r="63" spans="1:14" ht="50.4" customHeight="1">
       <c r="A63" s="11"/>
-      <c r="B63" s="112" t="str">
+      <c r="B63" s="123" t="str">
         <f>master!B52</f>
         <v>ハンズオン編:ChatGPT</v>
       </c>
@@ -5840,9 +5842,9 @@
         <f>master!C52</f>
         <v>生成ＡＩハンズオン</v>
       </c>
-      <c r="D63" s="115"/>
-      <c r="E63" s="116"/>
-      <c r="F63" s="117"/>
+      <c r="D63" s="117"/>
+      <c r="E63" s="118"/>
+      <c r="F63" s="119"/>
       <c r="G63" s="72" t="s">
         <v>125</v>
       </c>
@@ -5860,14 +5862,14 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="11"/>
-      <c r="B64" s="113"/>
+      <c r="B64" s="124"/>
       <c r="C64" s="72" t="str">
         <f>master!C53</f>
         <v>ChatGPTの使い方（一般チャット）</v>
       </c>
-      <c r="D64" s="115"/>
-      <c r="E64" s="116"/>
-      <c r="F64" s="117"/>
+      <c r="D64" s="117"/>
+      <c r="E64" s="118"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="72" t="s">
         <v>120</v>
       </c>
@@ -5885,16 +5887,16 @@
     </row>
     <row r="65" spans="1:14" ht="50.4">
       <c r="A65" s="11"/>
-      <c r="B65" s="113"/>
+      <c r="B65" s="124"/>
       <c r="C65" s="72" t="str">
         <f>master!C54</f>
         <v>プロンプトを入れてみる</v>
       </c>
-      <c r="D65" s="115" t="s">
-        <v>178</v>
-      </c>
-      <c r="E65" s="116"/>
-      <c r="F65" s="117"/>
+      <c r="D65" s="117" t="s">
+        <v>171</v>
+      </c>
+      <c r="E65" s="118"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="72" t="s">
         <v>125</v>
       </c>
@@ -5912,16 +5914,16 @@
     </row>
     <row r="66" spans="1:14" ht="63">
       <c r="A66" s="11"/>
-      <c r="B66" s="113"/>
+      <c r="B66" s="124"/>
       <c r="C66" s="72" t="str">
         <f>master!C55</f>
         <v>ハンズオン例</v>
       </c>
-      <c r="D66" s="115" t="s">
-        <v>148</v>
-      </c>
-      <c r="E66" s="116"/>
-      <c r="F66" s="117"/>
+      <c r="D66" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="E66" s="118"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="72" t="s">
         <v>123</v>
       </c>
@@ -5939,16 +5941,16 @@
     </row>
     <row r="67" spans="1:14" ht="126">
       <c r="A67" s="11"/>
-      <c r="B67" s="113"/>
+      <c r="B67" s="124"/>
       <c r="C67" s="72" t="str">
         <f>master!C56</f>
         <v>例１：【レポート作成】　佐々木社長の調査を行う</v>
       </c>
-      <c r="D67" s="115" t="s">
-        <v>174</v>
-      </c>
-      <c r="E67" s="116"/>
-      <c r="F67" s="117"/>
+      <c r="D67" s="117" t="s">
+        <v>168</v>
+      </c>
+      <c r="E67" s="118"/>
+      <c r="F67" s="119"/>
       <c r="G67" s="72" t="s">
         <v>128</v>
       </c>
@@ -5966,16 +5968,16 @@
     </row>
     <row r="68" spans="1:14" ht="126" customHeight="1">
       <c r="A68" s="11"/>
-      <c r="B68" s="113"/>
+      <c r="B68" s="124"/>
       <c r="C68" s="72" t="str">
         <f>master!C57</f>
         <v>例２：顧客提案向けの企画書を作りたい</v>
       </c>
-      <c r="D68" s="115" t="s">
-        <v>174</v>
-      </c>
-      <c r="E68" s="116"/>
-      <c r="F68" s="117"/>
+      <c r="D68" s="117" t="s">
+        <v>168</v>
+      </c>
+      <c r="E68" s="118"/>
+      <c r="F68" s="119"/>
       <c r="G68" s="72" t="s">
         <v>128</v>
       </c>
@@ -5993,16 +5995,16 @@
     </row>
     <row r="69" spans="1:14" ht="126" customHeight="1">
       <c r="A69" s="11"/>
-      <c r="B69" s="113"/>
+      <c r="B69" s="124"/>
       <c r="C69" s="72" t="str">
         <f>master!C58</f>
         <v>例３：１００本ノックを作ってみる</v>
       </c>
-      <c r="D69" s="115" t="s">
-        <v>174</v>
-      </c>
-      <c r="E69" s="116"/>
-      <c r="F69" s="117"/>
+      <c r="D69" s="117" t="s">
+        <v>168</v>
+      </c>
+      <c r="E69" s="118"/>
+      <c r="F69" s="119"/>
       <c r="G69" s="72" t="s">
         <v>128</v>
       </c>
@@ -6020,14 +6022,14 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="11"/>
-      <c r="B70" s="114"/>
+      <c r="B70" s="125"/>
       <c r="C70" s="72" t="str">
         <f>master!C59</f>
         <v>ChatGPT まとめ</v>
       </c>
-      <c r="D70" s="115"/>
-      <c r="E70" s="116"/>
-      <c r="F70" s="117"/>
+      <c r="D70" s="117"/>
+      <c r="E70" s="118"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="72" t="s">
         <v>120</v>
       </c>
@@ -6045,7 +6047,7 @@
     </row>
     <row r="71" spans="1:14" ht="15" customHeight="1">
       <c r="A71" s="11"/>
-      <c r="B71" s="112" t="str">
+      <c r="B71" s="123" t="str">
         <f>master!B60</f>
         <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
       </c>
@@ -6053,9 +6055,9 @@
         <f>master!C60</f>
         <v>生成ＡＩハンズオン</v>
       </c>
-      <c r="D71" s="115"/>
-      <c r="E71" s="116"/>
-      <c r="F71" s="117"/>
+      <c r="D71" s="117"/>
+      <c r="E71" s="118"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="72" t="s">
         <v>120</v>
       </c>
@@ -6073,16 +6075,16 @@
     </row>
     <row r="72" spans="1:14" ht="25.2">
       <c r="A72" s="11"/>
-      <c r="B72" s="113"/>
+      <c r="B72" s="124"/>
       <c r="C72" s="72" t="str">
         <f>master!C61</f>
         <v>Visual Studio Code を開く</v>
       </c>
-      <c r="D72" s="115" t="s">
-        <v>175</v>
-      </c>
-      <c r="E72" s="116"/>
-      <c r="F72" s="117"/>
+      <c r="D72" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="E72" s="118"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="72" t="s">
         <v>132</v>
       </c>
@@ -6100,16 +6102,16 @@
     </row>
     <row r="73" spans="1:14" ht="37.799999999999997">
       <c r="A73" s="11"/>
-      <c r="B73" s="113"/>
+      <c r="B73" s="124"/>
       <c r="C73" s="72" t="str">
         <f>master!C62</f>
         <v>コード補完機能</v>
       </c>
-      <c r="D73" s="115" t="s">
-        <v>176</v>
-      </c>
-      <c r="E73" s="116"/>
-      <c r="F73" s="117"/>
+      <c r="D73" s="117" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" s="118"/>
+      <c r="F73" s="119"/>
       <c r="G73" s="72" t="s">
         <v>124</v>
       </c>
@@ -6127,18 +6129,18 @@
     </row>
     <row r="74" spans="1:14" ht="100.8">
       <c r="A74" s="11"/>
-      <c r="B74" s="113"/>
+      <c r="B74" s="124"/>
       <c r="C74" s="72" t="str">
         <f>master!C63</f>
         <v>チャット機能</v>
       </c>
-      <c r="D74" s="115" t="s">
-        <v>177</v>
-      </c>
-      <c r="E74" s="116"/>
-      <c r="F74" s="117"/>
+      <c r="D74" s="117" t="s">
+        <v>203</v>
+      </c>
+      <c r="E74" s="118"/>
+      <c r="F74" s="119"/>
       <c r="G74" s="72" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H74" s="73"/>
       <c r="I74" s="74" t="s">
@@ -6154,14 +6156,14 @@
     </row>
     <row r="75" spans="1:14" ht="15" customHeight="1">
       <c r="A75" s="11"/>
-      <c r="B75" s="113"/>
+      <c r="B75" s="124"/>
       <c r="C75" s="72" t="str">
         <f>master!C64</f>
         <v>ChatGPT で 簡単なアプリやゲームを作ってみましょう</v>
       </c>
-      <c r="D75" s="115"/>
-      <c r="E75" s="116"/>
-      <c r="F75" s="117"/>
+      <c r="D75" s="117"/>
+      <c r="E75" s="118"/>
+      <c r="F75" s="119"/>
       <c r="G75" s="72" t="s">
         <v>120</v>
       </c>
@@ -6179,16 +6181,16 @@
     </row>
     <row r="76" spans="1:14" ht="25.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="113"/>
+      <c r="B76" s="124"/>
       <c r="C76" s="72" t="str">
         <f>master!C65</f>
         <v>例１　高級志向テトリス</v>
       </c>
-      <c r="D76" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E76" s="116"/>
-      <c r="F76" s="117"/>
+      <c r="D76" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E76" s="118"/>
+      <c r="F76" s="119"/>
       <c r="G76" s="72" t="s">
         <v>132</v>
       </c>
@@ -6206,16 +6208,16 @@
     </row>
     <row r="77" spans="1:14" ht="25.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="113"/>
+      <c r="B77" s="124"/>
       <c r="C77" s="72" t="str">
         <f>master!C66</f>
         <v>例）わくわく！にっぽんダーツの旅</v>
       </c>
-      <c r="D77" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E77" s="116"/>
-      <c r="F77" s="117"/>
+      <c r="D77" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E77" s="118"/>
+      <c r="F77" s="119"/>
       <c r="G77" s="72" t="s">
         <v>132</v>
       </c>
@@ -6233,16 +6235,16 @@
     </row>
     <row r="78" spans="1:14" ht="25.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="113"/>
+      <c r="B78" s="124"/>
       <c r="C78" s="72" t="str">
         <f>master!C67</f>
         <v>例）タスク管理ツール</v>
       </c>
-      <c r="D78" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E78" s="116"/>
-      <c r="F78" s="117"/>
+      <c r="D78" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E78" s="118"/>
+      <c r="F78" s="119"/>
       <c r="G78" s="72" t="s">
         <v>132</v>
       </c>
@@ -6260,13 +6262,13 @@
     </row>
     <row r="79" spans="1:14" ht="126">
       <c r="A79" s="11"/>
-      <c r="B79" s="113"/>
+      <c r="B79" s="124"/>
       <c r="C79" s="72"/>
-      <c r="D79" s="115" t="s">
-        <v>150</v>
-      </c>
-      <c r="E79" s="116"/>
-      <c r="F79" s="117"/>
+      <c r="D79" s="117" t="s">
+        <v>147</v>
+      </c>
+      <c r="E79" s="118"/>
+      <c r="F79" s="119"/>
       <c r="G79" s="72" t="s">
         <v>128</v>
       </c>
@@ -6284,16 +6286,16 @@
     </row>
     <row r="80" spans="1:14" ht="63">
       <c r="A80" s="11"/>
-      <c r="B80" s="113"/>
+      <c r="B80" s="124"/>
       <c r="C80" s="72" t="str">
         <f>master!C68</f>
         <v>ディレクトリ作成とファイル配置</v>
       </c>
-      <c r="D80" s="115" t="s">
-        <v>151</v>
-      </c>
-      <c r="E80" s="116"/>
-      <c r="F80" s="117"/>
+      <c r="D80" s="117" t="s">
+        <v>148</v>
+      </c>
+      <c r="E80" s="118"/>
+      <c r="F80" s="119"/>
       <c r="G80" s="72" t="s">
         <v>123</v>
       </c>
@@ -6311,16 +6313,16 @@
     </row>
     <row r="81" spans="1:14" ht="25.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="113"/>
+      <c r="B81" s="124"/>
       <c r="C81" s="72" t="str">
         <f>master!C69</f>
         <v>チャット機能：Aｓｋ</v>
       </c>
-      <c r="D81" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E81" s="116"/>
-      <c r="F81" s="117"/>
+      <c r="D81" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E81" s="118"/>
+      <c r="F81" s="119"/>
       <c r="G81" s="72" t="s">
         <v>132</v>
       </c>
@@ -6338,16 +6340,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="113"/>
+      <c r="B82" s="124"/>
       <c r="C82" s="72" t="str">
         <f>master!C70</f>
         <v>Askモードについて</v>
       </c>
-      <c r="D82" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="E82" s="116"/>
-      <c r="F82" s="117"/>
+      <c r="D82" s="117" t="s">
+        <v>175</v>
+      </c>
+      <c r="E82" s="118"/>
+      <c r="F82" s="119"/>
       <c r="G82" s="72" t="s">
         <v>125</v>
       </c>
@@ -6365,16 +6367,16 @@
     </row>
     <row r="83" spans="1:14" ht="25.2">
       <c r="A83" s="11"/>
-      <c r="B83" s="113"/>
+      <c r="B83" s="124"/>
       <c r="C83" s="91" t="str">
         <f>master!C71</f>
         <v>実行例</v>
       </c>
-      <c r="D83" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E83" s="116"/>
-      <c r="F83" s="117"/>
+      <c r="D83" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E83" s="118"/>
+      <c r="F83" s="119"/>
       <c r="G83" s="72" t="s">
         <v>132</v>
       </c>
@@ -6392,13 +6394,13 @@
     </row>
     <row r="84" spans="1:14" ht="37.799999999999997">
       <c r="A84" s="11"/>
-      <c r="B84" s="113"/>
+      <c r="B84" s="124"/>
       <c r="C84" s="92"/>
-      <c r="D84" s="115" t="s">
-        <v>204</v>
-      </c>
-      <c r="E84" s="116"/>
-      <c r="F84" s="117"/>
+      <c r="D84" s="117" t="s">
+        <v>194</v>
+      </c>
+      <c r="E84" s="118"/>
+      <c r="F84" s="119"/>
       <c r="G84" s="72" t="s">
         <v>124</v>
       </c>
@@ -6416,16 +6418,16 @@
     </row>
     <row r="85" spans="1:14" ht="25.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="113"/>
+      <c r="B85" s="124"/>
       <c r="C85" s="72" t="str">
         <f>master!C72</f>
         <v>Askモードまとめ</v>
       </c>
-      <c r="D85" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E85" s="116"/>
-      <c r="F85" s="117"/>
+      <c r="D85" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E85" s="118"/>
+      <c r="F85" s="119"/>
       <c r="G85" s="72" t="s">
         <v>132</v>
       </c>
@@ -6443,16 +6445,16 @@
     </row>
     <row r="86" spans="1:14" ht="25.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="113"/>
+      <c r="B86" s="124"/>
       <c r="C86" s="72" t="str">
         <f>master!C73</f>
         <v>チャット機能：Agent</v>
       </c>
-      <c r="D86" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E86" s="116"/>
-      <c r="F86" s="117"/>
+      <c r="D86" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E86" s="118"/>
+      <c r="F86" s="119"/>
       <c r="G86" s="72" t="s">
         <v>132</v>
       </c>
@@ -6470,16 +6472,16 @@
     </row>
     <row r="87" spans="1:14" ht="25.2">
       <c r="A87" s="11"/>
-      <c r="B87" s="113"/>
+      <c r="B87" s="124"/>
       <c r="C87" s="72" t="str">
         <f>master!C74</f>
         <v>Agentモード</v>
       </c>
-      <c r="D87" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E87" s="116"/>
-      <c r="F87" s="117"/>
+      <c r="D87" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E87" s="118"/>
+      <c r="F87" s="119"/>
       <c r="G87" s="72" t="s">
         <v>132</v>
       </c>
@@ -6497,16 +6499,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="113"/>
+      <c r="B88" s="124"/>
       <c r="C88" s="72" t="str">
         <f>master!C75</f>
         <v>実行例</v>
       </c>
-      <c r="D88" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="E88" s="116"/>
-      <c r="F88" s="117"/>
+      <c r="D88" s="117" t="s">
+        <v>175</v>
+      </c>
+      <c r="E88" s="118"/>
+      <c r="F88" s="119"/>
       <c r="G88" s="72" t="s">
         <v>124</v>
       </c>
@@ -6524,16 +6526,16 @@
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="113"/>
+      <c r="B89" s="124"/>
       <c r="C89" s="72" t="str">
         <f>master!C76</f>
         <v>READMEの内容を確認しましょう</v>
       </c>
-      <c r="D89" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="E89" s="116"/>
-      <c r="F89" s="117"/>
+      <c r="D89" s="117" t="s">
+        <v>175</v>
+      </c>
+      <c r="E89" s="118"/>
+      <c r="F89" s="119"/>
       <c r="G89" s="72" t="s">
         <v>124</v>
       </c>
@@ -6551,16 +6553,16 @@
     </row>
     <row r="90" spans="1:14" ht="37.799999999999997">
       <c r="A90" s="11"/>
-      <c r="B90" s="113"/>
+      <c r="B90" s="124"/>
       <c r="C90" s="91" t="str">
         <f>master!C77</f>
         <v>Changeログを作ってみましょう</v>
       </c>
-      <c r="D90" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="E90" s="116"/>
-      <c r="F90" s="117"/>
+      <c r="D90" s="117" t="s">
+        <v>175</v>
+      </c>
+      <c r="E90" s="118"/>
+      <c r="F90" s="119"/>
       <c r="G90" s="72" t="s">
         <v>124</v>
       </c>
@@ -6578,13 +6580,13 @@
     </row>
     <row r="91" spans="1:14" ht="37.799999999999997">
       <c r="A91" s="11"/>
-      <c r="B91" s="113"/>
+      <c r="B91" s="124"/>
       <c r="C91" s="92"/>
-      <c r="D91" s="115" t="s">
-        <v>200</v>
-      </c>
-      <c r="E91" s="116"/>
-      <c r="F91" s="117"/>
+      <c r="D91" s="117" t="s">
+        <v>190</v>
+      </c>
+      <c r="E91" s="118"/>
+      <c r="F91" s="119"/>
       <c r="G91" s="72" t="s">
         <v>124</v>
       </c>
@@ -6602,16 +6604,16 @@
     </row>
     <row r="92" spans="1:14" ht="25.2">
       <c r="A92" s="11"/>
-      <c r="B92" s="113"/>
+      <c r="B92" s="124"/>
       <c r="C92" s="72" t="str">
         <f>master!C78</f>
         <v>チャット機能：Plan</v>
       </c>
-      <c r="D92" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E92" s="116"/>
-      <c r="F92" s="117"/>
+      <c r="D92" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E92" s="118"/>
+      <c r="F92" s="119"/>
       <c r="G92" s="72" t="s">
         <v>132</v>
       </c>
@@ -6629,16 +6631,16 @@
     </row>
     <row r="93" spans="1:14" ht="37.799999999999997">
       <c r="A93" s="11"/>
-      <c r="B93" s="113"/>
+      <c r="B93" s="124"/>
       <c r="C93" s="72" t="str">
         <f>master!C79</f>
         <v>Planモードで機能追加してみましょう</v>
       </c>
-      <c r="D93" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="E93" s="116"/>
-      <c r="F93" s="117"/>
+      <c r="D93" s="117" t="s">
+        <v>175</v>
+      </c>
+      <c r="E93" s="118"/>
+      <c r="F93" s="119"/>
       <c r="G93" s="72" t="s">
         <v>124</v>
       </c>
@@ -6656,16 +6658,16 @@
     </row>
     <row r="94" spans="1:14" ht="25.2">
       <c r="A94" s="11"/>
-      <c r="B94" s="113"/>
+      <c r="B94" s="124"/>
       <c r="C94" s="72" t="str">
         <f>master!C80</f>
         <v>実行例</v>
       </c>
-      <c r="D94" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E94" s="116"/>
-      <c r="F94" s="117"/>
+      <c r="D94" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E94" s="118"/>
+      <c r="F94" s="119"/>
       <c r="G94" s="72" t="s">
         <v>132</v>
       </c>
@@ -6683,16 +6685,16 @@
     </row>
     <row r="95" spans="1:14" ht="25.2">
       <c r="A95" s="11"/>
-      <c r="B95" s="113"/>
+      <c r="B95" s="124"/>
       <c r="C95" s="91" t="str">
         <f>master!C81</f>
         <v>実行結果</v>
       </c>
-      <c r="D95" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E95" s="116"/>
-      <c r="F95" s="117"/>
+      <c r="D95" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E95" s="118"/>
+      <c r="F95" s="119"/>
       <c r="G95" s="72" t="s">
         <v>132</v>
       </c>
@@ -6710,13 +6712,13 @@
     </row>
     <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="113"/>
+      <c r="B96" s="124"/>
       <c r="C96" s="92"/>
-      <c r="D96" s="115" t="s">
-        <v>200</v>
-      </c>
-      <c r="E96" s="116"/>
-      <c r="F96" s="117"/>
+      <c r="D96" s="117" t="s">
+        <v>190</v>
+      </c>
+      <c r="E96" s="118"/>
+      <c r="F96" s="119"/>
       <c r="G96" s="72" t="s">
         <v>124</v>
       </c>
@@ -6734,16 +6736,16 @@
     </row>
     <row r="97" spans="1:14" ht="25.2">
       <c r="A97" s="11"/>
-      <c r="B97" s="113"/>
+      <c r="B97" s="124"/>
       <c r="C97" s="72" t="str">
         <f>master!C82</f>
         <v>Planモード＆Agentモードまとめ</v>
       </c>
-      <c r="D97" s="115" t="s">
-        <v>145</v>
-      </c>
-      <c r="E97" s="116"/>
-      <c r="F97" s="117"/>
+      <c r="D97" s="117" t="s">
+        <v>142</v>
+      </c>
+      <c r="E97" s="118"/>
+      <c r="F97" s="119"/>
       <c r="G97" s="72" t="s">
         <v>132</v>
       </c>
@@ -6769,11 +6771,11 @@
         <f>master!C83</f>
         <v>開発したゲームやアプリをプレゼン</v>
       </c>
-      <c r="D98" s="115" t="s">
-        <v>199</v>
-      </c>
-      <c r="E98" s="116"/>
-      <c r="F98" s="117"/>
+      <c r="D98" s="117" t="s">
+        <v>189</v>
+      </c>
+      <c r="E98" s="118"/>
+      <c r="F98" s="119"/>
       <c r="G98" s="72" t="s">
         <v>127</v>
       </c>
@@ -6785,7 +6787,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="K98" s="76" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
@@ -6797,36 +6799,55 @@
     <row r="100" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B15:B25"/>
-    <mergeCell ref="B26:B34"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B63:B70"/>
+    <mergeCell ref="B71:B97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D45:F45"/>
@@ -6851,55 +6872,36 @@
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B63:B70"/>
-    <mergeCell ref="B71:B97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="B15:B25"/>
+    <mergeCell ref="B26:B34"/>
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="K11:K12"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6925,457 +6927,456 @@
   <dimension ref="B1:C83"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="125" customWidth="1"/>
-    <col min="2" max="2" width="40.109375" style="125" customWidth="1"/>
-    <col min="3" max="3" width="44" style="125" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="125"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.109375" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" s="125" customFormat="1">
-      <c r="B1" s="125" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" s="125" customFormat="1">
-      <c r="B2" s="126" t="s">
+    <row r="1" spans="2:3">
+      <c r="B1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3">
+      <c r="B2" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="126" t="s">
+      <c r="C2" s="93" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3" s="125" customFormat="1">
-      <c r="B3" s="125" t="s">
+    <row r="3" spans="2:3">
+      <c r="B3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="125" t="s">
+      <c r="C3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="2:3" s="125" customFormat="1">
-      <c r="B4" s="125" t="s">
+    <row r="4" spans="2:3">
+      <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:3" s="125" customFormat="1">
-      <c r="C5" s="125" t="s">
+    <row r="5" spans="2:3">
+      <c r="C5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="2:3" s="125" customFormat="1">
-      <c r="C6" s="125" t="s">
+    <row r="6" spans="2:3">
+      <c r="C6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="2:3" s="125" customFormat="1">
-      <c r="C7" s="125" t="s">
+    <row r="7" spans="2:3">
+      <c r="C7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:3" s="125" customFormat="1">
-      <c r="C8" s="125" t="s">
+    <row r="8" spans="2:3">
+      <c r="C8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="2:3" s="125" customFormat="1">
-      <c r="C9" s="125" t="s">
+    <row r="9" spans="2:3">
+      <c r="C9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:3" s="125" customFormat="1">
-      <c r="C10" s="125" t="s">
+    <row r="10" spans="2:3">
+      <c r="C10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="2:3" s="125" customFormat="1">
-      <c r="C11" s="125" t="s">
+    <row r="11" spans="2:3">
+      <c r="C11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="2:3" s="125" customFormat="1">
-      <c r="C12" s="125" t="s">
+    <row r="12" spans="2:3">
+      <c r="C12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="2:3" s="125" customFormat="1">
-      <c r="C13" s="125" t="s">
+    <row r="13" spans="2:3">
+      <c r="C13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:3" s="125" customFormat="1">
-      <c r="C14" s="125" t="s">
+    <row r="14" spans="2:3">
+      <c r="C14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:3" s="125" customFormat="1">
-      <c r="B15" s="125" t="s">
+    <row r="15" spans="2:3">
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="125" t="s">
+      <c r="C15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="2:3" s="125" customFormat="1">
-      <c r="C16" s="125" t="s">
+    <row r="16" spans="2:3">
+      <c r="C16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:3" s="125" customFormat="1">
-      <c r="C17" s="125" t="s">
+    <row r="17" spans="2:3">
+      <c r="C17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="2:3" s="125" customFormat="1">
-      <c r="C18" s="125" t="s">
+    <row r="18" spans="2:3">
+      <c r="C18" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="2:3" s="125" customFormat="1">
-      <c r="C19" s="125" t="s">
+    <row r="19" spans="2:3">
+      <c r="C19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="2:3" s="125" customFormat="1">
-      <c r="C20" s="125" t="s">
+    <row r="20" spans="2:3">
+      <c r="C20" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="2:3" s="125" customFormat="1">
-      <c r="C21" s="125" t="s">
+    <row r="21" spans="2:3">
+      <c r="C21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="2:3" s="125" customFormat="1">
-      <c r="C22" s="125" t="s">
+    <row r="22" spans="2:3">
+      <c r="C22" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="2:3" s="125" customFormat="1">
-      <c r="C23" s="125" t="s">
+    <row r="23" spans="2:3">
+      <c r="C23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="2:3" s="125" customFormat="1">
-      <c r="B24" s="125" t="s">
+    <row r="24" spans="2:3">
+      <c r="B24" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="125" t="s">
+      <c r="C24" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="2:3" s="125" customFormat="1">
-      <c r="C25" s="125" t="s">
+    <row r="25" spans="2:3">
+      <c r="C25" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="2:3" s="125" customFormat="1">
-      <c r="C26" s="125" t="s">
+    <row r="26" spans="2:3">
+      <c r="C26" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="2:3" s="125" customFormat="1">
-      <c r="C27" s="125" t="s">
+    <row r="27" spans="2:3">
+      <c r="C27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="2:3" s="125" customFormat="1">
-      <c r="C28" s="125" t="s">
+    <row r="28" spans="2:3">
+      <c r="C28" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="2:3" s="125" customFormat="1">
-      <c r="B29" s="125" t="s">
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="125" t="s">
+      <c r="C29" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="2:3" s="125" customFormat="1">
-      <c r="C30" s="125" t="s">
+    <row r="30" spans="2:3">
+      <c r="C30" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="2:3" s="125" customFormat="1">
-      <c r="C31" s="125" t="s">
+    <row r="31" spans="2:3">
+      <c r="C31" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="2:3" s="125" customFormat="1">
-      <c r="C32" s="125" t="s">
+    <row r="32" spans="2:3">
+      <c r="C32" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:3" s="125" customFormat="1">
-      <c r="C33" s="125" t="s">
+    <row r="33" spans="2:3">
+      <c r="C33" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="2:3" s="125" customFormat="1">
-      <c r="C34" s="125" t="s">
+    <row r="34" spans="2:3">
+      <c r="C34" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="2:3" s="125" customFormat="1">
-      <c r="C35" s="125" t="s">
+    <row r="35" spans="2:3">
+      <c r="C35" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="2:3" s="125" customFormat="1">
-      <c r="C36" s="125" t="s">
+    <row r="36" spans="2:3">
+      <c r="C36" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="2:3" s="125" customFormat="1">
-      <c r="C37" s="125" t="s">
+    <row r="37" spans="2:3">
+      <c r="C37" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="2:3" s="125" customFormat="1">
-      <c r="C38" s="125" t="s">
+    <row r="38" spans="2:3">
+      <c r="C38" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="2:3" s="125" customFormat="1">
-      <c r="C39" s="125" t="s">
+    <row r="39" spans="2:3">
+      <c r="C39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="2:3" s="125" customFormat="1">
-      <c r="C40" s="125" t="s">
+    <row r="40" spans="2:3">
+      <c r="C40" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="2:3" s="125" customFormat="1">
-      <c r="C41" s="125" t="s">
+    <row r="41" spans="2:3">
+      <c r="C41" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="2:3" s="125" customFormat="1">
-      <c r="C42" s="125" t="s">
+    <row r="42" spans="2:3">
+      <c r="C42" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="2:3" s="125" customFormat="1">
-      <c r="B43" s="125" t="s">
+    <row r="43" spans="2:3">
+      <c r="B43" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="125" t="s">
+      <c r="C43" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="2:3" s="125" customFormat="1">
-      <c r="C44" s="125" t="s">
+    <row r="44" spans="2:3">
+      <c r="C44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="2:3" s="125" customFormat="1">
-      <c r="C45" s="125" t="s">
+    <row r="45" spans="2:3">
+      <c r="C45" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="2:3" s="125" customFormat="1">
-      <c r="C46" s="125" t="s">
+    <row r="46" spans="2:3">
+      <c r="C46" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="2:3" s="125" customFormat="1">
-      <c r="C47" s="125" t="s">
+    <row r="47" spans="2:3">
+      <c r="C47" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="2:3" s="125" customFormat="1">
-      <c r="C48" s="125" t="s">
+    <row r="48" spans="2:3">
+      <c r="C48" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="2:3" s="125" customFormat="1">
-      <c r="C49" s="125" t="s">
+    <row r="49" spans="2:3">
+      <c r="C49" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="2:3" s="125" customFormat="1">
-      <c r="C50" s="125" t="s">
+    <row r="50" spans="2:3">
+      <c r="C50" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="2:3" s="125" customFormat="1">
-      <c r="B51" s="125" t="s">
+    <row r="51" spans="2:3">
+      <c r="B51" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="125" t="s">
+      <c r="C51" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="2:3" s="125" customFormat="1">
-      <c r="B52" s="125" t="s">
-        <v>193</v>
-      </c>
-      <c r="C52" s="125" t="s">
+    <row r="52" spans="2:3">
+      <c r="B52" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="53" spans="2:3" s="125" customFormat="1">
-      <c r="C53" s="125" t="s">
+    <row r="53" spans="2:3">
+      <c r="C53" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="2:3" s="125" customFormat="1">
-      <c r="C54" s="125" t="s">
+    <row r="54" spans="2:3">
+      <c r="C54" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="55" spans="2:3" s="125" customFormat="1">
-      <c r="C55" s="125" t="s">
+    <row r="55" spans="2:3">
+      <c r="C55" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="56" spans="2:3" s="125" customFormat="1">
-      <c r="C56" s="125" t="s">
+    <row r="56" spans="2:3">
+      <c r="C56" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="57" spans="2:3" s="125" customFormat="1">
-      <c r="C57" s="125" t="s">
+    <row r="57" spans="2:3">
+      <c r="C57" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="2:3" s="125" customFormat="1">
-      <c r="C58" s="125" t="s">
+    <row r="58" spans="2:3">
+      <c r="C58" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="2:3" s="125" customFormat="1">
-      <c r="C59" s="125" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" s="125" customFormat="1">
-      <c r="B60" s="125" t="s">
-        <v>194</v>
-      </c>
-      <c r="C60" s="125" t="s">
+    <row r="59" spans="2:3">
+      <c r="C59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3">
+      <c r="B60" t="s">
+        <v>184</v>
+      </c>
+      <c r="C60" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="2:3" s="125" customFormat="1">
-      <c r="C61" s="125" t="s">
+    <row r="61" spans="2:3">
+      <c r="C61" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="62" spans="2:3" s="125" customFormat="1">
-      <c r="C62" s="125" t="s">
+    <row r="62" spans="2:3">
+      <c r="C62" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="63" spans="2:3" s="125" customFormat="1">
-      <c r="C63" s="125" t="s">
+    <row r="63" spans="2:3">
+      <c r="C63" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="2:3" s="125" customFormat="1">
-      <c r="C64" s="125" t="s">
+    <row r="64" spans="2:3">
+      <c r="C64" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="3:3" s="125" customFormat="1">
-      <c r="C65" s="125" t="s">
+    <row r="65" spans="3:3">
+      <c r="C65" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="66" spans="3:3" s="125" customFormat="1">
-      <c r="C66" s="125" t="s">
+    <row r="66" spans="3:3">
+      <c r="C66" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="67" spans="3:3" s="125" customFormat="1">
-      <c r="C67" s="125" t="s">
+    <row r="67" spans="3:3">
+      <c r="C67" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="68" spans="3:3" s="125" customFormat="1">
-      <c r="C68" s="125" t="s">
+    <row r="68" spans="3:3">
+      <c r="C68" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="69" spans="3:3" s="125" customFormat="1">
-      <c r="C69" s="125" t="s">
+    <row r="69" spans="3:3">
+      <c r="C69" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="70" spans="3:3" s="125" customFormat="1">
-      <c r="C70" s="125" t="s">
+    <row r="70" spans="3:3">
+      <c r="C70" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="3:3" s="125" customFormat="1">
-      <c r="C71" s="125" t="s">
+    <row r="71" spans="3:3">
+      <c r="C71" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="72" spans="3:3" s="125" customFormat="1">
-      <c r="C72" s="125" t="s">
+    <row r="72" spans="3:3">
+      <c r="C72" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="73" spans="3:3" s="125" customFormat="1">
-      <c r="C73" s="125" t="s">
+    <row r="73" spans="3:3">
+      <c r="C73" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="74" spans="3:3" s="125" customFormat="1">
-      <c r="C74" s="125" t="s">
+    <row r="74" spans="3:3">
+      <c r="C74" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="75" spans="3:3" s="125" customFormat="1">
-      <c r="C75" s="125" t="s">
+    <row r="75" spans="3:3">
+      <c r="C75" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="76" spans="3:3" s="125" customFormat="1">
-      <c r="C76" s="125" t="s">
+    <row r="76" spans="3:3">
+      <c r="C76" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="3:3" s="125" customFormat="1">
-      <c r="C77" s="125" t="s">
+    <row r="77" spans="3:3">
+      <c r="C77" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="78" spans="3:3" s="125" customFormat="1">
-      <c r="C78" s="125" t="s">
+    <row r="78" spans="3:3">
+      <c r="C78" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="3:3" s="125" customFormat="1">
-      <c r="C79" s="125" t="s">
+    <row r="79" spans="3:3">
+      <c r="C79" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="80" spans="3:3" s="125" customFormat="1">
-      <c r="C80" s="125" t="s">
+    <row r="80" spans="3:3">
+      <c r="C80" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="81" spans="2:3" s="125" customFormat="1">
-      <c r="C81" s="125" t="s">
+    <row r="81" spans="2:3">
+      <c r="C81" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="2:3" s="125" customFormat="1">
-      <c r="C82" s="125" t="s">
+    <row r="82" spans="2:3">
+      <c r="C82" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="83" spans="2:3" s="125" customFormat="1">
-      <c r="B83" s="125" t="s">
-        <v>198</v>
-      </c>
-      <c r="C83" s="125" t="s">
+    <row r="83" spans="2:3">
+      <c r="B83" t="s">
+        <v>188</v>
+      </c>
+      <c r="C83" t="s">
         <v>118</v>
       </c>
     </row>

--- a/IG/AI Native-生成AI_IG.xlsx
+++ b/IG/AI Native-生成AI_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3885BB11-D456-4EE6-BE89-123685B6F428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D90175C-23DA-42A7-850E-EFB3C2207669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（1日）'!$A$1:$H$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$99</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="205">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -310,19 +310,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>研修ファイルサーバの保存先</t>
-    <rPh sb="0" eb="2">
-      <t>ケンシュウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>実施上のの注意点</t>
@@ -2843,7 +2830,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2907,18 +2894,9 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3039,9 +3017,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -3177,6 +3152,42 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3186,41 +3197,14 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3594,15 +3578,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="95" t="str">
+      <c r="B2" s="91" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3615,10 +3599,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="97"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3626,34 +3610,34 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="100" t="s">
+      <c r="B7" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="100"/>
+      <c r="C7" s="96"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A10" s="40">
+      <c r="A10" s="37">
         <v>0.39583333333333331</v>
       </c>
       <c r="B10" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="80" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -3661,355 +3645,355 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="42"/>
-      <c r="B11" s="70">
+      <c r="A11" s="39"/>
+      <c r="B11" s="66">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="81" t="str">
+      <c r="C11" s="77" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
       <c r="G11" s="14"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="40">
+      <c r="A12" s="37">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="82"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="78"/>
       <c r="G12" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="41"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="83"/>
-      <c r="F13" s="26"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="79"/>
+      <c r="F13" s="23"/>
       <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="41"/>
-      <c r="B14" s="40">
+      <c r="A14" s="38"/>
+      <c r="B14" s="37">
         <v>0.4375</v>
       </c>
-      <c r="C14" s="81" t="str">
+      <c r="C14" s="77" t="str">
         <f>master!B4</f>
         <v>導入編</v>
       </c>
-      <c r="F14" s="94"/>
+      <c r="F14" s="90"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="42"/>
-      <c r="B15" s="55" t="s">
+      <c r="A15" s="39"/>
+      <c r="B15" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="82"/>
-      <c r="F15" s="94"/>
+      <c r="C15" s="78"/>
+      <c r="F15" s="90"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="40">
+      <c r="A16" s="37">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="83"/>
-      <c r="F16" s="94"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="79"/>
+      <c r="F16" s="90"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="41"/>
-      <c r="B17" s="43">
+      <c r="A17" s="38"/>
+      <c r="B17" s="40">
         <v>0.46875</v>
       </c>
-      <c r="C17" s="81" t="str">
+      <c r="C17" s="77" t="str">
         <f>master!B15</f>
         <v>復習編</v>
       </c>
-      <c r="F17" s="94"/>
+      <c r="F17" s="90"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="41"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="83"/>
-      <c r="F18" s="94"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="79"/>
+      <c r="F18" s="90"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="42"/>
-      <c r="B19" s="45">
+      <c r="A19" s="39"/>
+      <c r="B19" s="42">
         <v>0.48958333333333331</v>
       </c>
-      <c r="C19" s="80" t="str">
+      <c r="C19" s="76" t="str">
         <f>master!B24</f>
         <v>AI-Native研修の目的</v>
       </c>
-      <c r="F19" s="94"/>
+      <c r="F19" s="90"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="67">
+      <c r="A20" s="63">
         <v>0.5</v>
       </c>
-      <c r="B20" s="67">
+      <c r="B20" s="63">
         <v>0.5</v>
       </c>
-      <c r="C20" s="81" t="str">
+      <c r="C20" s="77" t="str">
         <f>master!B29</f>
         <v>キャリア編</v>
       </c>
-      <c r="F20" s="94"/>
+      <c r="F20" s="90"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="60"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="83"/>
-      <c r="F21" s="94"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="79"/>
+      <c r="F21" s="90"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41">
+      <c r="A22" s="38"/>
+      <c r="B22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="85" t="s">
+      <c r="C22" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="25"/>
+      <c r="F22" s="22"/>
       <c r="G22" s="10"/>
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="42"/>
-      <c r="B23" s="41" t="s">
+      <c r="A23" s="39"/>
+      <c r="B23" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="86"/>
-      <c r="F23" s="25"/>
+      <c r="C23" s="82"/>
+      <c r="F23" s="22"/>
       <c r="G23" s="10"/>
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="40">
+      <c r="A24" s="37">
         <v>0.54166666666666663</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="86"/>
-      <c r="F24" s="25"/>
+      <c r="C24" s="82"/>
+      <c r="F24" s="22"/>
       <c r="G24" s="10"/>
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="41"/>
-      <c r="B25" s="42" t="s">
+      <c r="A25" s="38"/>
+      <c r="B25" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="87"/>
-      <c r="F25" s="25"/>
+      <c r="C25" s="83"/>
+      <c r="F25" s="22"/>
       <c r="G25" s="10"/>
       <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="41"/>
-      <c r="B26" s="45">
+      <c r="A26" s="38"/>
+      <c r="B26" s="42">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="83"/>
-      <c r="F26" s="94"/>
+      <c r="C26" s="79"/>
+      <c r="F26" s="90"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="42"/>
-      <c r="B27" s="43">
+      <c r="A27" s="39"/>
+      <c r="B27" s="40">
         <v>0.57291666666666663</v>
       </c>
-      <c r="C27" s="81" t="str">
+      <c r="C27" s="77" t="str">
         <f>master!B43</f>
         <v>NTTデータの強み編</v>
       </c>
-      <c r="F27" s="94"/>
+      <c r="F27" s="90"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="40">
+      <c r="A28" s="37">
         <v>0.58333333333333337</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="83"/>
-      <c r="F28" s="94"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="79"/>
+      <c r="F28" s="90"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="41"/>
-      <c r="B29" s="43">
+      <c r="A29" s="38"/>
+      <c r="B29" s="40">
         <v>0.59375</v>
       </c>
-      <c r="C29" s="69" t="str">
+      <c r="C29" s="65" t="str">
         <f>master!B52</f>
         <v>ハンズオン編:ChatGPT</v>
       </c>
-      <c r="D29" s="59"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="94"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="90"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="41"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="94"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="90"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="42"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="59"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="94"/>
+      <c r="F31" s="90"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="67">
+      <c r="A32" s="63">
         <v>0.625</v>
       </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="59"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="94"/>
+      <c r="F32" s="90"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="60"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="94"/>
+      <c r="A33" s="57"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="60"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="90"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="60"/>
-      <c r="B34" s="43">
+      <c r="A34" s="57"/>
+      <c r="B34" s="40">
         <v>0.60416666666666663</v>
       </c>
-      <c r="C34" s="69" t="str">
+      <c r="C34" s="65" t="str">
         <f>master!B60</f>
         <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
       </c>
-      <c r="D34" s="59"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="94"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="90"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="42"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="94"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="90"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="40">
+      <c r="A36" s="37">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="59"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="94"/>
+      <c r="F36" s="90"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="41"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="63"/>
-      <c r="D37" s="59"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="56"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="94"/>
+      <c r="F37" s="90"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="41"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="59"/>
+      <c r="A38" s="38"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="94"/>
+      <c r="F38" s="90"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="41"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="59"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="56"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="94"/>
+      <c r="F39" s="90"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="43">
+      <c r="A40" s="40">
         <v>0.70833333333333337</v>
       </c>
-      <c r="B40" s="43">
+      <c r="B40" s="40">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C40" s="63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D40" s="59"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="94"/>
+      <c r="C40" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D40" s="56"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="90"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="41"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="63"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="94"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="90"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="45"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="94"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="90"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A43" s="44"/>
-      <c r="B43" s="90">
+      <c r="A43" s="41"/>
+      <c r="B43" s="86">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="89" t="s">
-        <v>185</v>
-      </c>
-      <c r="D43" s="60"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="25"/>
+      <c r="C43" s="85" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="57"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="22"/>
       <c r="G43" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.6" thickBot="1">
       <c r="A44" s="6"/>
-      <c r="D44" s="23"/>
+      <c r="D44" s="21"/>
       <c r="H44" s="6"/>
     </row>
   </sheetData>
@@ -4033,7 +4017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:L13"/>
+  <dimension ref="A2:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -4043,25 +4027,25 @@
     <col min="5" max="5" width="16.33203125" style="10" customWidth="1"/>
     <col min="6" max="6" width="10.44140625" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="30" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" style="27" customWidth="1"/>
     <col min="9" max="10" width="6.6640625" style="10" customWidth="1"/>
     <col min="11" max="11" width="38.44140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="4.6640625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" s="34" customFormat="1" ht="36.75" customHeight="1">
+    <row r="2" spans="1:12" s="31" customFormat="1" ht="36.75" customHeight="1">
       <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:12">
@@ -4070,36 +4054,36 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="29"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="19"/>
       <c r="J3" s="19"/>
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="106"/>
+      <c r="C4" s="102"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="29"/>
+      <c r="H4" s="26"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="107"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4108,132 +4092,126 @@
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="108" t="s">
+      <c r="C7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="108"/>
-      <c r="F7" s="36" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="33" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="48" t="s">
+      <c r="C8" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="39" t="s">
+      <c r="E8" s="44"/>
+      <c r="F8" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="36" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="24"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="G9" s="10"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+    <row r="10" spans="1:12">
+      <c r="A10" s="10"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="105" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="97" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="97"/>
+      <c r="K10" s="97" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="102" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="109" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="101" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="98"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" ht="63">
       <c r="A12" s="10"/>
-      <c r="B12" s="102"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="102"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="99" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="122" t="s">
+        <v>181</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="62">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K12" s="20"/>
       <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:12" ht="63">
-      <c r="A13" s="10"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="103" t="s">
-        <v>181</v>
-      </c>
-      <c r="E13" s="104"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="65" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="66">
-        <v>1.0416666666666666E-2</v>
-      </c>
-      <c r="K13" s="20"/>
-      <c r="L13" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:J10"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4246,7 +4224,7 @@
           <x14:formula1>
             <xm:f>master!$C$48:$C$50</xm:f>
           </x14:formula1>
-          <xm:sqref>H13</xm:sqref>
+          <xm:sqref>H12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4306,12 +4284,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4322,32 +4300,32 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="33"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="113"/>
-      <c r="C6" s="113"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="33"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30"/>
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="10"/>
@@ -4359,23 +4337,23 @@
       <c r="M7" s="10"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36" t="s">
+      <c r="D8" s="104" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="104"/>
+      <c r="F8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="51"/>
+      <c r="I8" s="48"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -4383,20 +4361,20 @@
       <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="B9" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="71" t="s">
+      <c r="B9" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="C9" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39" t="s">
+      <c r="E9" s="124"/>
+      <c r="F9" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="36" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="6"/>
@@ -4406,29 +4384,29 @@
     </row>
     <row r="11" spans="1:14" ht="24" customHeight="1">
       <c r="A11" s="10"/>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="102" t="s">
+      <c r="D11" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102" t="s">
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="101" t="s">
+      <c r="H11" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="111" t="s">
+      <c r="I11" s="119" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="120"/>
+      <c r="K11" s="97" t="s">
         <v>33</v>
-      </c>
-      <c r="J11" s="112"/>
-      <c r="K11" s="101" t="s">
-        <v>34</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -4436,405 +4414,405 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="10"/>
-      <c r="B12" s="102"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="31" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="31" t="s">
+      <c r="J12" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="102"/>
+      <c r="K12" s="98"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" ht="75.599999999999994">
       <c r="A13" s="10"/>
-      <c r="B13" s="121" t="str">
+      <c r="B13" s="107" t="str">
         <f>master!B3</f>
         <v>自己紹介</v>
       </c>
-      <c r="C13" s="54" t="str">
+      <c r="C13" s="51" t="str">
         <f>master!C3</f>
         <v>ー</v>
       </c>
-      <c r="D13" s="114" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="115"/>
-      <c r="F13" s="116"/>
-      <c r="G13" s="54" t="s">
-        <v>121</v>
+      <c r="D13" s="115" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" s="116"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="51" t="s">
+        <v>120</v>
       </c>
       <c r="H13" s="12"/>
-      <c r="I13" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="50">
+      <c r="I13" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K13" s="46"/>
+      <c r="K13" s="43"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" ht="88.2">
       <c r="A14" s="10"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="117" t="s">
-        <v>180</v>
-      </c>
-      <c r="E14" s="118"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="72" t="s">
+      <c r="B14" s="108"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="112" t="s">
         <v>179</v>
       </c>
-      <c r="H14" s="73"/>
-      <c r="I14" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="75">
+      <c r="E14" s="113"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="71">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K14" s="76"/>
+      <c r="K14" s="72"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="138.6">
       <c r="A15" s="10"/>
-      <c r="B15" s="120" t="str">
+      <c r="B15" s="118" t="str">
         <f>master!B4</f>
         <v>導入編</v>
       </c>
-      <c r="C15" s="54" t="str">
+      <c r="C15" s="51" t="str">
         <f>master!C4</f>
         <v>あなたはもう生成ＡＩを使っていますか？</v>
       </c>
-      <c r="D15" s="114" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="115"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="54" t="s">
-        <v>122</v>
+      <c r="D15" s="115" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="116"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="51" t="s">
+        <v>121</v>
       </c>
       <c r="H15" s="12"/>
-      <c r="I15" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="50">
+      <c r="I15" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K15" s="46"/>
+      <c r="K15" s="43"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" ht="75.599999999999994">
       <c r="A16" s="11"/>
-      <c r="B16" s="120"/>
-      <c r="C16" s="54" t="str">
+      <c r="B16" s="118"/>
+      <c r="C16" s="51" t="str">
         <f>master!C5</f>
         <v>FYI：システム開発SaaS　「GEAR.indigo」</v>
       </c>
-      <c r="D16" s="114" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" s="115"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="54" t="s">
-        <v>126</v>
+      <c r="D16" s="115" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="116"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="51" t="s">
+        <v>125</v>
       </c>
       <c r="H16" s="12"/>
-      <c r="I16" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" s="50">
+      <c r="I16" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K16" s="46"/>
+      <c r="K16" s="43"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="37.799999999999997">
       <c r="A17" s="11"/>
-      <c r="B17" s="120"/>
-      <c r="C17" s="54" t="str">
+      <c r="B17" s="118"/>
+      <c r="C17" s="51" t="str">
         <f>master!C6</f>
         <v>FYI：GEAR.indigo　「業務要件一覧」</v>
       </c>
-      <c r="D17" s="114" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="115"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="54" t="s">
-        <v>124</v>
+      <c r="D17" s="115" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="116"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H17" s="12"/>
-      <c r="I17" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="50">
+      <c r="I17" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K17" s="46"/>
+      <c r="K17" s="43"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
     <row r="18" spans="1:14" ht="37.799999999999997">
       <c r="A18" s="11"/>
-      <c r="B18" s="120"/>
-      <c r="C18" s="54" t="str">
+      <c r="B18" s="118"/>
+      <c r="C18" s="51" t="str">
         <f>master!C7</f>
         <v>FYI：GEAR.indigo　「システム化業務フロー」</v>
       </c>
-      <c r="D18" s="114" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" s="115"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="54" t="s">
-        <v>124</v>
+      <c r="D18" s="115" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="116"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H18" s="12"/>
-      <c r="I18" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="50">
+      <c r="I18" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K18" s="46"/>
+      <c r="K18" s="43"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="120"/>
-      <c r="C19" s="54" t="str">
+      <c r="B19" s="118"/>
+      <c r="C19" s="51" t="str">
         <f>master!C8</f>
         <v>FYI：GEAR.indigo　「テーブル定義書」</v>
       </c>
-      <c r="D19" s="114" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" s="115"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="54" t="s">
-        <v>124</v>
+      <c r="D19" s="115" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="116"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H19" s="12"/>
-      <c r="I19" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" s="50">
+      <c r="I19" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K19" s="46"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="1:14" ht="37.799999999999997">
       <c r="A20" s="11"/>
-      <c r="B20" s="120"/>
-      <c r="C20" s="54" t="str">
+      <c r="B20" s="118"/>
+      <c r="C20" s="51" t="str">
         <f>master!C9</f>
         <v>FYI：GEAR.indigo　「画面定義書」</v>
       </c>
-      <c r="D20" s="114" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="115"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="54" t="s">
-        <v>124</v>
+      <c r="D20" s="115" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="116"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H20" s="12"/>
-      <c r="I20" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" s="50">
+      <c r="I20" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K20" s="46"/>
+      <c r="K20" s="43"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
     <row r="21" spans="1:14" ht="50.4">
       <c r="A21" s="11"/>
-      <c r="B21" s="120"/>
-      <c r="C21" s="54" t="str">
+      <c r="B21" s="118"/>
+      <c r="C21" s="51" t="str">
         <f>master!C10</f>
         <v>GEAR.indigo が （いずれ）見せてくれるもの</v>
       </c>
-      <c r="D21" s="114" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" s="115"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="54" t="s">
-        <v>125</v>
+      <c r="D21" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="116"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" s="50">
+      <c r="I21" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K21" s="46"/>
+      <c r="K21" s="43"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" ht="37.799999999999997">
       <c r="A22" s="11"/>
-      <c r="B22" s="120"/>
-      <c r="C22" s="54" t="str">
+      <c r="B22" s="118"/>
+      <c r="C22" s="51" t="str">
         <f>master!C11</f>
         <v>あなたはどちらになりたいですか？</v>
       </c>
-      <c r="D22" s="114" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="115"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="54" t="s">
-        <v>124</v>
+      <c r="D22" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="116"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H22" s="12"/>
-      <c r="I22" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" s="50">
+      <c r="I22" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K22" s="46"/>
+      <c r="K22" s="43"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" ht="37.799999999999997">
       <c r="A23" s="11"/>
-      <c r="B23" s="120"/>
-      <c r="C23" s="54" t="str">
+      <c r="B23" s="118"/>
+      <c r="C23" s="51" t="str">
         <f>master!C12</f>
         <v>いま、生成AIができること　（システム開発関連）</v>
       </c>
-      <c r="D23" s="114" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="115"/>
-      <c r="F23" s="116"/>
-      <c r="G23" s="54" t="s">
-        <v>124</v>
+      <c r="D23" s="115" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="116"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H23" s="12"/>
-      <c r="I23" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J23" s="50">
+      <c r="I23" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K23" s="46"/>
+      <c r="K23" s="43"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="120"/>
-      <c r="C24" s="54" t="str">
+      <c r="B24" s="118"/>
+      <c r="C24" s="51" t="str">
         <f>master!C13</f>
         <v>いま、生成ＡＩができないこと</v>
       </c>
-      <c r="D24" s="114" t="s">
-        <v>204</v>
-      </c>
-      <c r="E24" s="115"/>
-      <c r="F24" s="116"/>
-      <c r="G24" s="54" t="s">
-        <v>126</v>
+      <c r="D24" s="115" t="s">
+        <v>203</v>
+      </c>
+      <c r="E24" s="116"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="51" t="s">
+        <v>125</v>
       </c>
       <c r="H24" s="12"/>
-      <c r="I24" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J24" s="50">
+      <c r="I24" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K24" s="46"/>
+      <c r="K24" s="43"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" ht="226.8">
       <c r="A25" s="11"/>
-      <c r="B25" s="120"/>
-      <c r="C25" s="54" t="str">
+      <c r="B25" s="118"/>
+      <c r="C25" s="51" t="str">
         <f>master!C14</f>
         <v>生成ＡＩを使う心得８条</v>
       </c>
-      <c r="D25" s="114" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" s="115"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="54" t="s">
+      <c r="D25" s="115" t="s">
         <v>135</v>
       </c>
+      <c r="E25" s="116"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="51" t="s">
+        <v>134</v>
+      </c>
       <c r="H25" s="12"/>
-      <c r="I25" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J25" s="50">
+      <c r="I25" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K25" s="46"/>
+      <c r="K25" s="43"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
     <row r="26" spans="1:14" ht="25.2">
       <c r="A26" s="11"/>
-      <c r="B26" s="120" t="str">
+      <c r="B26" s="118" t="str">
         <f>master!B15</f>
         <v>復習編</v>
       </c>
-      <c r="C26" s="54" t="str">
+      <c r="C26" s="51" t="str">
         <f>master!C15</f>
         <v>NTTDATAが目指す方向性</v>
       </c>
-      <c r="D26" s="114" t="s">
-        <v>205</v>
-      </c>
-      <c r="E26" s="115"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="54" t="s">
-        <v>132</v>
+      <c r="D26" s="115" t="s">
+        <v>204</v>
+      </c>
+      <c r="E26" s="116"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="51" t="s">
+        <v>131</v>
       </c>
       <c r="H26" s="12"/>
-      <c r="I26" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" s="50">
+      <c r="I26" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K26" s="46" t="s">
-        <v>196</v>
+      <c r="K26" s="43" t="s">
+        <v>195</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -4842,28 +4820,28 @@
     </row>
     <row r="27" spans="1:14" ht="25.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="120"/>
-      <c r="C27" s="54" t="str">
+      <c r="B27" s="118"/>
+      <c r="C27" s="51" t="str">
         <f>master!C16</f>
         <v>NTTデータ新入社員向け生成AI基礎講座</v>
       </c>
-      <c r="D27" s="114" t="s">
-        <v>205</v>
-      </c>
-      <c r="E27" s="115"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="54" t="s">
-        <v>132</v>
+      <c r="D27" s="115" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" s="116"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="51" t="s">
+        <v>131</v>
       </c>
       <c r="H27" s="12"/>
-      <c r="I27" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" s="50">
+      <c r="I27" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K27" s="46" t="s">
-        <v>196</v>
+      <c r="K27" s="43" t="s">
+        <v>195</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -4871,354 +4849,354 @@
     </row>
     <row r="28" spans="1:14" ht="25.2">
       <c r="A28" s="11"/>
-      <c r="B28" s="120"/>
-      <c r="C28" s="54" t="str">
+      <c r="B28" s="118"/>
+      <c r="C28" s="51" t="str">
         <f>master!C17</f>
         <v>プロンプト設計の基本</v>
       </c>
-      <c r="D28" s="114" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" s="115"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="54" t="s">
-        <v>132</v>
+      <c r="D28" s="115" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="116"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="51" t="s">
+        <v>131</v>
       </c>
       <c r="H28" s="12"/>
-      <c r="I28" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J28" s="50">
+      <c r="I28" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K28" s="46"/>
+      <c r="K28" s="43"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
     <row r="29" spans="1:14" ht="75.599999999999994">
       <c r="A29" s="11"/>
-      <c r="B29" s="120"/>
-      <c r="C29" s="54" t="str">
+      <c r="B29" s="118"/>
+      <c r="C29" s="51" t="str">
         <f>master!C18</f>
         <v>プロンプト設計の基本を踏まえた構造型プロンプト</v>
       </c>
-      <c r="D29" s="114" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" s="115"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="54" t="s">
-        <v>126</v>
+      <c r="D29" s="115" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="116"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="51" t="s">
+        <v>125</v>
       </c>
       <c r="H29" s="12"/>
-      <c r="I29" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J29" s="50">
+      <c r="I29" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K29" s="46"/>
+      <c r="K29" s="43"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="11"/>
-      <c r="B30" s="120"/>
-      <c r="C30" s="54" t="str">
+      <c r="B30" s="118"/>
+      <c r="C30" s="51" t="str">
         <f>master!C19</f>
         <v>本セクションで学ぶこと</v>
       </c>
-      <c r="D30" s="114"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="116"/>
-      <c r="G30" s="54" t="s">
-        <v>120</v>
+      <c r="D30" s="115"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="51" t="s">
+        <v>119</v>
       </c>
       <c r="H30" s="12"/>
-      <c r="I30" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="50">
+      <c r="I30" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K30" s="46"/>
+      <c r="K30" s="43"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
     <row r="31" spans="1:14" ht="50.4">
       <c r="A31" s="11"/>
-      <c r="B31" s="120"/>
-      <c r="C31" s="54" t="str">
+      <c r="B31" s="118"/>
+      <c r="C31" s="51" t="str">
         <f>master!C20</f>
         <v>エージェントAIとは何か？</v>
       </c>
-      <c r="D31" s="114" t="s">
-        <v>159</v>
-      </c>
-      <c r="E31" s="115"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="54" t="s">
-        <v>125</v>
+      <c r="D31" s="115" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" s="116"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H31" s="12"/>
-      <c r="I31" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="50">
+      <c r="I31" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K31" s="46"/>
+      <c r="K31" s="43"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
     <row r="32" spans="1:14" ht="25.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="120"/>
-      <c r="C32" s="54" t="str">
+      <c r="B32" s="118"/>
+      <c r="C32" s="51" t="str">
         <f>master!C21</f>
         <v>エージェントの処理</v>
       </c>
-      <c r="D32" s="114" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="115"/>
-      <c r="F32" s="116"/>
-      <c r="G32" s="54" t="s">
-        <v>132</v>
+      <c r="D32" s="115" t="s">
+        <v>150</v>
+      </c>
+      <c r="E32" s="116"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="51" t="s">
+        <v>131</v>
       </c>
       <c r="H32" s="12"/>
-      <c r="I32" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" s="50">
+      <c r="I32" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K32" s="46"/>
+      <c r="K32" s="43"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="120"/>
-      <c r="C33" s="54" t="str">
+      <c r="B33" s="118"/>
+      <c r="C33" s="51" t="str">
         <f>master!C22</f>
         <v>AIエージェントのアーキテクチャ</v>
       </c>
-      <c r="D33" s="114" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="115"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="54" t="s">
-        <v>124</v>
+      <c r="D33" s="115" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="116"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H33" s="12"/>
-      <c r="I33" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J33" s="50">
+      <c r="I33" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K33" s="46"/>
+      <c r="K33" s="43"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="120"/>
-      <c r="C34" s="54" t="str">
+      <c r="B34" s="118"/>
+      <c r="C34" s="51" t="str">
         <f>master!C23</f>
         <v>AIの強みを生かすポイント</v>
       </c>
-      <c r="D34" s="114" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="115"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="54" t="s">
-        <v>124</v>
+      <c r="D34" s="115" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="116"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H34" s="12"/>
-      <c r="I34" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J34" s="50">
+      <c r="I34" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K34" s="46"/>
+      <c r="K34" s="43"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="11"/>
-      <c r="B35" s="120" t="str">
+      <c r="B35" s="118" t="str">
         <f>master!B24</f>
         <v>AI-Native研修の目的</v>
       </c>
-      <c r="C35" s="54" t="str">
+      <c r="C35" s="51" t="str">
         <f>master!C24</f>
         <v>1.研修概要</v>
       </c>
-      <c r="D35" s="114"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="54" t="s">
-        <v>120</v>
+      <c r="D35" s="115"/>
+      <c r="E35" s="116"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="51" t="s">
+        <v>119</v>
       </c>
       <c r="H35" s="12"/>
-      <c r="I35" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="J35" s="50">
+      <c r="I35" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="J35" s="47">
         <v>0</v>
       </c>
-      <c r="K35" s="46"/>
+      <c r="K35" s="43"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
     <row r="36" spans="1:14" ht="25.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="120"/>
-      <c r="C36" s="54" t="str">
+      <c r="B36" s="118"/>
+      <c r="C36" s="51" t="str">
         <f>master!C25</f>
         <v>2-1　背景目的</v>
       </c>
-      <c r="D36" s="114" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" s="115"/>
-      <c r="F36" s="116"/>
-      <c r="G36" s="54" t="s">
-        <v>132</v>
+      <c r="D36" s="115" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="116"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="51" t="s">
+        <v>131</v>
       </c>
       <c r="H36" s="12"/>
-      <c r="I36" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J36" s="50">
+      <c r="I36" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K36" s="46"/>
+      <c r="K36" s="43"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
     <row r="37" spans="1:14" ht="151.19999999999999">
       <c r="A37" s="11"/>
-      <c r="B37" s="120"/>
-      <c r="C37" s="54" t="str">
+      <c r="B37" s="118"/>
+      <c r="C37" s="51" t="str">
         <f>master!C26</f>
         <v>2-3　研修のゴールと獲得可能な経験</v>
       </c>
-      <c r="D37" s="114" t="s">
-        <v>198</v>
-      </c>
-      <c r="E37" s="115"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="54" t="s">
+      <c r="D37" s="115" t="s">
         <v>197</v>
       </c>
+      <c r="E37" s="116"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="51" t="s">
+        <v>196</v>
+      </c>
       <c r="H37" s="12"/>
-      <c r="I37" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J37" s="50">
+      <c r="I37" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K37" s="46"/>
+      <c r="K37" s="43"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="120"/>
-      <c r="C38" s="54" t="str">
+      <c r="B38" s="118"/>
+      <c r="C38" s="51" t="str">
         <f>master!C27</f>
         <v>AIエージェントを用いたシステム開発タスクの実行の大まかな流れ</v>
       </c>
-      <c r="D38" s="114" t="s">
-        <v>152</v>
-      </c>
-      <c r="E38" s="115"/>
-      <c r="F38" s="116"/>
-      <c r="G38" s="54" t="s">
-        <v>124</v>
+      <c r="D38" s="115" t="s">
+        <v>151</v>
+      </c>
+      <c r="E38" s="116"/>
+      <c r="F38" s="117"/>
+      <c r="G38" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H38" s="12"/>
-      <c r="I38" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J38" s="50">
+      <c r="I38" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K38" s="46"/>
+      <c r="K38" s="43"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
     <row r="39" spans="1:14" ht="37.799999999999997">
       <c r="A39" s="11"/>
-      <c r="B39" s="120"/>
-      <c r="C39" s="54" t="str">
+      <c r="B39" s="118"/>
+      <c r="C39" s="51" t="str">
         <f>master!C28</f>
         <v>学ぶ範囲</v>
       </c>
-      <c r="D39" s="114" t="s">
-        <v>160</v>
-      </c>
-      <c r="E39" s="115"/>
-      <c r="F39" s="116"/>
-      <c r="G39" s="54" t="s">
-        <v>124</v>
+      <c r="D39" s="115" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" s="116"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H39" s="12"/>
-      <c r="I39" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J39" s="50">
+      <c r="I39" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K39" s="46"/>
+      <c r="K39" s="43"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
     <row r="40" spans="1:14" ht="50.4">
       <c r="A40" s="11"/>
-      <c r="B40" s="120" t="str">
+      <c r="B40" s="118" t="str">
         <f>master!B29</f>
         <v>キャリア編</v>
       </c>
-      <c r="C40" s="54" t="str">
+      <c r="C40" s="51" t="str">
         <f>master!C29</f>
         <v>おまけ：新人の仕事はどうなるか？ これまで</v>
       </c>
-      <c r="D40" s="114" t="s">
-        <v>162</v>
-      </c>
-      <c r="E40" s="115"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="54" t="s">
-        <v>125</v>
+      <c r="D40" s="115" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="116"/>
+      <c r="F40" s="117"/>
+      <c r="G40" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H40" s="12"/>
-      <c r="I40" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J40" s="50">
+      <c r="I40" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K40" s="46" t="s">
-        <v>191</v>
+      <c r="K40" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
@@ -5226,28 +5204,28 @@
     </row>
     <row r="41" spans="1:14" ht="63">
       <c r="A41" s="11"/>
-      <c r="B41" s="120"/>
-      <c r="C41" s="54" t="str">
+      <c r="B41" s="118"/>
+      <c r="C41" s="51" t="str">
         <f>master!C30</f>
         <v>おまけ：生成AI before/after</v>
       </c>
-      <c r="D41" s="114" t="s">
-        <v>163</v>
-      </c>
-      <c r="E41" s="115"/>
-      <c r="F41" s="116"/>
-      <c r="G41" s="54" t="s">
-        <v>123</v>
+      <c r="D41" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" s="116"/>
+      <c r="F41" s="117"/>
+      <c r="G41" s="51" t="s">
+        <v>122</v>
       </c>
       <c r="H41" s="12"/>
-      <c r="I41" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J41" s="50">
+      <c r="I41" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K41" s="46" t="s">
-        <v>191</v>
+      <c r="K41" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
@@ -5255,28 +5233,28 @@
     </row>
     <row r="42" spans="1:14" ht="50.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="120"/>
-      <c r="C42" s="54" t="str">
+      <c r="B42" s="118"/>
+      <c r="C42" s="51" t="str">
         <f>master!C31</f>
         <v>おまけ：新人の仕事はどうなるか？　これから</v>
       </c>
-      <c r="D42" s="114" t="s">
-        <v>161</v>
-      </c>
-      <c r="E42" s="115"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="54" t="s">
-        <v>125</v>
+      <c r="D42" s="115" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="116"/>
+      <c r="F42" s="117"/>
+      <c r="G42" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H42" s="12"/>
-      <c r="I42" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J42" s="50">
+      <c r="I42" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K42" s="46" t="s">
-        <v>191</v>
+      <c r="K42" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -5284,28 +5262,28 @@
     </row>
     <row r="43" spans="1:14" ht="100.8">
       <c r="A43" s="11"/>
-      <c r="B43" s="120"/>
-      <c r="C43" s="54" t="str">
+      <c r="B43" s="118"/>
+      <c r="C43" s="51" t="str">
         <f>master!C32</f>
         <v>代表的な若手の仕事</v>
       </c>
-      <c r="D43" s="114" t="s">
-        <v>199</v>
-      </c>
-      <c r="E43" s="115"/>
-      <c r="F43" s="116"/>
-      <c r="G43" s="54" t="s">
-        <v>141</v>
+      <c r="D43" s="115" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="116"/>
+      <c r="F43" s="117"/>
+      <c r="G43" s="51" t="s">
+        <v>140</v>
       </c>
       <c r="H43" s="12"/>
-      <c r="I43" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J43" s="50">
+      <c r="I43" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K43" s="46" t="s">
-        <v>191</v>
+      <c r="K43" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -5313,28 +5291,28 @@
     </row>
     <row r="44" spans="1:14" ht="88.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="120"/>
-      <c r="C44" s="54" t="str">
+      <c r="B44" s="118"/>
+      <c r="C44" s="51" t="str">
         <f>master!C33</f>
         <v>そもそも</v>
       </c>
-      <c r="D44" s="114" t="s">
-        <v>200</v>
-      </c>
-      <c r="E44" s="115"/>
-      <c r="F44" s="116"/>
-      <c r="G44" s="54" t="s">
-        <v>130</v>
+      <c r="D44" s="115" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" s="116"/>
+      <c r="F44" s="117"/>
+      <c r="G44" s="51" t="s">
+        <v>129</v>
       </c>
       <c r="H44" s="12"/>
-      <c r="I44" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="50">
+      <c r="I44" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K44" s="46" t="s">
-        <v>191</v>
+      <c r="K44" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
@@ -5342,28 +5320,28 @@
     </row>
     <row r="45" spans="1:14" ht="37.799999999999997">
       <c r="A45" s="11"/>
-      <c r="B45" s="120"/>
-      <c r="C45" s="54" t="str">
+      <c r="B45" s="118"/>
+      <c r="C45" s="51" t="str">
         <f>master!C34</f>
         <v>2040年の就業構造推計（改定版）の概要</v>
       </c>
-      <c r="D45" s="114" t="s">
-        <v>164</v>
-      </c>
-      <c r="E45" s="115"/>
-      <c r="F45" s="116"/>
-      <c r="G45" s="54" t="s">
-        <v>124</v>
+      <c r="D45" s="115" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" s="116"/>
+      <c r="F45" s="117"/>
+      <c r="G45" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H45" s="12"/>
-      <c r="I45" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J45" s="50">
+      <c r="I45" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K45" s="46" t="s">
-        <v>191</v>
+      <c r="K45" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
@@ -5371,28 +5349,28 @@
     </row>
     <row r="46" spans="1:14" ht="50.4">
       <c r="A46" s="11"/>
-      <c r="B46" s="120"/>
-      <c r="C46" s="54" t="str">
+      <c r="B46" s="118"/>
+      <c r="C46" s="51" t="str">
         <f>master!C35</f>
         <v>全国版就業構造推計（改定版）・職業間ミスマッチ</v>
       </c>
-      <c r="D46" s="114" t="s">
-        <v>165</v>
-      </c>
-      <c r="E46" s="115"/>
-      <c r="F46" s="116"/>
-      <c r="G46" s="54" t="s">
-        <v>125</v>
+      <c r="D46" s="115" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" s="116"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H46" s="12"/>
-      <c r="I46" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J46" s="50">
+      <c r="I46" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K46" s="46" t="s">
-        <v>191</v>
+      <c r="K46" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -5400,28 +5378,28 @@
     </row>
     <row r="47" spans="1:14" ht="50.4">
       <c r="A47" s="11"/>
-      <c r="B47" s="120"/>
-      <c r="C47" s="54" t="str">
+      <c r="B47" s="118"/>
+      <c r="C47" s="51" t="str">
         <f>master!C36</f>
         <v>（参考）将来の産業構造は・・・</v>
       </c>
-      <c r="D47" s="114" t="s">
-        <v>166</v>
-      </c>
-      <c r="E47" s="115"/>
-      <c r="F47" s="116"/>
-      <c r="G47" s="54" t="s">
-        <v>125</v>
+      <c r="D47" s="115" t="s">
+        <v>165</v>
+      </c>
+      <c r="E47" s="116"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H47" s="12"/>
-      <c r="I47" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J47" s="50">
+      <c r="I47" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K47" s="46" t="s">
-        <v>191</v>
+      <c r="K47" s="43" t="s">
+        <v>190</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
@@ -5429,1376 +5407,1456 @@
     </row>
     <row r="48" spans="1:14" ht="63">
       <c r="A48" s="11"/>
-      <c r="B48" s="120"/>
-      <c r="C48" s="54" t="str">
+      <c r="B48" s="118"/>
+      <c r="C48" s="51" t="str">
         <f>master!C37</f>
         <v>ヒント１：生成ＡＩと原理原則</v>
       </c>
-      <c r="D48" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="E48" s="115"/>
-      <c r="F48" s="116"/>
-      <c r="G48" s="54" t="s">
-        <v>123</v>
+      <c r="D48" s="115" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48" s="116"/>
+      <c r="F48" s="117"/>
+      <c r="G48" s="51" t="s">
+        <v>122</v>
       </c>
       <c r="H48" s="12"/>
-      <c r="I48" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J48" s="50">
+      <c r="I48" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K48" s="46"/>
+      <c r="K48" s="43"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" ht="50.4">
       <c r="A49" s="11"/>
-      <c r="B49" s="120"/>
-      <c r="C49" s="54" t="str">
+      <c r="B49" s="118"/>
+      <c r="C49" s="51" t="str">
         <f>master!C38</f>
         <v>ヒント2：プロンプトによる生成AIの挙動の違い</v>
       </c>
-      <c r="D49" s="114" t="s">
-        <v>192</v>
-      </c>
-      <c r="E49" s="115"/>
-      <c r="F49" s="116"/>
-      <c r="G49" s="54" t="s">
-        <v>125</v>
+      <c r="D49" s="115" t="s">
+        <v>191</v>
+      </c>
+      <c r="E49" s="116"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H49" s="12"/>
-      <c r="I49" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J49" s="50">
+      <c r="I49" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K49" s="46"/>
+      <c r="K49" s="43"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" ht="189">
       <c r="A50" s="11"/>
-      <c r="B50" s="120"/>
-      <c r="C50" s="54" t="str">
+      <c r="B50" s="118"/>
+      <c r="C50" s="51" t="str">
         <f>master!C39</f>
         <v>ヒント３：それでも生成AIを積極的に使うしかない</v>
       </c>
-      <c r="D50" s="114" t="s">
-        <v>193</v>
-      </c>
-      <c r="E50" s="115"/>
-      <c r="F50" s="116"/>
-      <c r="G50" s="54" t="s">
-        <v>134</v>
+      <c r="D50" s="115" t="s">
+        <v>192</v>
+      </c>
+      <c r="E50" s="116"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="51" t="s">
+        <v>133</v>
       </c>
       <c r="H50" s="12"/>
-      <c r="I50" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J50" s="50">
+      <c r="I50" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K50" s="46"/>
+      <c r="K50" s="43"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="11"/>
-      <c r="B51" s="120"/>
-      <c r="C51" s="54" t="str">
+      <c r="B51" s="118"/>
+      <c r="C51" s="51" t="str">
         <f>master!C40</f>
         <v>1. 研修概要</v>
       </c>
-      <c r="D51" s="114"/>
-      <c r="E51" s="115"/>
-      <c r="F51" s="116"/>
-      <c r="G51" s="54" t="s">
-        <v>120</v>
+      <c r="D51" s="115"/>
+      <c r="E51" s="116"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="51" t="s">
+        <v>119</v>
       </c>
       <c r="H51" s="12"/>
-      <c r="I51" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="J51" s="50">
+      <c r="I51" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="J51" s="47">
         <v>0</v>
       </c>
-      <c r="K51" s="46"/>
+      <c r="K51" s="43"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
     <row r="52" spans="1:14" ht="15" customHeight="1">
       <c r="A52" s="11"/>
-      <c r="B52" s="120"/>
-      <c r="C52" s="54" t="str">
+      <c r="B52" s="118"/>
+      <c r="C52" s="51" t="str">
         <f>master!C41</f>
         <v>デジタルブートキャンプの目的</v>
       </c>
-      <c r="D52" s="114"/>
-      <c r="E52" s="115"/>
-      <c r="F52" s="116"/>
-      <c r="G52" s="54" t="s">
-        <v>120</v>
+      <c r="D52" s="115"/>
+      <c r="E52" s="116"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="51" t="s">
+        <v>119</v>
       </c>
       <c r="H52" s="12"/>
-      <c r="I52" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J52" s="50">
+      <c r="I52" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K52" s="46"/>
+      <c r="K52" s="43"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="120"/>
-      <c r="C53" s="54" t="str">
+      <c r="B53" s="118"/>
+      <c r="C53" s="51" t="str">
         <f>master!C42</f>
         <v>まとめ</v>
       </c>
-      <c r="D53" s="114" t="s">
-        <v>167</v>
-      </c>
-      <c r="E53" s="115"/>
-      <c r="F53" s="116"/>
-      <c r="G53" s="54" t="s">
-        <v>125</v>
+      <c r="D53" s="115" t="s">
+        <v>166</v>
+      </c>
+      <c r="E53" s="116"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H53" s="12"/>
-      <c r="I53" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J53" s="50">
+      <c r="I53" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" s="47">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K53" s="46"/>
+      <c r="K53" s="43"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="120" t="str">
+      <c r="B54" s="118" t="str">
         <f>master!B43</f>
         <v>NTTデータの強み編</v>
       </c>
-      <c r="C54" s="54" t="str">
+      <c r="C54" s="51" t="str">
         <f>master!C43</f>
         <v>2025年の変動</v>
       </c>
-      <c r="D54" s="114" t="s">
-        <v>143</v>
-      </c>
-      <c r="E54" s="115"/>
-      <c r="F54" s="116"/>
-      <c r="G54" s="54" t="s">
-        <v>132</v>
+      <c r="D54" s="115" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" s="116"/>
+      <c r="F54" s="117"/>
+      <c r="G54" s="51" t="s">
+        <v>131</v>
       </c>
       <c r="H54" s="12"/>
-      <c r="I54" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J54" s="50">
+      <c r="I54" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" s="47">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K54" s="46"/>
+      <c r="K54" s="43"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" ht="50.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="120"/>
-      <c r="C55" s="54" t="str">
+      <c r="B55" s="118"/>
+      <c r="C55" s="51" t="str">
         <f>master!C44</f>
         <v>2025年の変動　AIエージェントの台頭</v>
       </c>
-      <c r="D55" s="114" t="s">
-        <v>173</v>
-      </c>
-      <c r="E55" s="115"/>
-      <c r="F55" s="116"/>
-      <c r="G55" s="54" t="s">
-        <v>125</v>
+      <c r="D55" s="115" t="s">
+        <v>172</v>
+      </c>
+      <c r="E55" s="116"/>
+      <c r="F55" s="117"/>
+      <c r="G55" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H55" s="12"/>
-      <c r="I55" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J55" s="50">
+      <c r="I55" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K55" s="46"/>
+      <c r="K55" s="43"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" ht="50.4">
       <c r="A56" s="11"/>
-      <c r="B56" s="120"/>
-      <c r="C56" s="54" t="str">
+      <c r="B56" s="118"/>
+      <c r="C56" s="51" t="str">
         <f>master!C45</f>
         <v>2025年の変動　Vibe Coding</v>
       </c>
-      <c r="D56" s="114" t="s">
-        <v>172</v>
-      </c>
-      <c r="E56" s="115"/>
-      <c r="F56" s="116"/>
-      <c r="G56" s="54" t="s">
-        <v>125</v>
+      <c r="D56" s="115" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="116"/>
+      <c r="F56" s="117"/>
+      <c r="G56" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H56" s="12"/>
-      <c r="I56" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J56" s="50">
+      <c r="I56" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K56" s="46"/>
+      <c r="K56" s="43"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="88.2">
       <c r="A57" s="11"/>
-      <c r="B57" s="120"/>
-      <c r="C57" s="54" t="str">
+      <c r="B57" s="118"/>
+      <c r="C57" s="51" t="str">
         <f>master!C46</f>
         <v>2025年の変動　Spec Driven Development</v>
       </c>
-      <c r="D57" s="114" t="s">
-        <v>201</v>
-      </c>
-      <c r="E57" s="115"/>
-      <c r="F57" s="116"/>
-      <c r="G57" s="54" t="s">
-        <v>130</v>
+      <c r="D57" s="115" t="s">
+        <v>200</v>
+      </c>
+      <c r="E57" s="116"/>
+      <c r="F57" s="117"/>
+      <c r="G57" s="51" t="s">
+        <v>129</v>
       </c>
       <c r="H57" s="12"/>
-      <c r="I57" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J57" s="50">
+      <c r="I57" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K57" s="46"/>
+      <c r="K57" s="43"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" ht="50.4">
       <c r="A58" s="11"/>
-      <c r="B58" s="120"/>
-      <c r="C58" s="54" t="str">
+      <c r="B58" s="118"/>
+      <c r="C58" s="51" t="str">
         <f>master!C47</f>
         <v>2025年の変動　ハーネスエンジニアリング</v>
       </c>
-      <c r="D58" s="114" t="s">
-        <v>202</v>
-      </c>
-      <c r="E58" s="115"/>
-      <c r="F58" s="116"/>
-      <c r="G58" s="54" t="s">
-        <v>125</v>
+      <c r="D58" s="115" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" s="116"/>
+      <c r="F58" s="117"/>
+      <c r="G58" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="H58" s="12"/>
-      <c r="I58" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J58" s="50">
+      <c r="I58" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K58" s="46"/>
+      <c r="K58" s="43"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" ht="75.599999999999994">
       <c r="A59" s="11"/>
-      <c r="B59" s="120"/>
-      <c r="C59" s="54" t="str">
+      <c r="B59" s="118"/>
+      <c r="C59" s="51" t="str">
         <f>master!C48</f>
         <v>2025年の変動　動向まとめ</v>
       </c>
-      <c r="D59" s="114" t="s">
-        <v>174</v>
-      </c>
-      <c r="E59" s="115"/>
-      <c r="F59" s="116"/>
-      <c r="G59" s="54" t="s">
-        <v>126</v>
+      <c r="D59" s="115" t="s">
+        <v>173</v>
+      </c>
+      <c r="E59" s="116"/>
+      <c r="F59" s="117"/>
+      <c r="G59" s="51" t="s">
+        <v>125</v>
       </c>
       <c r="H59" s="12"/>
-      <c r="I59" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J59" s="50">
+      <c r="I59" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K59" s="46"/>
+      <c r="K59" s="43"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" ht="113.4">
       <c r="A60" s="11"/>
-      <c r="B60" s="120"/>
-      <c r="C60" s="54" t="str">
+      <c r="B60" s="118"/>
+      <c r="C60" s="51" t="str">
         <f>master!C49</f>
         <v>2026年 ソフトウェア開発における課題とNTTDグループの強み</v>
       </c>
-      <c r="D60" s="114" t="s">
-        <v>176</v>
-      </c>
-      <c r="E60" s="115"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="54" t="s">
-        <v>127</v>
+      <c r="D60" s="115" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" s="116"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="51" t="s">
+        <v>126</v>
       </c>
       <c r="H60" s="12"/>
-      <c r="I60" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J60" s="50">
+      <c r="I60" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" s="47">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K60" s="46"/>
+      <c r="K60" s="43"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14" ht="37.799999999999997">
       <c r="A61" s="11"/>
-      <c r="B61" s="120"/>
-      <c r="C61" s="54" t="str">
+      <c r="B61" s="118"/>
+      <c r="C61" s="51" t="str">
         <f>master!C50</f>
         <v>2025年の変動</v>
       </c>
-      <c r="D61" s="114" t="s">
-        <v>177</v>
-      </c>
-      <c r="E61" s="115"/>
-      <c r="F61" s="116"/>
-      <c r="G61" s="54" t="s">
-        <v>124</v>
+      <c r="D61" s="115" t="s">
+        <v>176</v>
+      </c>
+      <c r="E61" s="116"/>
+      <c r="F61" s="117"/>
+      <c r="G61" s="51" t="s">
+        <v>123</v>
       </c>
       <c r="H61" s="12"/>
-      <c r="I61" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J61" s="50">
+      <c r="I61" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J61" s="47">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K61" s="46"/>
+      <c r="K61" s="43"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
     <row r="62" spans="1:14" ht="15" customHeight="1">
       <c r="A62" s="11"/>
-      <c r="B62" s="77" t="str">
+      <c r="B62" s="73" t="str">
         <f>master!B51</f>
         <v>デジタルソサエティ事業部取組紹介</v>
       </c>
-      <c r="C62" s="54" t="str">
+      <c r="C62" s="51" t="str">
         <f>master!C51</f>
         <v>ー</v>
       </c>
-      <c r="D62" s="114"/>
-      <c r="E62" s="115"/>
-      <c r="F62" s="116"/>
-      <c r="G62" s="54" t="s">
-        <v>120</v>
+      <c r="D62" s="115"/>
+      <c r="E62" s="116"/>
+      <c r="F62" s="117"/>
+      <c r="G62" s="51" t="s">
+        <v>119</v>
       </c>
       <c r="H62" s="12"/>
-      <c r="I62" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="J62" s="50">
+      <c r="I62" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="J62" s="47">
         <v>0</v>
       </c>
-      <c r="K62" s="46"/>
+      <c r="K62" s="43"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
     <row r="63" spans="1:14" ht="50.4" customHeight="1">
       <c r="A63" s="11"/>
-      <c r="B63" s="123" t="str">
+      <c r="B63" s="109" t="str">
         <f>master!B52</f>
         <v>ハンズオン編:ChatGPT</v>
       </c>
-      <c r="C63" s="72" t="str">
+      <c r="C63" s="68" t="str">
         <f>master!C52</f>
         <v>生成ＡＩハンズオン</v>
       </c>
-      <c r="D63" s="117"/>
-      <c r="E63" s="118"/>
-      <c r="F63" s="119"/>
-      <c r="G63" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="H63" s="73"/>
-      <c r="I63" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J63" s="75">
+      <c r="D63" s="112"/>
+      <c r="E63" s="113"/>
+      <c r="F63" s="114"/>
+      <c r="G63" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="H63" s="69"/>
+      <c r="I63" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K63" s="76"/>
+      <c r="K63" s="72"/>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="11"/>
-      <c r="B64" s="124"/>
-      <c r="C64" s="72" t="str">
+      <c r="B64" s="110"/>
+      <c r="C64" s="68" t="str">
         <f>master!C53</f>
         <v>ChatGPTの使い方（一般チャット）</v>
       </c>
-      <c r="D64" s="117"/>
-      <c r="E64" s="118"/>
-      <c r="F64" s="119"/>
-      <c r="G64" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="H64" s="73"/>
-      <c r="I64" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J64" s="75">
+      <c r="D64" s="112"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="114"/>
+      <c r="G64" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="H64" s="69"/>
+      <c r="I64" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K64" s="76"/>
+      <c r="K64" s="72"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
     <row r="65" spans="1:14" ht="50.4">
       <c r="A65" s="11"/>
-      <c r="B65" s="124"/>
-      <c r="C65" s="72" t="str">
+      <c r="B65" s="110"/>
+      <c r="C65" s="68" t="str">
         <f>master!C54</f>
         <v>プロンプトを入れてみる</v>
       </c>
-      <c r="D65" s="117" t="s">
-        <v>171</v>
-      </c>
-      <c r="E65" s="118"/>
-      <c r="F65" s="119"/>
-      <c r="G65" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="H65" s="73"/>
-      <c r="I65" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J65" s="75">
+      <c r="D65" s="112" t="s">
+        <v>170</v>
+      </c>
+      <c r="E65" s="113"/>
+      <c r="F65" s="114"/>
+      <c r="G65" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="H65" s="69"/>
+      <c r="I65" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" s="71">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K65" s="76"/>
+      <c r="K65" s="72"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
     <row r="66" spans="1:14" ht="63">
       <c r="A66" s="11"/>
-      <c r="B66" s="124"/>
-      <c r="C66" s="72" t="str">
+      <c r="B66" s="110"/>
+      <c r="C66" s="68" t="str">
         <f>master!C55</f>
         <v>ハンズオン例</v>
       </c>
-      <c r="D66" s="117" t="s">
-        <v>145</v>
-      </c>
-      <c r="E66" s="118"/>
-      <c r="F66" s="119"/>
-      <c r="G66" s="72" t="s">
-        <v>123</v>
-      </c>
-      <c r="H66" s="73"/>
-      <c r="I66" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J66" s="75">
+      <c r="D66" s="112" t="s">
+        <v>144</v>
+      </c>
+      <c r="E66" s="113"/>
+      <c r="F66" s="114"/>
+      <c r="G66" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="H66" s="69"/>
+      <c r="I66" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J66" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K66" s="76"/>
+      <c r="K66" s="72"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
     <row r="67" spans="1:14" ht="126">
       <c r="A67" s="11"/>
-      <c r="B67" s="124"/>
-      <c r="C67" s="72" t="str">
+      <c r="B67" s="110"/>
+      <c r="C67" s="68" t="str">
         <f>master!C56</f>
         <v>例１：【レポート作成】　佐々木社長の調査を行う</v>
       </c>
-      <c r="D67" s="117" t="s">
-        <v>168</v>
-      </c>
-      <c r="E67" s="118"/>
-      <c r="F67" s="119"/>
-      <c r="G67" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="H67" s="73"/>
-      <c r="I67" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J67" s="75">
+      <c r="D67" s="112" t="s">
+        <v>167</v>
+      </c>
+      <c r="E67" s="113"/>
+      <c r="F67" s="114"/>
+      <c r="G67" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="H67" s="69"/>
+      <c r="I67" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" s="71">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K67" s="76"/>
+      <c r="K67" s="72"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
     <row r="68" spans="1:14" ht="126" customHeight="1">
       <c r="A68" s="11"/>
-      <c r="B68" s="124"/>
-      <c r="C68" s="72" t="str">
+      <c r="B68" s="110"/>
+      <c r="C68" s="68" t="str">
         <f>master!C57</f>
         <v>例２：顧客提案向けの企画書を作りたい</v>
       </c>
-      <c r="D68" s="117" t="s">
-        <v>168</v>
-      </c>
-      <c r="E68" s="118"/>
-      <c r="F68" s="119"/>
-      <c r="G68" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="H68" s="73"/>
-      <c r="I68" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J68" s="75">
+      <c r="D68" s="112" t="s">
+        <v>167</v>
+      </c>
+      <c r="E68" s="113"/>
+      <c r="F68" s="114"/>
+      <c r="G68" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="H68" s="69"/>
+      <c r="I68" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J68" s="71">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K68" s="76"/>
+      <c r="K68" s="72"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
     <row r="69" spans="1:14" ht="126" customHeight="1">
       <c r="A69" s="11"/>
-      <c r="B69" s="124"/>
-      <c r="C69" s="72" t="str">
+      <c r="B69" s="110"/>
+      <c r="C69" s="68" t="str">
         <f>master!C58</f>
         <v>例３：１００本ノックを作ってみる</v>
       </c>
-      <c r="D69" s="117" t="s">
-        <v>168</v>
-      </c>
-      <c r="E69" s="118"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="H69" s="73"/>
-      <c r="I69" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J69" s="75">
+      <c r="D69" s="112" t="s">
+        <v>167</v>
+      </c>
+      <c r="E69" s="113"/>
+      <c r="F69" s="114"/>
+      <c r="G69" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="H69" s="69"/>
+      <c r="I69" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" s="71">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K69" s="76"/>
+      <c r="K69" s="72"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="11"/>
-      <c r="B70" s="125"/>
-      <c r="C70" s="72" t="str">
+      <c r="B70" s="111"/>
+      <c r="C70" s="68" t="str">
         <f>master!C59</f>
         <v>ChatGPT まとめ</v>
       </c>
-      <c r="D70" s="117"/>
-      <c r="E70" s="118"/>
-      <c r="F70" s="119"/>
-      <c r="G70" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="H70" s="73"/>
-      <c r="I70" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J70" s="75">
+      <c r="D70" s="112"/>
+      <c r="E70" s="113"/>
+      <c r="F70" s="114"/>
+      <c r="G70" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="H70" s="69"/>
+      <c r="I70" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J70" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K70" s="76"/>
+      <c r="K70" s="72"/>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
     <row r="71" spans="1:14" ht="15" customHeight="1">
       <c r="A71" s="11"/>
-      <c r="B71" s="123" t="str">
+      <c r="B71" s="109" t="str">
         <f>master!B60</f>
         <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
       </c>
-      <c r="C71" s="72" t="str">
+      <c r="C71" s="68" t="str">
         <f>master!C60</f>
         <v>生成ＡＩハンズオン</v>
       </c>
-      <c r="D71" s="117"/>
-      <c r="E71" s="118"/>
-      <c r="F71" s="119"/>
-      <c r="G71" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="H71" s="73"/>
-      <c r="I71" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J71" s="75">
+      <c r="D71" s="112"/>
+      <c r="E71" s="113"/>
+      <c r="F71" s="114"/>
+      <c r="G71" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="H71" s="69"/>
+      <c r="I71" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K71" s="76"/>
+      <c r="K71" s="72"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
     <row r="72" spans="1:14" ht="25.2">
       <c r="A72" s="11"/>
-      <c r="B72" s="124"/>
-      <c r="C72" s="72" t="str">
+      <c r="B72" s="110"/>
+      <c r="C72" s="68" t="str">
         <f>master!C61</f>
         <v>Visual Studio Code を開く</v>
       </c>
-      <c r="D72" s="117" t="s">
-        <v>169</v>
-      </c>
-      <c r="E72" s="118"/>
-      <c r="F72" s="119"/>
-      <c r="G72" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H72" s="73"/>
-      <c r="I72" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J72" s="75">
+      <c r="D72" s="112" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="113"/>
+      <c r="F72" s="114"/>
+      <c r="G72" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H72" s="69"/>
+      <c r="I72" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K72" s="76"/>
+      <c r="K72" s="72"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
     <row r="73" spans="1:14" ht="37.799999999999997">
       <c r="A73" s="11"/>
-      <c r="B73" s="124"/>
-      <c r="C73" s="72" t="str">
+      <c r="B73" s="110"/>
+      <c r="C73" s="68" t="str">
         <f>master!C62</f>
         <v>コード補完機能</v>
       </c>
-      <c r="D73" s="117" t="s">
-        <v>170</v>
-      </c>
-      <c r="E73" s="118"/>
-      <c r="F73" s="119"/>
-      <c r="G73" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H73" s="73"/>
-      <c r="I73" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J73" s="75">
+      <c r="D73" s="112" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" s="113"/>
+      <c r="F73" s="114"/>
+      <c r="G73" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="H73" s="69"/>
+      <c r="I73" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" s="71">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K73" s="76"/>
+      <c r="K73" s="72"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
     <row r="74" spans="1:14" ht="100.8">
       <c r="A74" s="11"/>
-      <c r="B74" s="124"/>
-      <c r="C74" s="72" t="str">
+      <c r="B74" s="110"/>
+      <c r="C74" s="68" t="str">
         <f>master!C63</f>
         <v>チャット機能</v>
       </c>
-      <c r="D74" s="117" t="s">
-        <v>203</v>
-      </c>
-      <c r="E74" s="118"/>
-      <c r="F74" s="119"/>
-      <c r="G74" s="72" t="s">
-        <v>141</v>
-      </c>
-      <c r="H74" s="73"/>
-      <c r="I74" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J74" s="75">
+      <c r="D74" s="112" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" s="113"/>
+      <c r="F74" s="114"/>
+      <c r="G74" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="H74" s="69"/>
+      <c r="I74" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" s="71">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K74" s="76"/>
+      <c r="K74" s="72"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
     <row r="75" spans="1:14" ht="15" customHeight="1">
       <c r="A75" s="11"/>
-      <c r="B75" s="124"/>
-      <c r="C75" s="72" t="str">
+      <c r="B75" s="110"/>
+      <c r="C75" s="68" t="str">
         <f>master!C64</f>
         <v>ChatGPT で 簡単なアプリやゲームを作ってみましょう</v>
       </c>
-      <c r="D75" s="117"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="119"/>
-      <c r="G75" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="H75" s="73"/>
-      <c r="I75" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J75" s="75">
+      <c r="D75" s="112"/>
+      <c r="E75" s="113"/>
+      <c r="F75" s="114"/>
+      <c r="G75" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="H75" s="69"/>
+      <c r="I75" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J75" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K75" s="76"/>
+      <c r="K75" s="72"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
     <row r="76" spans="1:14" ht="25.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="124"/>
-      <c r="C76" s="72" t="str">
+      <c r="B76" s="110"/>
+      <c r="C76" s="68" t="str">
         <f>master!C65</f>
         <v>例１　高級志向テトリス</v>
       </c>
-      <c r="D76" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E76" s="118"/>
-      <c r="F76" s="119"/>
-      <c r="G76" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H76" s="73"/>
-      <c r="I76" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J76" s="75">
+      <c r="D76" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E76" s="113"/>
+      <c r="F76" s="114"/>
+      <c r="G76" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H76" s="69"/>
+      <c r="I76" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K76" s="76"/>
+      <c r="K76" s="72"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" ht="25.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="124"/>
-      <c r="C77" s="72" t="str">
+      <c r="B77" s="110"/>
+      <c r="C77" s="68" t="str">
         <f>master!C66</f>
         <v>例）わくわく！にっぽんダーツの旅</v>
       </c>
-      <c r="D77" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E77" s="118"/>
-      <c r="F77" s="119"/>
-      <c r="G77" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H77" s="73"/>
-      <c r="I77" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J77" s="75">
+      <c r="D77" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E77" s="113"/>
+      <c r="F77" s="114"/>
+      <c r="G77" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H77" s="69"/>
+      <c r="I77" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J77" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K77" s="76"/>
+      <c r="K77" s="72"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
     <row r="78" spans="1:14" ht="25.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="124"/>
-      <c r="C78" s="72" t="str">
+      <c r="B78" s="110"/>
+      <c r="C78" s="68" t="str">
         <f>master!C67</f>
         <v>例）タスク管理ツール</v>
       </c>
-      <c r="D78" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E78" s="118"/>
-      <c r="F78" s="119"/>
-      <c r="G78" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H78" s="73"/>
-      <c r="I78" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J78" s="75">
+      <c r="D78" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E78" s="113"/>
+      <c r="F78" s="114"/>
+      <c r="G78" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H78" s="69"/>
+      <c r="I78" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K78" s="76"/>
+      <c r="K78" s="72"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
     <row r="79" spans="1:14" ht="126">
       <c r="A79" s="11"/>
-      <c r="B79" s="124"/>
-      <c r="C79" s="72"/>
-      <c r="D79" s="117" t="s">
-        <v>147</v>
-      </c>
-      <c r="E79" s="118"/>
-      <c r="F79" s="119"/>
-      <c r="G79" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="H79" s="73"/>
-      <c r="I79" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J79" s="75">
+      <c r="B79" s="110"/>
+      <c r="C79" s="68"/>
+      <c r="D79" s="112" t="s">
+        <v>146</v>
+      </c>
+      <c r="E79" s="113"/>
+      <c r="F79" s="114"/>
+      <c r="G79" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="H79" s="69"/>
+      <c r="I79" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" s="71">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K79" s="76"/>
+      <c r="K79" s="72"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
     </row>
     <row r="80" spans="1:14" ht="63">
       <c r="A80" s="11"/>
-      <c r="B80" s="124"/>
-      <c r="C80" s="72" t="str">
+      <c r="B80" s="110"/>
+      <c r="C80" s="68" t="str">
         <f>master!C68</f>
         <v>ディレクトリ作成とファイル配置</v>
       </c>
-      <c r="D80" s="117" t="s">
-        <v>148</v>
-      </c>
-      <c r="E80" s="118"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="72" t="s">
-        <v>123</v>
-      </c>
-      <c r="H80" s="73"/>
-      <c r="I80" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J80" s="75">
+      <c r="D80" s="112" t="s">
+        <v>147</v>
+      </c>
+      <c r="E80" s="113"/>
+      <c r="F80" s="114"/>
+      <c r="G80" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="H80" s="69"/>
+      <c r="I80" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" s="71">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K80" s="76"/>
+      <c r="K80" s="72"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" ht="25.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="124"/>
-      <c r="C81" s="72" t="str">
+      <c r="B81" s="110"/>
+      <c r="C81" s="68" t="str">
         <f>master!C69</f>
         <v>チャット機能：Aｓｋ</v>
       </c>
-      <c r="D81" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E81" s="118"/>
-      <c r="F81" s="119"/>
-      <c r="G81" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H81" s="73"/>
-      <c r="I81" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J81" s="75">
+      <c r="D81" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E81" s="113"/>
+      <c r="F81" s="114"/>
+      <c r="G81" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H81" s="69"/>
+      <c r="I81" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J81" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K81" s="76"/>
+      <c r="K81" s="72"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
       <c r="N81" s="6"/>
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="124"/>
-      <c r="C82" s="72" t="str">
+      <c r="B82" s="110"/>
+      <c r="C82" s="68" t="str">
         <f>master!C70</f>
         <v>Askモードについて</v>
       </c>
-      <c r="D82" s="117" t="s">
-        <v>175</v>
-      </c>
-      <c r="E82" s="118"/>
-      <c r="F82" s="119"/>
-      <c r="G82" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="H82" s="73"/>
-      <c r="I82" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J82" s="75">
+      <c r="D82" s="112" t="s">
+        <v>174</v>
+      </c>
+      <c r="E82" s="113"/>
+      <c r="F82" s="114"/>
+      <c r="G82" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="H82" s="69"/>
+      <c r="I82" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" s="71">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K82" s="76"/>
+      <c r="K82" s="72"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
     </row>
     <row r="83" spans="1:14" ht="25.2">
       <c r="A83" s="11"/>
-      <c r="B83" s="124"/>
-      <c r="C83" s="91" t="str">
+      <c r="B83" s="110"/>
+      <c r="C83" s="87" t="str">
         <f>master!C71</f>
         <v>実行例</v>
       </c>
-      <c r="D83" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E83" s="118"/>
-      <c r="F83" s="119"/>
-      <c r="G83" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H83" s="73"/>
-      <c r="I83" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J83" s="75">
+      <c r="D83" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E83" s="113"/>
+      <c r="F83" s="114"/>
+      <c r="G83" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H83" s="69"/>
+      <c r="I83" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" s="71">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K83" s="76"/>
+      <c r="K83" s="72"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
     <row r="84" spans="1:14" ht="37.799999999999997">
       <c r="A84" s="11"/>
-      <c r="B84" s="124"/>
-      <c r="C84" s="92"/>
-      <c r="D84" s="117" t="s">
-        <v>194</v>
-      </c>
-      <c r="E84" s="118"/>
-      <c r="F84" s="119"/>
-      <c r="G84" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H84" s="73"/>
-      <c r="I84" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J84" s="75">
+      <c r="B84" s="110"/>
+      <c r="C84" s="88"/>
+      <c r="D84" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="E84" s="113"/>
+      <c r="F84" s="114"/>
+      <c r="G84" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="H84" s="69"/>
+      <c r="I84" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" s="71">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K84" s="76"/>
+      <c r="K84" s="72"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
     </row>
     <row r="85" spans="1:14" ht="25.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="124"/>
-      <c r="C85" s="72" t="str">
+      <c r="B85" s="110"/>
+      <c r="C85" s="68" t="str">
         <f>master!C72</f>
         <v>Askモードまとめ</v>
       </c>
-      <c r="D85" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E85" s="118"/>
-      <c r="F85" s="119"/>
-      <c r="G85" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H85" s="73"/>
-      <c r="I85" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J85" s="75">
+      <c r="D85" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E85" s="113"/>
+      <c r="F85" s="114"/>
+      <c r="G85" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H85" s="69"/>
+      <c r="I85" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" s="71">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K85" s="76"/>
+      <c r="K85" s="72"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
     <row r="86" spans="1:14" ht="25.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="124"/>
-      <c r="C86" s="72" t="str">
+      <c r="B86" s="110"/>
+      <c r="C86" s="68" t="str">
         <f>master!C73</f>
         <v>チャット機能：Agent</v>
       </c>
-      <c r="D86" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E86" s="118"/>
-      <c r="F86" s="119"/>
-      <c r="G86" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H86" s="73"/>
-      <c r="I86" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J86" s="75">
+      <c r="D86" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E86" s="113"/>
+      <c r="F86" s="114"/>
+      <c r="G86" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H86" s="69"/>
+      <c r="I86" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" s="71">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K86" s="76"/>
+      <c r="K86" s="72"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
       <c r="N86" s="6"/>
     </row>
     <row r="87" spans="1:14" ht="25.2">
       <c r="A87" s="11"/>
-      <c r="B87" s="124"/>
-      <c r="C87" s="72" t="str">
+      <c r="B87" s="110"/>
+      <c r="C87" s="68" t="str">
         <f>master!C74</f>
         <v>Agentモード</v>
       </c>
-      <c r="D87" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E87" s="118"/>
-      <c r="F87" s="119"/>
-      <c r="G87" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H87" s="73"/>
-      <c r="I87" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J87" s="75">
+      <c r="D87" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E87" s="113"/>
+      <c r="F87" s="114"/>
+      <c r="G87" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H87" s="69"/>
+      <c r="I87" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="71">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K87" s="76"/>
+      <c r="K87" s="72"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
       <c r="N87" s="6"/>
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="124"/>
-      <c r="C88" s="72" t="str">
+      <c r="B88" s="110"/>
+      <c r="C88" s="68" t="str">
         <f>master!C75</f>
         <v>実行例</v>
       </c>
-      <c r="D88" s="117" t="s">
-        <v>175</v>
-      </c>
-      <c r="E88" s="118"/>
-      <c r="F88" s="119"/>
-      <c r="G88" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H88" s="73"/>
-      <c r="I88" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J88" s="75">
+      <c r="D88" s="112" t="s">
+        <v>174</v>
+      </c>
+      <c r="E88" s="113"/>
+      <c r="F88" s="114"/>
+      <c r="G88" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="H88" s="69"/>
+      <c r="I88" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" s="71">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K88" s="76"/>
+      <c r="K88" s="72"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="124"/>
-      <c r="C89" s="72" t="str">
+      <c r="B89" s="110"/>
+      <c r="C89" s="68" t="str">
         <f>master!C76</f>
         <v>READMEの内容を確認しましょう</v>
       </c>
-      <c r="D89" s="117" t="s">
-        <v>175</v>
-      </c>
-      <c r="E89" s="118"/>
-      <c r="F89" s="119"/>
-      <c r="G89" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H89" s="73"/>
-      <c r="I89" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J89" s="75">
+      <c r="D89" s="112" t="s">
+        <v>174</v>
+      </c>
+      <c r="E89" s="113"/>
+      <c r="F89" s="114"/>
+      <c r="G89" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="H89" s="69"/>
+      <c r="I89" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" s="71">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K89" s="76"/>
+      <c r="K89" s="72"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
     <row r="90" spans="1:14" ht="37.799999999999997">
       <c r="A90" s="11"/>
-      <c r="B90" s="124"/>
-      <c r="C90" s="91" t="str">
+      <c r="B90" s="110"/>
+      <c r="C90" s="87" t="str">
         <f>master!C77</f>
         <v>Changeログを作ってみましょう</v>
       </c>
-      <c r="D90" s="117" t="s">
-        <v>175</v>
-      </c>
-      <c r="E90" s="118"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H90" s="73"/>
-      <c r="I90" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J90" s="75">
+      <c r="D90" s="112" t="s">
+        <v>174</v>
+      </c>
+      <c r="E90" s="113"/>
+      <c r="F90" s="114"/>
+      <c r="G90" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="H90" s="69"/>
+      <c r="I90" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K90" s="76"/>
+      <c r="K90" s="72"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" ht="37.799999999999997">
       <c r="A91" s="11"/>
-      <c r="B91" s="124"/>
-      <c r="C91" s="92"/>
-      <c r="D91" s="117" t="s">
-        <v>190</v>
-      </c>
-      <c r="E91" s="118"/>
-      <c r="F91" s="119"/>
-      <c r="G91" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H91" s="73"/>
-      <c r="I91" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J91" s="75">
+      <c r="B91" s="110"/>
+      <c r="C91" s="88"/>
+      <c r="D91" s="112" t="s">
+        <v>189</v>
+      </c>
+      <c r="E91" s="113"/>
+      <c r="F91" s="114"/>
+      <c r="G91" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="H91" s="69"/>
+      <c r="I91" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" s="71">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K91" s="76"/>
+      <c r="K91" s="72"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
     <row r="92" spans="1:14" ht="25.2">
       <c r="A92" s="11"/>
-      <c r="B92" s="124"/>
-      <c r="C92" s="72" t="str">
+      <c r="B92" s="110"/>
+      <c r="C92" s="68" t="str">
         <f>master!C78</f>
         <v>チャット機能：Plan</v>
       </c>
-      <c r="D92" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E92" s="118"/>
-      <c r="F92" s="119"/>
-      <c r="G92" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H92" s="73"/>
-      <c r="I92" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J92" s="75">
+      <c r="D92" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E92" s="113"/>
+      <c r="F92" s="114"/>
+      <c r="G92" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H92" s="69"/>
+      <c r="I92" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" s="71">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K92" s="76"/>
+      <c r="K92" s="72"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
     <row r="93" spans="1:14" ht="37.799999999999997">
       <c r="A93" s="11"/>
-      <c r="B93" s="124"/>
-      <c r="C93" s="72" t="str">
+      <c r="B93" s="110"/>
+      <c r="C93" s="68" t="str">
         <f>master!C79</f>
         <v>Planモードで機能追加してみましょう</v>
       </c>
-      <c r="D93" s="117" t="s">
-        <v>175</v>
-      </c>
-      <c r="E93" s="118"/>
-      <c r="F93" s="119"/>
-      <c r="G93" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H93" s="73"/>
-      <c r="I93" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J93" s="75">
+      <c r="D93" s="112" t="s">
+        <v>174</v>
+      </c>
+      <c r="E93" s="113"/>
+      <c r="F93" s="114"/>
+      <c r="G93" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="H93" s="69"/>
+      <c r="I93" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" s="71">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K93" s="76"/>
+      <c r="K93" s="72"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
     </row>
     <row r="94" spans="1:14" ht="25.2">
       <c r="A94" s="11"/>
-      <c r="B94" s="124"/>
-      <c r="C94" s="72" t="str">
+      <c r="B94" s="110"/>
+      <c r="C94" s="68" t="str">
         <f>master!C80</f>
         <v>実行例</v>
       </c>
-      <c r="D94" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E94" s="118"/>
-      <c r="F94" s="119"/>
-      <c r="G94" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H94" s="73"/>
-      <c r="I94" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J94" s="75">
+      <c r="D94" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E94" s="113"/>
+      <c r="F94" s="114"/>
+      <c r="G94" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H94" s="69"/>
+      <c r="I94" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J94" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K94" s="76"/>
+      <c r="K94" s="72"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
     <row r="95" spans="1:14" ht="25.2">
       <c r="A95" s="11"/>
-      <c r="B95" s="124"/>
-      <c r="C95" s="91" t="str">
+      <c r="B95" s="110"/>
+      <c r="C95" s="87" t="str">
         <f>master!C81</f>
         <v>実行結果</v>
       </c>
-      <c r="D95" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E95" s="118"/>
-      <c r="F95" s="119"/>
-      <c r="G95" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H95" s="73"/>
-      <c r="I95" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J95" s="75">
+      <c r="D95" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E95" s="113"/>
+      <c r="F95" s="114"/>
+      <c r="G95" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H95" s="69"/>
+      <c r="I95" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" s="71">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K95" s="76"/>
+      <c r="K95" s="72"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
     <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="124"/>
-      <c r="C96" s="92"/>
-      <c r="D96" s="117" t="s">
-        <v>190</v>
-      </c>
-      <c r="E96" s="118"/>
-      <c r="F96" s="119"/>
-      <c r="G96" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="H96" s="73"/>
-      <c r="I96" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J96" s="75">
+      <c r="B96" s="110"/>
+      <c r="C96" s="88"/>
+      <c r="D96" s="112" t="s">
+        <v>189</v>
+      </c>
+      <c r="E96" s="113"/>
+      <c r="F96" s="114"/>
+      <c r="G96" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="H96" s="69"/>
+      <c r="I96" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J96" s="71">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K96" s="76"/>
+      <c r="K96" s="72"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
       <c r="N96" s="6"/>
     </row>
     <row r="97" spans="1:14" ht="25.2">
       <c r="A97" s="11"/>
-      <c r="B97" s="124"/>
-      <c r="C97" s="72" t="str">
+      <c r="B97" s="110"/>
+      <c r="C97" s="68" t="str">
         <f>master!C82</f>
         <v>Planモード＆Agentモードまとめ</v>
       </c>
-      <c r="D97" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="E97" s="118"/>
-      <c r="F97" s="119"/>
-      <c r="G97" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="H97" s="73"/>
-      <c r="I97" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J97" s="75">
+      <c r="D97" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E97" s="113"/>
+      <c r="F97" s="114"/>
+      <c r="G97" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="H97" s="69"/>
+      <c r="I97" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J97" s="71">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K97" s="76"/>
+      <c r="K97" s="72"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
     <row r="98" spans="1:14" ht="113.4">
       <c r="A98" s="11"/>
-      <c r="B98" s="88" t="str">
+      <c r="B98" s="84" t="str">
         <f>master!B83</f>
         <v>プレゼン</v>
       </c>
-      <c r="C98" s="72" t="str">
+      <c r="C98" s="68" t="str">
         <f>master!C83</f>
         <v>開発したゲームやアプリをプレゼン</v>
       </c>
-      <c r="D98" s="117" t="s">
-        <v>189</v>
-      </c>
-      <c r="E98" s="118"/>
-      <c r="F98" s="119"/>
-      <c r="G98" s="72" t="s">
-        <v>127</v>
-      </c>
-      <c r="H98" s="73"/>
-      <c r="I98" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="J98" s="75">
+      <c r="D98" s="112" t="s">
+        <v>188</v>
+      </c>
+      <c r="E98" s="113"/>
+      <c r="F98" s="114"/>
+      <c r="G98" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="H98" s="69"/>
+      <c r="I98" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J98" s="71">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K98" s="76" t="s">
-        <v>186</v>
+      <c r="K98" s="72" t="s">
+        <v>185</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
     </row>
     <row r="99" spans="1:14" ht="15" customHeight="1">
-      <c r="J99" s="49"/>
+      <c r="J99" s="46"/>
     </row>
     <row r="100" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="104">
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B15:B25"/>
+    <mergeCell ref="B26:B34"/>
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="B40:B53"/>
+    <mergeCell ref="B54:B61"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B63:B70"/>
     <mergeCell ref="B71:B97"/>
@@ -6823,85 +6881,6 @@
     <mergeCell ref="D81:F81"/>
     <mergeCell ref="D82:F82"/>
     <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="B40:B53"/>
-    <mergeCell ref="B54:B61"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="B15:B25"/>
-    <mergeCell ref="B26:B34"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="K11:K12"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6934,450 +6913,450 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="89" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="C17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="C23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="C31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="C35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="C40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="B43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="C44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="C49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="C50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="B51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="B52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="C53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="2:3">
       <c r="C54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="2:3">
       <c r="C55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="2:3">
       <c r="C56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="2:3">
       <c r="C57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="2:3">
       <c r="C58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="2:3">
       <c r="C59" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="2:3">
       <c r="B60" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="2:3">
       <c r="C61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="2:3">
       <c r="C62" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="2:3">
       <c r="C63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="2:3">
       <c r="C64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="3:3">
       <c r="C65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="3:3">
       <c r="C66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="3:3">
       <c r="C67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="3:3">
       <c r="C68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="3:3">
       <c r="C69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="3:3">
       <c r="C70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="3:3">
       <c r="C72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="3:3">
       <c r="C73" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" spans="3:3">
       <c r="C74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="3:3">
       <c r="C75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="3:3">
       <c r="C76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="3:3">
       <c r="C77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="3:3">
       <c r="C78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="3:3">
       <c r="C79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="3:3">
       <c r="C80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81" spans="2:3">
       <c r="C81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="2:3">
       <c r="C82" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="B83" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C83" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/IG/AI Native-生成AI_IG.xlsx
+++ b/IG/AI Native-生成AI_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D90175C-23DA-42A7-850E-EFB3C2207669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C09084C-BF9C-4FF5-9386-ED8F2B890F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（1日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$99</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$98</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -63,7 +63,7 @@
     <author>ishida</author>
   </authors>
   <commentList>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="206">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -2401,6 +2401,22 @@
     </rPh>
     <rPh sb="26" eb="27">
       <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>生成AIを利用してあらかじめ自己紹介文を作成しておく。</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>ジコショウカイブン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2830,7 +2846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3101,6 +3117,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3152,6 +3171,36 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -3166,45 +3215,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3578,15 +3588,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="91" t="str">
+      <c r="B2" s="92" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-生成AI_IG」</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3599,10 +3609,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="93"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3610,18 +3620,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="96"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="96"/>
+      <c r="C7" s="97"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="24"/>
@@ -3681,7 +3691,7 @@
         <f>master!B4</f>
         <v>導入編</v>
       </c>
-      <c r="F14" s="90"/>
+      <c r="F14" s="91"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
@@ -3690,7 +3700,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="78"/>
-      <c r="F15" s="90"/>
+      <c r="F15" s="91"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -3699,7 +3709,7 @@
       </c>
       <c r="B16" s="41"/>
       <c r="C16" s="79"/>
-      <c r="F16" s="90"/>
+      <c r="F16" s="91"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
@@ -3711,14 +3721,14 @@
         <f>master!B15</f>
         <v>復習編</v>
       </c>
-      <c r="F17" s="90"/>
+      <c r="F17" s="91"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="38"/>
       <c r="B18" s="41"/>
       <c r="C18" s="79"/>
-      <c r="F18" s="90"/>
+      <c r="F18" s="91"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3730,7 +3740,7 @@
         <f>master!B24</f>
         <v>AI-Native研修の目的</v>
       </c>
-      <c r="F19" s="90"/>
+      <c r="F19" s="91"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
@@ -3744,14 +3754,14 @@
         <f>master!B29</f>
         <v>キャリア編</v>
       </c>
-      <c r="F20" s="90"/>
+      <c r="F20" s="91"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="57"/>
       <c r="B21" s="59"/>
       <c r="C21" s="79"/>
-      <c r="F21" s="90"/>
+      <c r="F21" s="91"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3804,7 +3814,7 @@
         <v>0.5625</v>
       </c>
       <c r="C26" s="79"/>
-      <c r="F26" s="90"/>
+      <c r="F26" s="91"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -3817,7 +3827,7 @@
         <f>master!B43</f>
         <v>NTTデータの強み編</v>
       </c>
-      <c r="F27" s="90"/>
+      <c r="F27" s="91"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3827,7 +3837,7 @@
       </c>
       <c r="B28" s="41"/>
       <c r="C28" s="79"/>
-      <c r="F28" s="90"/>
+      <c r="F28" s="91"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -3841,7 +3851,7 @@
       </c>
       <c r="D29" s="56"/>
       <c r="E29" s="53"/>
-      <c r="F29" s="90"/>
+      <c r="F29" s="91"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -3850,7 +3860,7 @@
       <c r="C30" s="60"/>
       <c r="D30" s="56"/>
       <c r="E30" s="53"/>
-      <c r="F30" s="90"/>
+      <c r="F30" s="91"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
@@ -3859,7 +3869,7 @@
       <c r="C31" s="60"/>
       <c r="D31" s="56"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="90"/>
+      <c r="F31" s="91"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
@@ -3870,7 +3880,7 @@
       <c r="C32" s="60"/>
       <c r="D32" s="56"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="90"/>
+      <c r="F32" s="91"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
@@ -3879,7 +3889,7 @@
       <c r="C33" s="60"/>
       <c r="D33" s="56"/>
       <c r="E33" s="53"/>
-      <c r="F33" s="90"/>
+      <c r="F33" s="91"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
@@ -3893,7 +3903,7 @@
       </c>
       <c r="D34" s="56"/>
       <c r="E34" s="53"/>
-      <c r="F34" s="90"/>
+      <c r="F34" s="91"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
@@ -3902,7 +3912,7 @@
       <c r="C35" s="60"/>
       <c r="D35" s="56"/>
       <c r="E35" s="53"/>
-      <c r="F35" s="90"/>
+      <c r="F35" s="91"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3913,7 +3923,7 @@
       <c r="C36" s="60"/>
       <c r="D36" s="56"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="90"/>
+      <c r="F36" s="91"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
@@ -3922,7 +3932,7 @@
       <c r="C37" s="60"/>
       <c r="D37" s="56"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="90"/>
+      <c r="F37" s="91"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
@@ -3931,7 +3941,7 @@
       <c r="C38" s="60"/>
       <c r="D38" s="56"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="90"/>
+      <c r="F38" s="91"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
@@ -3940,7 +3950,7 @@
       <c r="C39" s="64"/>
       <c r="D39" s="56"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="90"/>
+      <c r="F39" s="91"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3955,7 +3965,7 @@
       </c>
       <c r="D40" s="56"/>
       <c r="E40" s="53"/>
-      <c r="F40" s="90"/>
+      <c r="F40" s="91"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -3964,7 +3974,7 @@
       <c r="C41" s="60"/>
       <c r="D41" s="58"/>
       <c r="E41" s="54"/>
-      <c r="F41" s="90"/>
+      <c r="F41" s="91"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
@@ -3973,7 +3983,7 @@
       <c r="C42" s="61"/>
       <c r="D42" s="56"/>
       <c r="E42" s="54"/>
-      <c r="F42" s="90"/>
+      <c r="F42" s="91"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
@@ -4060,10 +4070,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="102"/>
+      <c r="C4" s="103"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4074,16 +4084,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4098,10 +4108,10 @@
       <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="104"/>
+      <c r="E7" s="105"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -4133,46 +4143,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98" t="s">
+      <c r="B10" s="99"/>
+      <c r="C10" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98" t="s">
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="105" t="s">
+      <c r="H10" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="97" t="s">
+      <c r="I10" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97" t="s">
+      <c r="J10" s="98"/>
+      <c r="K10" s="98" t="s">
         <v>31</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="106"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="107"/>
       <c r="I11" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="98"/>
+      <c r="K11" s="99"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -4181,12 +4191,12 @@
       <c r="C12" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="99" t="s">
+      <c r="D12" s="100" t="s">
         <v>180</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="122" t="s">
+      <c r="E12" s="101"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="90" t="s">
         <v>181</v>
       </c>
       <c r="H12" s="20"/>
@@ -4234,7 +4244,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N100"/>
+  <dimension ref="A2:N99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -4284,12 +4294,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4300,243 +4310,258 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
+      <c r="B5" s="110" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
-    <row r="6" spans="1:14" ht="32.4" customHeight="1">
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="30"/>
+    <row r="6" spans="1:14">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="B7" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="105"/>
+      <c r="F7" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="48"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="B8" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="104" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="104"/>
-      <c r="F8" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="48"/>
-      <c r="J8" s="6"/>
+      <c r="B8" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="44"/>
+      <c r="F8" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>19</v>
+      </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14">
-      <c r="B9" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="123" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="124"/>
-      <c r="F9" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="11" spans="1:14" ht="24" customHeight="1">
+    <row r="10" spans="1:14" ht="24" customHeight="1">
+      <c r="A10" s="10"/>
+      <c r="B10" s="99" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="99" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="99" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="98" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="108" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="109"/>
+      <c r="K10" s="98" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="10"/>
-      <c r="B11" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="98" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="98" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="97" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="119" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="120"/>
-      <c r="K11" s="97" t="s">
-        <v>33</v>
-      </c>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="99"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" ht="75.599999999999994">
       <c r="A12" s="10"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="97"/>
-      <c r="I12" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="98"/>
+      <c r="B12" s="118" t="str">
+        <f>master!B3</f>
+        <v>自己紹介</v>
+      </c>
+      <c r="C12" s="51" t="str">
+        <f>master!C3</f>
+        <v>ー</v>
+      </c>
+      <c r="D12" s="111" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="47">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K12" s="43"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" ht="75.599999999999994">
+    <row r="13" spans="1:14" ht="88.2">
       <c r="A13" s="10"/>
-      <c r="B13" s="107" t="str">
-        <f>master!B3</f>
-        <v>自己紹介</v>
-      </c>
-      <c r="C13" s="51" t="str">
-        <f>master!C3</f>
-        <v>ー</v>
-      </c>
-      <c r="D13" s="115" t="s">
-        <v>177</v>
-      </c>
-      <c r="E13" s="116"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="47">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K13" s="43"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="114" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="115"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="69"/>
+      <c r="I13" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="71">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K13" s="72"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="88.2">
+    <row r="14" spans="1:14" ht="138.6">
       <c r="A14" s="10"/>
-      <c r="B14" s="108"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="112" t="s">
-        <v>179</v>
-      </c>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" s="69"/>
-      <c r="I14" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="71">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K14" s="72"/>
+      <c r="B14" s="117" t="str">
+        <f>master!B4</f>
+        <v>導入編</v>
+      </c>
+      <c r="C14" s="51" t="str">
+        <f>master!C4</f>
+        <v>あなたはもう生成ＡＩを使っていますか？</v>
+      </c>
+      <c r="D14" s="111" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="47">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K14" s="43"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" ht="138.6">
-      <c r="A15" s="10"/>
-      <c r="B15" s="118" t="str">
-        <f>master!B4</f>
-        <v>導入編</v>
-      </c>
+    <row r="15" spans="1:14" ht="75.599999999999994">
+      <c r="A15" s="11"/>
+      <c r="B15" s="117"/>
       <c r="C15" s="51" t="str">
-        <f>master!C4</f>
-        <v>あなたはもう生成ＡＩを使っていますか？</v>
-      </c>
-      <c r="D15" s="115" t="s">
-        <v>152</v>
-      </c>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117"/>
+        <f>master!C5</f>
+        <v>FYI：システム開発SaaS　「GEAR.indigo」</v>
+      </c>
+      <c r="D15" s="111" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="112"/>
+      <c r="F15" s="113"/>
       <c r="G15" s="51" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K15" s="43"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="75.599999999999994">
+    <row r="16" spans="1:14" ht="37.799999999999997">
       <c r="A16" s="11"/>
-      <c r="B16" s="118"/>
+      <c r="B16" s="117"/>
       <c r="C16" s="51" t="str">
-        <f>master!C5</f>
-        <v>FYI：システム開発SaaS　「GEAR.indigo」</v>
-      </c>
-      <c r="D16" s="115" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="116"/>
-      <c r="F16" s="117"/>
+        <f>master!C6</f>
+        <v>FYI：GEAR.indigo　「業務要件一覧」</v>
+      </c>
+      <c r="D16" s="111" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="112"/>
+      <c r="F16" s="113"/>
       <c r="G16" s="51" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J16" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K16" s="43"/>
       <c r="L16" s="6"/>
@@ -4545,16 +4570,16 @@
     </row>
     <row r="17" spans="1:14" ht="37.799999999999997">
       <c r="A17" s="11"/>
-      <c r="B17" s="118"/>
+      <c r="B17" s="117"/>
       <c r="C17" s="51" t="str">
-        <f>master!C6</f>
-        <v>FYI：GEAR.indigo　「業務要件一覧」</v>
-      </c>
-      <c r="D17" s="115" t="s">
-        <v>154</v>
-      </c>
-      <c r="E17" s="116"/>
-      <c r="F17" s="117"/>
+        <f>master!C7</f>
+        <v>FYI：GEAR.indigo　「システム化業務フロー」</v>
+      </c>
+      <c r="D17" s="111" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="112"/>
+      <c r="F17" s="113"/>
       <c r="G17" s="51" t="s">
         <v>123</v>
       </c>
@@ -4572,16 +4597,16 @@
     </row>
     <row r="18" spans="1:14" ht="37.799999999999997">
       <c r="A18" s="11"/>
-      <c r="B18" s="118"/>
+      <c r="B18" s="117"/>
       <c r="C18" s="51" t="str">
-        <f>master!C7</f>
-        <v>FYI：GEAR.indigo　「システム化業務フロー」</v>
-      </c>
-      <c r="D18" s="115" t="s">
-        <v>155</v>
-      </c>
-      <c r="E18" s="116"/>
-      <c r="F18" s="117"/>
+        <f>master!C8</f>
+        <v>FYI：GEAR.indigo　「テーブル定義書」</v>
+      </c>
+      <c r="D18" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" s="112"/>
+      <c r="F18" s="113"/>
       <c r="G18" s="51" t="s">
         <v>123</v>
       </c>
@@ -4599,16 +4624,16 @@
     </row>
     <row r="19" spans="1:14" ht="37.799999999999997">
       <c r="A19" s="11"/>
-      <c r="B19" s="118"/>
+      <c r="B19" s="117"/>
       <c r="C19" s="51" t="str">
-        <f>master!C8</f>
-        <v>FYI：GEAR.indigo　「テーブル定義書」</v>
-      </c>
-      <c r="D19" s="115" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="116"/>
-      <c r="F19" s="117"/>
+        <f>master!C9</f>
+        <v>FYI：GEAR.indigo　「画面定義書」</v>
+      </c>
+      <c r="D19" s="111" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="112"/>
+      <c r="F19" s="113"/>
       <c r="G19" s="51" t="s">
         <v>123</v>
       </c>
@@ -4624,47 +4649,47 @@
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="37.799999999999997">
+    <row r="20" spans="1:14" ht="50.4">
       <c r="A20" s="11"/>
-      <c r="B20" s="118"/>
+      <c r="B20" s="117"/>
       <c r="C20" s="51" t="str">
-        <f>master!C9</f>
-        <v>FYI：GEAR.indigo　「画面定義書」</v>
-      </c>
-      <c r="D20" s="115" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="116"/>
-      <c r="F20" s="117"/>
+        <f>master!C10</f>
+        <v>GEAR.indigo が （いずれ）見せてくれるもの</v>
+      </c>
+      <c r="D20" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="113"/>
       <c r="G20" s="51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="47">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K20" s="43"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="50.4">
+    <row r="21" spans="1:14" ht="37.799999999999997">
       <c r="A21" s="11"/>
-      <c r="B21" s="118"/>
+      <c r="B21" s="117"/>
       <c r="C21" s="51" t="str">
-        <f>master!C10</f>
-        <v>GEAR.indigo が （いずれ）見せてくれるもの</v>
-      </c>
-      <c r="D21" s="115" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" s="116"/>
-      <c r="F21" s="117"/>
+        <f>master!C11</f>
+        <v>あなたはどちらになりたいですか？</v>
+      </c>
+      <c r="D21" s="111" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="112"/>
+      <c r="F21" s="113"/>
       <c r="G21" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="49" t="s">
@@ -4680,16 +4705,16 @@
     </row>
     <row r="22" spans="1:14" ht="37.799999999999997">
       <c r="A22" s="11"/>
-      <c r="B22" s="118"/>
+      <c r="B22" s="117"/>
       <c r="C22" s="51" t="str">
-        <f>master!C11</f>
-        <v>あなたはどちらになりたいですか？</v>
-      </c>
-      <c r="D22" s="115" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" s="116"/>
-      <c r="F22" s="117"/>
+        <f>master!C12</f>
+        <v>いま、生成AIができること　（システム開発関連）</v>
+      </c>
+      <c r="D22" s="111" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="112"/>
+      <c r="F22" s="113"/>
       <c r="G22" s="51" t="s">
         <v>123</v>
       </c>
@@ -4698,27 +4723,27 @@
         <v>25</v>
       </c>
       <c r="J22" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K22" s="43"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="37.799999999999997">
+    <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="118"/>
+      <c r="B23" s="117"/>
       <c r="C23" s="51" t="str">
-        <f>master!C12</f>
-        <v>いま、生成AIができること　（システム開発関連）</v>
-      </c>
-      <c r="D23" s="115" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" s="116"/>
-      <c r="F23" s="117"/>
+        <f>master!C13</f>
+        <v>いま、生成ＡＩができないこと</v>
+      </c>
+      <c r="D23" s="111" t="s">
+        <v>203</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="113"/>
       <c r="G23" s="51" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="49" t="s">
@@ -4732,20 +4757,20 @@
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="75.599999999999994">
+    <row r="24" spans="1:14" ht="226.8">
       <c r="A24" s="11"/>
-      <c r="B24" s="118"/>
+      <c r="B24" s="117"/>
       <c r="C24" s="51" t="str">
-        <f>master!C13</f>
-        <v>いま、生成ＡＩができないこと</v>
-      </c>
-      <c r="D24" s="115" t="s">
-        <v>203</v>
-      </c>
-      <c r="E24" s="116"/>
-      <c r="F24" s="117"/>
+        <f>master!C14</f>
+        <v>生成ＡＩを使う心得８条</v>
+      </c>
+      <c r="D24" s="111" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="113"/>
       <c r="G24" s="51" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="49" t="s">
@@ -4759,48 +4784,50 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="226.8">
+    <row r="25" spans="1:14" ht="25.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="118"/>
+      <c r="B25" s="117" t="str">
+        <f>master!B15</f>
+        <v>復習編</v>
+      </c>
       <c r="C25" s="51" t="str">
-        <f>master!C14</f>
-        <v>生成ＡＩを使う心得８条</v>
-      </c>
-      <c r="D25" s="115" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="116"/>
-      <c r="F25" s="117"/>
+        <f>master!C15</f>
+        <v>NTTDATAが目指す方向性</v>
+      </c>
+      <c r="D25" s="111" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" s="112"/>
+      <c r="F25" s="113"/>
       <c r="G25" s="51" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J25" s="47">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K25" s="43"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>195</v>
+      </c>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
     <row r="26" spans="1:14" ht="25.2">
       <c r="A26" s="11"/>
-      <c r="B26" s="118" t="str">
-        <f>master!B15</f>
-        <v>復習編</v>
-      </c>
+      <c r="B26" s="117"/>
       <c r="C26" s="51" t="str">
-        <f>master!C15</f>
-        <v>NTTDATAが目指す方向性</v>
-      </c>
-      <c r="D26" s="115" t="s">
+        <f>master!C16</f>
+        <v>NTTデータ新入社員向け生成AI基礎講座</v>
+      </c>
+      <c r="D26" s="111" t="s">
         <v>204</v>
       </c>
-      <c r="E26" s="116"/>
-      <c r="F26" s="117"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="113"/>
       <c r="G26" s="51" t="s">
         <v>131</v>
       </c>
@@ -4820,16 +4847,16 @@
     </row>
     <row r="27" spans="1:14" ht="25.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="118"/>
+      <c r="B27" s="117"/>
       <c r="C27" s="51" t="str">
-        <f>master!C16</f>
-        <v>NTTデータ新入社員向け生成AI基礎講座</v>
-      </c>
-      <c r="D27" s="115" t="s">
-        <v>204</v>
-      </c>
-      <c r="E27" s="116"/>
-      <c r="F27" s="117"/>
+        <f>master!C17</f>
+        <v>プロンプト設計の基本</v>
+      </c>
+      <c r="D27" s="111" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="112"/>
+      <c r="F27" s="113"/>
       <c r="G27" s="51" t="s">
         <v>131</v>
       </c>
@@ -4838,108 +4865,106 @@
         <v>25</v>
       </c>
       <c r="J27" s="47">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K27" s="43" t="s">
-        <v>195</v>
-      </c>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K27" s="43"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="25.2">
+    <row r="28" spans="1:14" ht="75.599999999999994">
       <c r="A28" s="11"/>
-      <c r="B28" s="118"/>
+      <c r="B28" s="117"/>
       <c r="C28" s="51" t="str">
-        <f>master!C17</f>
-        <v>プロンプト設計の基本</v>
-      </c>
-      <c r="D28" s="115" t="s">
-        <v>148</v>
-      </c>
-      <c r="E28" s="116"/>
-      <c r="F28" s="117"/>
+        <f>master!C18</f>
+        <v>プロンプト設計の基本を踏まえた構造型プロンプト</v>
+      </c>
+      <c r="D28" s="111" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" s="112"/>
+      <c r="F28" s="113"/>
       <c r="G28" s="51" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J28" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K28" s="43"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="75.599999999999994">
+    <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="11"/>
-      <c r="B29" s="118"/>
+      <c r="B29" s="117"/>
       <c r="C29" s="51" t="str">
-        <f>master!C18</f>
-        <v>プロンプト設計の基本を踏まえた構造型プロンプト</v>
-      </c>
-      <c r="D29" s="115" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" s="116"/>
-      <c r="F29" s="117"/>
+        <f>master!C19</f>
+        <v>本セクションで学ぶこと</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="113"/>
       <c r="G29" s="51" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J29" s="47">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K29" s="43"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1">
+    <row r="30" spans="1:14" ht="50.4">
       <c r="A30" s="11"/>
-      <c r="B30" s="118"/>
+      <c r="B30" s="117"/>
       <c r="C30" s="51" t="str">
-        <f>master!C19</f>
-        <v>本セクションで学ぶこと</v>
-      </c>
-      <c r="D30" s="115"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="117"/>
+        <f>master!C20</f>
+        <v>エージェントAIとは何か？</v>
+      </c>
+      <c r="D30" s="111" t="s">
+        <v>158</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="113"/>
       <c r="G30" s="51" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J30" s="47">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K30" s="43"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="50.4">
+    <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="118"/>
+      <c r="B31" s="117"/>
       <c r="C31" s="51" t="str">
-        <f>master!C20</f>
-        <v>エージェントAIとは何か？</v>
-      </c>
-      <c r="D31" s="115" t="s">
-        <v>158</v>
-      </c>
-      <c r="E31" s="116"/>
-      <c r="F31" s="117"/>
+        <f>master!C21</f>
+        <v>エージェントの処理</v>
+      </c>
+      <c r="D31" s="111" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="112"/>
+      <c r="F31" s="113"/>
       <c r="G31" s="51" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="49" t="s">
@@ -4953,27 +4978,27 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="25.2">
+    <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="118"/>
+      <c r="B32" s="117"/>
       <c r="C32" s="51" t="str">
-        <f>master!C21</f>
-        <v>エージェントの処理</v>
-      </c>
-      <c r="D32" s="115" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="116"/>
-      <c r="F32" s="117"/>
+        <f>master!C22</f>
+        <v>AIエージェントのアーキテクチャ</v>
+      </c>
+      <c r="D32" s="111" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="112"/>
+      <c r="F32" s="113"/>
       <c r="G32" s="51" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J32" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K32" s="43"/>
       <c r="L32" s="6"/>
@@ -4982,16 +5007,16 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="118"/>
+      <c r="B33" s="117"/>
       <c r="C33" s="51" t="str">
-        <f>master!C22</f>
-        <v>AIエージェントのアーキテクチャ</v>
-      </c>
-      <c r="D33" s="115" t="s">
-        <v>136</v>
-      </c>
-      <c r="E33" s="116"/>
-      <c r="F33" s="117"/>
+        <f>master!C23</f>
+        <v>AIの強みを生かすポイント</v>
+      </c>
+      <c r="D33" s="111" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="112"/>
+      <c r="F33" s="113"/>
       <c r="G33" s="51" t="s">
         <v>123</v>
       </c>
@@ -5000,109 +5025,109 @@
         <v>25</v>
       </c>
       <c r="J33" s="47">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K33" s="43"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14" ht="37.799999999999997">
+    <row r="34" spans="1:14">
       <c r="A34" s="11"/>
-      <c r="B34" s="118"/>
+      <c r="B34" s="117" t="str">
+        <f>master!B24</f>
+        <v>AI-Native研修の目的</v>
+      </c>
       <c r="C34" s="51" t="str">
-        <f>master!C23</f>
-        <v>AIの強みを生かすポイント</v>
-      </c>
-      <c r="D34" s="115" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="116"/>
-      <c r="F34" s="117"/>
+        <f>master!C24</f>
+        <v>1.研修概要</v>
+      </c>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="113"/>
       <c r="G34" s="51" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="49" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="J34" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>0</v>
       </c>
       <c r="K34" s="43"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" ht="25.2">
       <c r="A35" s="11"/>
-      <c r="B35" s="118" t="str">
-        <f>master!B24</f>
-        <v>AI-Native研修の目的</v>
-      </c>
+      <c r="B35" s="117"/>
       <c r="C35" s="51" t="str">
-        <f>master!C24</f>
-        <v>1.研修概要</v>
-      </c>
-      <c r="D35" s="115"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="117"/>
+        <f>master!C25</f>
+        <v>2-1　背景目的</v>
+      </c>
+      <c r="D35" s="111" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="113"/>
       <c r="G35" s="51" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="49" t="s">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="J35" s="47">
-        <v>0</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K35" s="43"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="25.2">
+    <row r="36" spans="1:14" ht="151.19999999999999">
       <c r="A36" s="11"/>
-      <c r="B36" s="118"/>
+      <c r="B36" s="117"/>
       <c r="C36" s="51" t="str">
-        <f>master!C25</f>
-        <v>2-1　背景目的</v>
-      </c>
-      <c r="D36" s="115" t="s">
-        <v>138</v>
-      </c>
-      <c r="E36" s="116"/>
-      <c r="F36" s="117"/>
+        <f>master!C26</f>
+        <v>2-3　研修のゴールと獲得可能な経験</v>
+      </c>
+      <c r="D36" s="111" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="112"/>
+      <c r="F36" s="113"/>
       <c r="G36" s="51" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J36" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K36" s="43"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="151.19999999999999">
+    <row r="37" spans="1:14" ht="37.799999999999997">
       <c r="A37" s="11"/>
-      <c r="B37" s="118"/>
+      <c r="B37" s="117"/>
       <c r="C37" s="51" t="str">
-        <f>master!C26</f>
-        <v>2-3　研修のゴールと獲得可能な経験</v>
-      </c>
-      <c r="D37" s="115" t="s">
-        <v>197</v>
-      </c>
-      <c r="E37" s="116"/>
-      <c r="F37" s="117"/>
+        <f>master!C27</f>
+        <v>AIエージェントを用いたシステム開発タスクの実行の大まかな流れ</v>
+      </c>
+      <c r="D37" s="111" t="s">
+        <v>151</v>
+      </c>
+      <c r="E37" s="112"/>
+      <c r="F37" s="113"/>
       <c r="G37" s="51" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="49" t="s">
@@ -5118,16 +5143,16 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="118"/>
+      <c r="B38" s="117"/>
       <c r="C38" s="51" t="str">
-        <f>master!C27</f>
-        <v>AIエージェントを用いたシステム開発タスクの実行の大まかな流れ</v>
-      </c>
-      <c r="D38" s="115" t="s">
-        <v>151</v>
-      </c>
-      <c r="E38" s="116"/>
-      <c r="F38" s="117"/>
+        <f>master!C28</f>
+        <v>学ぶ範囲</v>
+      </c>
+      <c r="D38" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" s="112"/>
+      <c r="F38" s="113"/>
       <c r="G38" s="51" t="s">
         <v>123</v>
       </c>
@@ -5143,50 +5168,52 @@
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="37.799999999999997">
+    <row r="39" spans="1:14" ht="50.4">
       <c r="A39" s="11"/>
-      <c r="B39" s="118"/>
+      <c r="B39" s="117" t="str">
+        <f>master!B29</f>
+        <v>キャリア編</v>
+      </c>
       <c r="C39" s="51" t="str">
-        <f>master!C28</f>
-        <v>学ぶ範囲</v>
-      </c>
-      <c r="D39" s="115" t="s">
-        <v>159</v>
-      </c>
-      <c r="E39" s="116"/>
-      <c r="F39" s="117"/>
+        <f>master!C29</f>
+        <v>おまけ：新人の仕事はどうなるか？ これまで</v>
+      </c>
+      <c r="D39" s="111" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" s="112"/>
+      <c r="F39" s="113"/>
       <c r="G39" s="51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J39" s="47">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K39" s="43"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K39" s="43" t="s">
+        <v>190</v>
+      </c>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="50.4">
+    <row r="40" spans="1:14" ht="63">
       <c r="A40" s="11"/>
-      <c r="B40" s="118" t="str">
-        <f>master!B29</f>
-        <v>キャリア編</v>
-      </c>
+      <c r="B40" s="117"/>
       <c r="C40" s="51" t="str">
-        <f>master!C29</f>
-        <v>おまけ：新人の仕事はどうなるか？ これまで</v>
-      </c>
-      <c r="D40" s="115" t="s">
-        <v>161</v>
-      </c>
-      <c r="E40" s="116"/>
-      <c r="F40" s="117"/>
+        <f>master!C30</f>
+        <v>おまけ：生成AI before/after</v>
+      </c>
+      <c r="D40" s="111" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" s="112"/>
+      <c r="F40" s="113"/>
       <c r="G40" s="51" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="49" t="s">
@@ -5202,20 +5229,20 @@
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="63">
+    <row r="41" spans="1:14" ht="50.4">
       <c r="A41" s="11"/>
-      <c r="B41" s="118"/>
+      <c r="B41" s="117"/>
       <c r="C41" s="51" t="str">
-        <f>master!C30</f>
-        <v>おまけ：生成AI before/after</v>
-      </c>
-      <c r="D41" s="115" t="s">
-        <v>162</v>
-      </c>
-      <c r="E41" s="116"/>
-      <c r="F41" s="117"/>
+        <f>master!C31</f>
+        <v>おまけ：新人の仕事はどうなるか？　これから</v>
+      </c>
+      <c r="D41" s="111" t="s">
+        <v>160</v>
+      </c>
+      <c r="E41" s="112"/>
+      <c r="F41" s="113"/>
       <c r="G41" s="51" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="49" t="s">
@@ -5231,27 +5258,27 @@
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" ht="50.4">
+    <row r="42" spans="1:14" ht="100.8">
       <c r="A42" s="11"/>
-      <c r="B42" s="118"/>
+      <c r="B42" s="117"/>
       <c r="C42" s="51" t="str">
-        <f>master!C31</f>
-        <v>おまけ：新人の仕事はどうなるか？　これから</v>
-      </c>
-      <c r="D42" s="115" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" s="116"/>
-      <c r="F42" s="117"/>
+        <f>master!C32</f>
+        <v>代表的な若手の仕事</v>
+      </c>
+      <c r="D42" s="111" t="s">
+        <v>198</v>
+      </c>
+      <c r="E42" s="112"/>
+      <c r="F42" s="113"/>
       <c r="G42" s="51" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J42" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K42" s="43" t="s">
         <v>190</v>
@@ -5260,27 +5287,27 @@
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" ht="100.8">
+    <row r="43" spans="1:14" ht="88.2">
       <c r="A43" s="11"/>
-      <c r="B43" s="118"/>
+      <c r="B43" s="117"/>
       <c r="C43" s="51" t="str">
-        <f>master!C32</f>
-        <v>代表的な若手の仕事</v>
-      </c>
-      <c r="D43" s="115" t="s">
-        <v>198</v>
-      </c>
-      <c r="E43" s="116"/>
-      <c r="F43" s="117"/>
+        <f>master!C33</f>
+        <v>そもそも</v>
+      </c>
+      <c r="D43" s="111" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="112"/>
+      <c r="F43" s="113"/>
       <c r="G43" s="51" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J43" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K43" s="43" t="s">
         <v>190</v>
@@ -5289,27 +5316,27 @@
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="88.2">
+    <row r="44" spans="1:14" ht="37.799999999999997">
       <c r="A44" s="11"/>
-      <c r="B44" s="118"/>
+      <c r="B44" s="117"/>
       <c r="C44" s="51" t="str">
-        <f>master!C33</f>
-        <v>そもそも</v>
-      </c>
-      <c r="D44" s="115" t="s">
-        <v>199</v>
-      </c>
-      <c r="E44" s="116"/>
-      <c r="F44" s="117"/>
+        <f>master!C34</f>
+        <v>2040年の就業構造推計（改定版）の概要</v>
+      </c>
+      <c r="D44" s="111" t="s">
+        <v>163</v>
+      </c>
+      <c r="E44" s="112"/>
+      <c r="F44" s="113"/>
       <c r="G44" s="51" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J44" s="47">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K44" s="43" t="s">
         <v>190</v>
@@ -5318,27 +5345,27 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="37.799999999999997">
+    <row r="45" spans="1:14" ht="50.4">
       <c r="A45" s="11"/>
-      <c r="B45" s="118"/>
+      <c r="B45" s="117"/>
       <c r="C45" s="51" t="str">
-        <f>master!C34</f>
-        <v>2040年の就業構造推計（改定版）の概要</v>
-      </c>
-      <c r="D45" s="115" t="s">
-        <v>163</v>
-      </c>
-      <c r="E45" s="116"/>
-      <c r="F45" s="117"/>
+        <f>master!C35</f>
+        <v>全国版就業構造推計（改定版）・職業間ミスマッチ</v>
+      </c>
+      <c r="D45" s="111" t="s">
+        <v>164</v>
+      </c>
+      <c r="E45" s="112"/>
+      <c r="F45" s="113"/>
       <c r="G45" s="51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J45" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K45" s="43" t="s">
         <v>190</v>
@@ -5349,16 +5376,16 @@
     </row>
     <row r="46" spans="1:14" ht="50.4">
       <c r="A46" s="11"/>
-      <c r="B46" s="118"/>
+      <c r="B46" s="117"/>
       <c r="C46" s="51" t="str">
-        <f>master!C35</f>
-        <v>全国版就業構造推計（改定版）・職業間ミスマッチ</v>
-      </c>
-      <c r="D46" s="115" t="s">
-        <v>164</v>
-      </c>
-      <c r="E46" s="116"/>
-      <c r="F46" s="117"/>
+        <f>master!C36</f>
+        <v>（参考）将来の産業構造は・・・</v>
+      </c>
+      <c r="D46" s="111" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="112"/>
+      <c r="F46" s="113"/>
       <c r="G46" s="51" t="s">
         <v>124</v>
       </c>
@@ -5376,49 +5403,47 @@
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:14" ht="50.4">
+    <row r="47" spans="1:14" ht="63">
       <c r="A47" s="11"/>
-      <c r="B47" s="118"/>
+      <c r="B47" s="117"/>
       <c r="C47" s="51" t="str">
-        <f>master!C36</f>
-        <v>（参考）将来の産業構造は・・・</v>
-      </c>
-      <c r="D47" s="115" t="s">
-        <v>165</v>
-      </c>
-      <c r="E47" s="116"/>
-      <c r="F47" s="117"/>
+        <f>master!C37</f>
+        <v>ヒント１：生成ＡＩと原理原則</v>
+      </c>
+      <c r="D47" s="111" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="112"/>
+      <c r="F47" s="113"/>
       <c r="G47" s="51" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J47" s="47">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K47" s="43" t="s">
-        <v>190</v>
-      </c>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K47" s="43"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="63">
+    <row r="48" spans="1:14" ht="50.4">
       <c r="A48" s="11"/>
-      <c r="B48" s="118"/>
+      <c r="B48" s="117"/>
       <c r="C48" s="51" t="str">
-        <f>master!C37</f>
-        <v>ヒント１：生成ＡＩと原理原則</v>
-      </c>
-      <c r="D48" s="115" t="s">
-        <v>139</v>
-      </c>
-      <c r="E48" s="116"/>
-      <c r="F48" s="117"/>
+        <f>master!C38</f>
+        <v>ヒント2：プロンプトによる生成AIの挙動の違い</v>
+      </c>
+      <c r="D48" s="111" t="s">
+        <v>191</v>
+      </c>
+      <c r="E48" s="112"/>
+      <c r="F48" s="113"/>
       <c r="G48" s="51" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="49" t="s">
@@ -5432,161 +5457,161 @@
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:14" ht="50.4">
+    <row r="49" spans="1:14" ht="189">
       <c r="A49" s="11"/>
-      <c r="B49" s="118"/>
+      <c r="B49" s="117"/>
       <c r="C49" s="51" t="str">
-        <f>master!C38</f>
-        <v>ヒント2：プロンプトによる生成AIの挙動の違い</v>
-      </c>
-      <c r="D49" s="115" t="s">
-        <v>191</v>
-      </c>
-      <c r="E49" s="116"/>
-      <c r="F49" s="117"/>
+        <f>master!C39</f>
+        <v>ヒント３：それでも生成AIを積極的に使うしかない</v>
+      </c>
+      <c r="D49" s="111" t="s">
+        <v>192</v>
+      </c>
+      <c r="E49" s="112"/>
+      <c r="F49" s="113"/>
       <c r="G49" s="51" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J49" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K49" s="43"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="189">
+    <row r="50" spans="1:14">
       <c r="A50" s="11"/>
-      <c r="B50" s="118"/>
+      <c r="B50" s="117"/>
       <c r="C50" s="51" t="str">
-        <f>master!C39</f>
-        <v>ヒント３：それでも生成AIを積極的に使うしかない</v>
-      </c>
-      <c r="D50" s="115" t="s">
-        <v>192</v>
-      </c>
-      <c r="E50" s="116"/>
-      <c r="F50" s="117"/>
+        <f>master!C40</f>
+        <v>1. 研修概要</v>
+      </c>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="113"/>
       <c r="G50" s="51" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="49" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="J50" s="47">
-        <v>3.472222222222222E-3</v>
+        <v>0</v>
       </c>
       <c r="K50" s="43"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" ht="15" customHeight="1">
       <c r="A51" s="11"/>
-      <c r="B51" s="118"/>
+      <c r="B51" s="117"/>
       <c r="C51" s="51" t="str">
-        <f>master!C40</f>
-        <v>1. 研修概要</v>
-      </c>
-      <c r="D51" s="115"/>
-      <c r="E51" s="116"/>
-      <c r="F51" s="117"/>
+        <f>master!C41</f>
+        <v>デジタルブートキャンプの目的</v>
+      </c>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="113"/>
       <c r="G51" s="51" t="s">
         <v>119</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="49" t="s">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="J51" s="47">
-        <v>0</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K51" s="43"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" ht="15" customHeight="1">
+    <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="118"/>
+      <c r="B52" s="117"/>
       <c r="C52" s="51" t="str">
-        <f>master!C41</f>
-        <v>デジタルブートキャンプの目的</v>
-      </c>
-      <c r="D52" s="115"/>
-      <c r="E52" s="116"/>
-      <c r="F52" s="117"/>
+        <f>master!C42</f>
+        <v>まとめ</v>
+      </c>
+      <c r="D52" s="111" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" s="112"/>
+      <c r="F52" s="113"/>
       <c r="G52" s="51" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J52" s="47">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K52" s="43"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:14" ht="50.4">
+    <row r="53" spans="1:14" ht="25.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="118"/>
+      <c r="B53" s="117" t="str">
+        <f>master!B43</f>
+        <v>NTTデータの強み編</v>
+      </c>
       <c r="C53" s="51" t="str">
-        <f>master!C42</f>
-        <v>まとめ</v>
-      </c>
-      <c r="D53" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="E53" s="116"/>
-      <c r="F53" s="117"/>
+        <f>master!C43</f>
+        <v>2025年の変動</v>
+      </c>
+      <c r="D53" s="111" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" s="112"/>
+      <c r="F53" s="113"/>
       <c r="G53" s="51" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J53" s="47">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K53" s="43"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:14" ht="25.2">
+    <row r="54" spans="1:14" ht="50.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="118" t="str">
-        <f>master!B43</f>
-        <v>NTTデータの強み編</v>
-      </c>
+      <c r="B54" s="117"/>
       <c r="C54" s="51" t="str">
-        <f>master!C43</f>
-        <v>2025年の変動</v>
-      </c>
-      <c r="D54" s="115" t="s">
-        <v>142</v>
-      </c>
-      <c r="E54" s="116"/>
-      <c r="F54" s="117"/>
+        <f>master!C44</f>
+        <v>2025年の変動　AIエージェントの台頭</v>
+      </c>
+      <c r="D54" s="111" t="s">
+        <v>172</v>
+      </c>
+      <c r="E54" s="112"/>
+      <c r="F54" s="113"/>
       <c r="G54" s="51" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J54" s="47">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K54" s="43"/>
       <c r="L54" s="6"/>
@@ -5595,16 +5620,16 @@
     </row>
     <row r="55" spans="1:14" ht="50.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="118"/>
+      <c r="B55" s="117"/>
       <c r="C55" s="51" t="str">
-        <f>master!C44</f>
-        <v>2025年の変動　AIエージェントの台頭</v>
-      </c>
-      <c r="D55" s="115" t="s">
-        <v>172</v>
-      </c>
-      <c r="E55" s="116"/>
-      <c r="F55" s="117"/>
+        <f>master!C45</f>
+        <v>2025年の変動　Vibe Coding</v>
+      </c>
+      <c r="D55" s="111" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" s="112"/>
+      <c r="F55" s="113"/>
       <c r="G55" s="51" t="s">
         <v>124</v>
       </c>
@@ -5620,20 +5645,20 @@
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:14" ht="50.4">
+    <row r="56" spans="1:14" ht="88.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="118"/>
+      <c r="B56" s="117"/>
       <c r="C56" s="51" t="str">
-        <f>master!C45</f>
-        <v>2025年の変動　Vibe Coding</v>
-      </c>
-      <c r="D56" s="115" t="s">
-        <v>171</v>
-      </c>
-      <c r="E56" s="116"/>
-      <c r="F56" s="117"/>
+        <f>master!C46</f>
+        <v>2025年の変動　Spec Driven Development</v>
+      </c>
+      <c r="D56" s="111" t="s">
+        <v>200</v>
+      </c>
+      <c r="E56" s="112"/>
+      <c r="F56" s="113"/>
       <c r="G56" s="51" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="49" t="s">
@@ -5647,20 +5672,20 @@
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="88.2">
+    <row r="57" spans="1:14" ht="50.4">
       <c r="A57" s="11"/>
-      <c r="B57" s="118"/>
+      <c r="B57" s="117"/>
       <c r="C57" s="51" t="str">
-        <f>master!C46</f>
-        <v>2025年の変動　Spec Driven Development</v>
-      </c>
-      <c r="D57" s="115" t="s">
-        <v>200</v>
-      </c>
-      <c r="E57" s="116"/>
-      <c r="F57" s="117"/>
+        <f>master!C47</f>
+        <v>2025年の変動　ハーネスエンジニアリング</v>
+      </c>
+      <c r="D57" s="111" t="s">
+        <v>201</v>
+      </c>
+      <c r="E57" s="112"/>
+      <c r="F57" s="113"/>
       <c r="G57" s="51" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="49" t="s">
@@ -5674,20 +5699,20 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="50.4">
+    <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="118"/>
+      <c r="B58" s="117"/>
       <c r="C58" s="51" t="str">
-        <f>master!C47</f>
-        <v>2025年の変動　ハーネスエンジニアリング</v>
-      </c>
-      <c r="D58" s="115" t="s">
-        <v>201</v>
-      </c>
-      <c r="E58" s="116"/>
-      <c r="F58" s="117"/>
+        <f>master!C48</f>
+        <v>2025年の変動　動向まとめ</v>
+      </c>
+      <c r="D58" s="111" t="s">
+        <v>173</v>
+      </c>
+      <c r="E58" s="112"/>
+      <c r="F58" s="113"/>
       <c r="G58" s="51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="49" t="s">
@@ -5701,20 +5726,20 @@
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:14" ht="75.599999999999994">
+    <row r="59" spans="1:14" ht="113.4">
       <c r="A59" s="11"/>
-      <c r="B59" s="118"/>
+      <c r="B59" s="117"/>
       <c r="C59" s="51" t="str">
-        <f>master!C48</f>
-        <v>2025年の変動　動向まとめ</v>
-      </c>
-      <c r="D59" s="115" t="s">
-        <v>173</v>
-      </c>
-      <c r="E59" s="116"/>
-      <c r="F59" s="117"/>
+        <f>master!C49</f>
+        <v>2026年 ソフトウェア開発における課題とNTTDグループの強み</v>
+      </c>
+      <c r="D59" s="111" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" s="112"/>
+      <c r="F59" s="113"/>
       <c r="G59" s="51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="49" t="s">
@@ -5728,103 +5753,101 @@
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:14" ht="113.4">
+    <row r="60" spans="1:14" ht="37.799999999999997">
       <c r="A60" s="11"/>
-      <c r="B60" s="118"/>
+      <c r="B60" s="117"/>
       <c r="C60" s="51" t="str">
-        <f>master!C49</f>
-        <v>2026年 ソフトウェア開発における課題とNTTDグループの強み</v>
-      </c>
-      <c r="D60" s="115" t="s">
-        <v>175</v>
-      </c>
-      <c r="E60" s="116"/>
-      <c r="F60" s="117"/>
+        <f>master!C50</f>
+        <v>2025年の変動</v>
+      </c>
+      <c r="D60" s="111" t="s">
+        <v>176</v>
+      </c>
+      <c r="E60" s="112"/>
+      <c r="F60" s="113"/>
       <c r="G60" s="51" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H60" s="12"/>
       <c r="I60" s="49" t="s">
         <v>25</v>
       </c>
       <c r="J60" s="47">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K60" s="43"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:14" ht="37.799999999999997">
+    <row r="61" spans="1:14" ht="15" customHeight="1">
       <c r="A61" s="11"/>
-      <c r="B61" s="118"/>
+      <c r="B61" s="73" t="str">
+        <f>master!B51</f>
+        <v>デジタルソサエティ事業部取組紹介</v>
+      </c>
       <c r="C61" s="51" t="str">
-        <f>master!C50</f>
-        <v>2025年の変動</v>
-      </c>
-      <c r="D61" s="115" t="s">
-        <v>176</v>
-      </c>
-      <c r="E61" s="116"/>
-      <c r="F61" s="117"/>
+        <f>master!C51</f>
+        <v>ー</v>
+      </c>
+      <c r="D61" s="111"/>
+      <c r="E61" s="112"/>
+      <c r="F61" s="113"/>
       <c r="G61" s="51" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H61" s="12"/>
       <c r="I61" s="49" t="s">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="J61" s="47">
-        <v>1.3888888888888889E-3</v>
+        <v>0</v>
       </c>
       <c r="K61" s="43"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:14" ht="15" customHeight="1">
+    <row r="62" spans="1:14" ht="50.4" customHeight="1">
       <c r="A62" s="11"/>
-      <c r="B62" s="73" t="str">
-        <f>master!B51</f>
-        <v>デジタルソサエティ事業部取組紹介</v>
-      </c>
-      <c r="C62" s="51" t="str">
-        <f>master!C51</f>
-        <v>ー</v>
-      </c>
-      <c r="D62" s="115"/>
-      <c r="E62" s="116"/>
-      <c r="F62" s="117"/>
-      <c r="G62" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="H62" s="12"/>
-      <c r="I62" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="J62" s="47">
-        <v>0</v>
-      </c>
-      <c r="K62" s="43"/>
+      <c r="B62" s="120" t="str">
+        <f>master!B52</f>
+        <v>ハンズオン編:ChatGPT</v>
+      </c>
+      <c r="C62" s="68" t="str">
+        <f>master!C52</f>
+        <v>生成ＡＩハンズオン</v>
+      </c>
+      <c r="D62" s="114"/>
+      <c r="E62" s="115"/>
+      <c r="F62" s="116"/>
+      <c r="G62" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="H62" s="69"/>
+      <c r="I62" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J62" s="71">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K62" s="72"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:14" ht="50.4" customHeight="1">
+    <row r="63" spans="1:14">
       <c r="A63" s="11"/>
-      <c r="B63" s="109" t="str">
-        <f>master!B52</f>
-        <v>ハンズオン編:ChatGPT</v>
-      </c>
+      <c r="B63" s="121"/>
       <c r="C63" s="68" t="str">
-        <f>master!C52</f>
-        <v>生成ＡＩハンズオン</v>
-      </c>
-      <c r="D63" s="112"/>
-      <c r="E63" s="113"/>
-      <c r="F63" s="114"/>
+        <f>master!C53</f>
+        <v>ChatGPTの使い方（一般チャット）</v>
+      </c>
+      <c r="D63" s="114"/>
+      <c r="E63" s="115"/>
+      <c r="F63" s="116"/>
       <c r="G63" s="68" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H63" s="69"/>
       <c r="I63" s="70" t="s">
@@ -5838,97 +5861,99 @@
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" ht="50.4">
       <c r="A64" s="11"/>
-      <c r="B64" s="110"/>
+      <c r="B64" s="121"/>
       <c r="C64" s="68" t="str">
-        <f>master!C53</f>
-        <v>ChatGPTの使い方（一般チャット）</v>
-      </c>
-      <c r="D64" s="112"/>
-      <c r="E64" s="113"/>
-      <c r="F64" s="114"/>
+        <f>master!C54</f>
+        <v>プロンプトを入れてみる</v>
+      </c>
+      <c r="D64" s="114" t="s">
+        <v>170</v>
+      </c>
+      <c r="E64" s="115"/>
+      <c r="F64" s="116"/>
       <c r="G64" s="68" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H64" s="69"/>
       <c r="I64" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J64" s="71">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888888E-2</v>
       </c>
       <c r="K64" s="72"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:14" ht="50.4">
+    <row r="65" spans="1:14" ht="63">
       <c r="A65" s="11"/>
-      <c r="B65" s="110"/>
+      <c r="B65" s="121"/>
       <c r="C65" s="68" t="str">
-        <f>master!C54</f>
-        <v>プロンプトを入れてみる</v>
-      </c>
-      <c r="D65" s="112" t="s">
-        <v>170</v>
-      </c>
-      <c r="E65" s="113"/>
-      <c r="F65" s="114"/>
+        <f>master!C55</f>
+        <v>ハンズオン例</v>
+      </c>
+      <c r="D65" s="114" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" s="115"/>
+      <c r="F65" s="116"/>
       <c r="G65" s="68" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H65" s="69"/>
       <c r="I65" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J65" s="71">
-        <v>1.3888888888888888E-2</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K65" s="72"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:14" ht="63">
+    <row r="66" spans="1:14" ht="126">
       <c r="A66" s="11"/>
-      <c r="B66" s="110"/>
+      <c r="B66" s="121"/>
       <c r="C66" s="68" t="str">
-        <f>master!C55</f>
-        <v>ハンズオン例</v>
-      </c>
-      <c r="D66" s="112" t="s">
-        <v>144</v>
-      </c>
-      <c r="E66" s="113"/>
-      <c r="F66" s="114"/>
+        <f>master!C56</f>
+        <v>例１：【レポート作成】　佐々木社長の調査を行う</v>
+      </c>
+      <c r="D66" s="114" t="s">
+        <v>167</v>
+      </c>
+      <c r="E66" s="115"/>
+      <c r="F66" s="116"/>
       <c r="G66" s="68" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H66" s="69"/>
       <c r="I66" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J66" s="71">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K66" s="72"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:14" ht="126">
+    <row r="67" spans="1:14" ht="126" customHeight="1">
       <c r="A67" s="11"/>
-      <c r="B67" s="110"/>
+      <c r="B67" s="121"/>
       <c r="C67" s="68" t="str">
-        <f>master!C56</f>
-        <v>例１：【レポート作成】　佐々木社長の調査を行う</v>
-      </c>
-      <c r="D67" s="112" t="s">
+        <f>master!C57</f>
+        <v>例２：顧客提案向けの企画書を作りたい</v>
+      </c>
+      <c r="D67" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="E67" s="113"/>
-      <c r="F67" s="114"/>
+      <c r="E67" s="115"/>
+      <c r="F67" s="116"/>
       <c r="G67" s="68" t="s">
         <v>127</v>
       </c>
@@ -5946,16 +5971,16 @@
     </row>
     <row r="68" spans="1:14" ht="126" customHeight="1">
       <c r="A68" s="11"/>
-      <c r="B68" s="110"/>
+      <c r="B68" s="121"/>
       <c r="C68" s="68" t="str">
-        <f>master!C57</f>
-        <v>例２：顧客提案向けの企画書を作りたい</v>
-      </c>
-      <c r="D68" s="112" t="s">
+        <f>master!C58</f>
+        <v>例３：１００本ノックを作ってみる</v>
+      </c>
+      <c r="D68" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="E68" s="113"/>
-      <c r="F68" s="114"/>
+      <c r="E68" s="115"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="68" t="s">
         <v>127</v>
       </c>
@@ -5971,43 +5996,44 @@
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:14" ht="126" customHeight="1">
+    <row r="69" spans="1:14">
       <c r="A69" s="11"/>
-      <c r="B69" s="110"/>
+      <c r="B69" s="122"/>
       <c r="C69" s="68" t="str">
-        <f>master!C58</f>
-        <v>例３：１００本ノックを作ってみる</v>
-      </c>
-      <c r="D69" s="112" t="s">
-        <v>167</v>
-      </c>
-      <c r="E69" s="113"/>
-      <c r="F69" s="114"/>
+        <f>master!C59</f>
+        <v>ChatGPT まとめ</v>
+      </c>
+      <c r="D69" s="114"/>
+      <c r="E69" s="115"/>
+      <c r="F69" s="116"/>
       <c r="G69" s="68" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H69" s="69"/>
       <c r="I69" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J69" s="71">
-        <v>6.9444444444444441E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K69" s="72"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" ht="15" customHeight="1">
       <c r="A70" s="11"/>
-      <c r="B70" s="111"/>
+      <c r="B70" s="120" t="str">
+        <f>master!B60</f>
+        <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
+      </c>
       <c r="C70" s="68" t="str">
-        <f>master!C59</f>
-        <v>ChatGPT まとめ</v>
-      </c>
-      <c r="D70" s="112"/>
-      <c r="E70" s="113"/>
-      <c r="F70" s="114"/>
+        <f>master!C60</f>
+        <v>生成ＡＩハンズオン</v>
+      </c>
+      <c r="D70" s="114"/>
+      <c r="E70" s="115"/>
+      <c r="F70" s="116"/>
       <c r="G70" s="68" t="s">
         <v>119</v>
       </c>
@@ -6023,21 +6049,20 @@
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
-    <row r="71" spans="1:14" ht="15" customHeight="1">
+    <row r="71" spans="1:14" ht="25.2">
       <c r="A71" s="11"/>
-      <c r="B71" s="109" t="str">
-        <f>master!B60</f>
-        <v xml:space="preserve">ハンズオン編:GitHub Copilot </v>
-      </c>
+      <c r="B71" s="121"/>
       <c r="C71" s="68" t="str">
-        <f>master!C60</f>
-        <v>生成ＡＩハンズオン</v>
-      </c>
-      <c r="D71" s="112"/>
-      <c r="E71" s="113"/>
-      <c r="F71" s="114"/>
+        <f>master!C61</f>
+        <v>Visual Studio Code を開く</v>
+      </c>
+      <c r="D71" s="114" t="s">
+        <v>168</v>
+      </c>
+      <c r="E71" s="115"/>
+      <c r="F71" s="116"/>
       <c r="G71" s="68" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="H71" s="69"/>
       <c r="I71" s="70" t="s">
@@ -6051,99 +6076,99 @@
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
-    <row r="72" spans="1:14" ht="25.2">
+    <row r="72" spans="1:14" ht="37.799999999999997">
       <c r="A72" s="11"/>
-      <c r="B72" s="110"/>
+      <c r="B72" s="121"/>
       <c r="C72" s="68" t="str">
-        <f>master!C61</f>
-        <v>Visual Studio Code を開く</v>
-      </c>
-      <c r="D72" s="112" t="s">
-        <v>168</v>
-      </c>
-      <c r="E72" s="113"/>
-      <c r="F72" s="114"/>
+        <f>master!C62</f>
+        <v>コード補完機能</v>
+      </c>
+      <c r="D72" s="114" t="s">
+        <v>169</v>
+      </c>
+      <c r="E72" s="115"/>
+      <c r="F72" s="116"/>
       <c r="G72" s="68" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H72" s="69"/>
       <c r="I72" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J72" s="71">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K72" s="72"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
-    <row r="73" spans="1:14" ht="37.799999999999997">
+    <row r="73" spans="1:14" ht="100.8">
       <c r="A73" s="11"/>
-      <c r="B73" s="110"/>
+      <c r="B73" s="121"/>
       <c r="C73" s="68" t="str">
-        <f>master!C62</f>
-        <v>コード補完機能</v>
-      </c>
-      <c r="D73" s="112" t="s">
-        <v>169</v>
-      </c>
-      <c r="E73" s="113"/>
-      <c r="F73" s="114"/>
+        <f>master!C63</f>
+        <v>チャット機能</v>
+      </c>
+      <c r="D73" s="114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E73" s="115"/>
+      <c r="F73" s="116"/>
       <c r="G73" s="68" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="H73" s="69"/>
       <c r="I73" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J73" s="71">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K73" s="72"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
-    <row r="74" spans="1:14" ht="100.8">
+    <row r="74" spans="1:14" ht="15" customHeight="1">
       <c r="A74" s="11"/>
-      <c r="B74" s="110"/>
+      <c r="B74" s="121"/>
       <c r="C74" s="68" t="str">
-        <f>master!C63</f>
-        <v>チャット機能</v>
-      </c>
-      <c r="D74" s="112" t="s">
-        <v>202</v>
-      </c>
-      <c r="E74" s="113"/>
-      <c r="F74" s="114"/>
+        <f>master!C64</f>
+        <v>ChatGPT で 簡単なアプリやゲームを作ってみましょう</v>
+      </c>
+      <c r="D74" s="114"/>
+      <c r="E74" s="115"/>
+      <c r="F74" s="116"/>
       <c r="G74" s="68" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="H74" s="69"/>
       <c r="I74" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J74" s="71">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K74" s="72"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
-    <row r="75" spans="1:14" ht="15" customHeight="1">
+    <row r="75" spans="1:14" ht="25.2">
       <c r="A75" s="11"/>
-      <c r="B75" s="110"/>
+      <c r="B75" s="121"/>
       <c r="C75" s="68" t="str">
-        <f>master!C64</f>
-        <v>ChatGPT で 簡単なアプリやゲームを作ってみましょう</v>
-      </c>
-      <c r="D75" s="112"/>
-      <c r="E75" s="113"/>
-      <c r="F75" s="114"/>
+        <f>master!C65</f>
+        <v>例１　高級志向テトリス</v>
+      </c>
+      <c r="D75" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E75" s="115"/>
+      <c r="F75" s="116"/>
       <c r="G75" s="68" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="H75" s="69"/>
       <c r="I75" s="70" t="s">
@@ -6159,16 +6184,16 @@
     </row>
     <row r="76" spans="1:14" ht="25.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="110"/>
+      <c r="B76" s="121"/>
       <c r="C76" s="68" t="str">
-        <f>master!C65</f>
-        <v>例１　高級志向テトリス</v>
-      </c>
-      <c r="D76" s="112" t="s">
+        <f>master!C66</f>
+        <v>例）わくわく！にっぽんダーツの旅</v>
+      </c>
+      <c r="D76" s="114" t="s">
         <v>141</v>
       </c>
-      <c r="E76" s="113"/>
-      <c r="F76" s="114"/>
+      <c r="E76" s="115"/>
+      <c r="F76" s="116"/>
       <c r="G76" s="68" t="s">
         <v>131</v>
       </c>
@@ -6186,16 +6211,16 @@
     </row>
     <row r="77" spans="1:14" ht="25.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="110"/>
+      <c r="B77" s="121"/>
       <c r="C77" s="68" t="str">
-        <f>master!C66</f>
-        <v>例）わくわく！にっぽんダーツの旅</v>
-      </c>
-      <c r="D77" s="112" t="s">
+        <f>master!C67</f>
+        <v>例）タスク管理ツール</v>
+      </c>
+      <c r="D77" s="114" t="s">
         <v>141</v>
       </c>
-      <c r="E77" s="113"/>
-      <c r="F77" s="114"/>
+      <c r="E77" s="115"/>
+      <c r="F77" s="116"/>
       <c r="G77" s="68" t="s">
         <v>131</v>
       </c>
@@ -6211,183 +6236,183 @@
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
-    <row r="78" spans="1:14" ht="25.2">
+    <row r="78" spans="1:14" ht="126">
       <c r="A78" s="11"/>
-      <c r="B78" s="110"/>
-      <c r="C78" s="68" t="str">
-        <f>master!C67</f>
-        <v>例）タスク管理ツール</v>
-      </c>
-      <c r="D78" s="112" t="s">
-        <v>141</v>
-      </c>
-      <c r="E78" s="113"/>
-      <c r="F78" s="114"/>
+      <c r="B78" s="121"/>
+      <c r="C78" s="68"/>
+      <c r="D78" s="114" t="s">
+        <v>146</v>
+      </c>
+      <c r="E78" s="115"/>
+      <c r="F78" s="116"/>
       <c r="G78" s="68" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H78" s="69"/>
       <c r="I78" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J78" s="71">
-        <v>6.9444444444444447E-4</v>
+        <v>1.0416666666666666E-2</v>
       </c>
       <c r="K78" s="72"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:14" ht="126">
+    <row r="79" spans="1:14" ht="63">
       <c r="A79" s="11"/>
-      <c r="B79" s="110"/>
-      <c r="C79" s="68"/>
-      <c r="D79" s="112" t="s">
-        <v>146</v>
-      </c>
-      <c r="E79" s="113"/>
-      <c r="F79" s="114"/>
+      <c r="B79" s="121"/>
+      <c r="C79" s="68" t="str">
+        <f>master!C68</f>
+        <v>ディレクトリ作成とファイル配置</v>
+      </c>
+      <c r="D79" s="114" t="s">
+        <v>147</v>
+      </c>
+      <c r="E79" s="115"/>
+      <c r="F79" s="116"/>
       <c r="G79" s="68" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H79" s="69"/>
       <c r="I79" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J79" s="71">
-        <v>1.0416666666666666E-2</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K79" s="72"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
     </row>
-    <row r="80" spans="1:14" ht="63">
+    <row r="80" spans="1:14" ht="25.2">
       <c r="A80" s="11"/>
-      <c r="B80" s="110"/>
+      <c r="B80" s="121"/>
       <c r="C80" s="68" t="str">
-        <f>master!C68</f>
-        <v>ディレクトリ作成とファイル配置</v>
-      </c>
-      <c r="D80" s="112" t="s">
-        <v>147</v>
-      </c>
-      <c r="E80" s="113"/>
-      <c r="F80" s="114"/>
+        <f>master!C69</f>
+        <v>チャット機能：Aｓｋ</v>
+      </c>
+      <c r="D80" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E80" s="115"/>
+      <c r="F80" s="116"/>
       <c r="G80" s="68" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H80" s="69"/>
       <c r="I80" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J80" s="71">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K80" s="72"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
-    <row r="81" spans="1:14" ht="25.2">
+    <row r="81" spans="1:14" ht="50.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="110"/>
+      <c r="B81" s="121"/>
       <c r="C81" s="68" t="str">
-        <f>master!C69</f>
-        <v>チャット機能：Aｓｋ</v>
-      </c>
-      <c r="D81" s="112" t="s">
-        <v>141</v>
-      </c>
-      <c r="E81" s="113"/>
-      <c r="F81" s="114"/>
+        <f>master!C70</f>
+        <v>Askモードについて</v>
+      </c>
+      <c r="D81" s="114" t="s">
+        <v>174</v>
+      </c>
+      <c r="E81" s="115"/>
+      <c r="F81" s="116"/>
       <c r="G81" s="68" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H81" s="69"/>
       <c r="I81" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J81" s="71">
-        <v>6.9444444444444447E-4</v>
+        <v>1.0416666666666666E-2</v>
       </c>
       <c r="K81" s="72"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
       <c r="N81" s="6"/>
     </row>
-    <row r="82" spans="1:14" ht="50.4">
+    <row r="82" spans="1:14" ht="25.2">
       <c r="A82" s="11"/>
-      <c r="B82" s="110"/>
-      <c r="C82" s="68" t="str">
-        <f>master!C70</f>
-        <v>Askモードについて</v>
-      </c>
-      <c r="D82" s="112" t="s">
-        <v>174</v>
-      </c>
-      <c r="E82" s="113"/>
-      <c r="F82" s="114"/>
+      <c r="B82" s="121"/>
+      <c r="C82" s="87" t="str">
+        <f>master!C71</f>
+        <v>実行例</v>
+      </c>
+      <c r="D82" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E82" s="115"/>
+      <c r="F82" s="116"/>
       <c r="G82" s="68" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H82" s="69"/>
       <c r="I82" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J82" s="71">
-        <v>1.0416666666666666E-2</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K82" s="72"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
     </row>
-    <row r="83" spans="1:14" ht="25.2">
+    <row r="83" spans="1:14" ht="37.799999999999997">
       <c r="A83" s="11"/>
-      <c r="B83" s="110"/>
-      <c r="C83" s="87" t="str">
-        <f>master!C71</f>
-        <v>実行例</v>
-      </c>
-      <c r="D83" s="112" t="s">
-        <v>141</v>
-      </c>
-      <c r="E83" s="113"/>
-      <c r="F83" s="114"/>
+      <c r="B83" s="121"/>
+      <c r="C83" s="88"/>
+      <c r="D83" s="114" t="s">
+        <v>193</v>
+      </c>
+      <c r="E83" s="115"/>
+      <c r="F83" s="116"/>
       <c r="G83" s="68" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H83" s="69"/>
       <c r="I83" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J83" s="71">
-        <v>1.3888888888888889E-3</v>
+        <v>1.3888888888888888E-2</v>
       </c>
       <c r="K83" s="72"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
-    <row r="84" spans="1:14" ht="37.799999999999997">
+    <row r="84" spans="1:14" ht="25.2">
       <c r="A84" s="11"/>
-      <c r="B84" s="110"/>
-      <c r="C84" s="88"/>
-      <c r="D84" s="112" t="s">
-        <v>193</v>
-      </c>
-      <c r="E84" s="113"/>
-      <c r="F84" s="114"/>
+      <c r="B84" s="121"/>
+      <c r="C84" s="68" t="str">
+        <f>master!C72</f>
+        <v>Askモードまとめ</v>
+      </c>
+      <c r="D84" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E84" s="115"/>
+      <c r="F84" s="116"/>
       <c r="G84" s="68" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H84" s="69"/>
       <c r="I84" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J84" s="71">
-        <v>1.3888888888888888E-2</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K84" s="72"/>
       <c r="L84" s="6"/>
@@ -6396,16 +6421,16 @@
     </row>
     <row r="85" spans="1:14" ht="25.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="110"/>
+      <c r="B85" s="121"/>
       <c r="C85" s="68" t="str">
-        <f>master!C72</f>
-        <v>Askモードまとめ</v>
-      </c>
-      <c r="D85" s="112" t="s">
+        <f>master!C73</f>
+        <v>チャット機能：Agent</v>
+      </c>
+      <c r="D85" s="114" t="s">
         <v>141</v>
       </c>
-      <c r="E85" s="113"/>
-      <c r="F85" s="114"/>
+      <c r="E85" s="115"/>
+      <c r="F85" s="116"/>
       <c r="G85" s="68" t="s">
         <v>131</v>
       </c>
@@ -6423,16 +6448,16 @@
     </row>
     <row r="86" spans="1:14" ht="25.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="110"/>
+      <c r="B86" s="121"/>
       <c r="C86" s="68" t="str">
-        <f>master!C73</f>
-        <v>チャット機能：Agent</v>
-      </c>
-      <c r="D86" s="112" t="s">
+        <f>master!C74</f>
+        <v>Agentモード</v>
+      </c>
+      <c r="D86" s="114" t="s">
         <v>141</v>
       </c>
-      <c r="E86" s="113"/>
-      <c r="F86" s="114"/>
+      <c r="E86" s="115"/>
+      <c r="F86" s="116"/>
       <c r="G86" s="68" t="s">
         <v>131</v>
       </c>
@@ -6441,34 +6466,34 @@
         <v>25</v>
       </c>
       <c r="J86" s="71">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K86" s="72"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
       <c r="N86" s="6"/>
     </row>
-    <row r="87" spans="1:14" ht="25.2">
+    <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="110"/>
+      <c r="B87" s="121"/>
       <c r="C87" s="68" t="str">
-        <f>master!C74</f>
-        <v>Agentモード</v>
-      </c>
-      <c r="D87" s="112" t="s">
-        <v>141</v>
-      </c>
-      <c r="E87" s="113"/>
-      <c r="F87" s="114"/>
+        <f>master!C75</f>
+        <v>実行例</v>
+      </c>
+      <c r="D87" s="114" t="s">
+        <v>174</v>
+      </c>
+      <c r="E87" s="115"/>
+      <c r="F87" s="116"/>
       <c r="G87" s="68" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H87" s="69"/>
       <c r="I87" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J87" s="71">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K87" s="72"/>
       <c r="L87" s="6"/>
@@ -6477,16 +6502,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="110"/>
+      <c r="B88" s="121"/>
       <c r="C88" s="68" t="str">
-        <f>master!C75</f>
-        <v>実行例</v>
-      </c>
-      <c r="D88" s="112" t="s">
+        <f>master!C76</f>
+        <v>READMEの内容を確認しましょう</v>
+      </c>
+      <c r="D88" s="114" t="s">
         <v>174</v>
       </c>
-      <c r="E88" s="113"/>
-      <c r="F88" s="114"/>
+      <c r="E88" s="115"/>
+      <c r="F88" s="116"/>
       <c r="G88" s="68" t="s">
         <v>123</v>
       </c>
@@ -6495,7 +6520,7 @@
         <v>25</v>
       </c>
       <c r="J88" s="71">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K88" s="72"/>
       <c r="L88" s="6"/>
@@ -6504,16 +6529,16 @@
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="110"/>
-      <c r="C89" s="68" t="str">
-        <f>master!C76</f>
-        <v>READMEの内容を確認しましょう</v>
-      </c>
-      <c r="D89" s="112" t="s">
+      <c r="B89" s="121"/>
+      <c r="C89" s="87" t="str">
+        <f>master!C77</f>
+        <v>Changeログを作ってみましょう</v>
+      </c>
+      <c r="D89" s="114" t="s">
         <v>174</v>
       </c>
-      <c r="E89" s="113"/>
-      <c r="F89" s="114"/>
+      <c r="E89" s="115"/>
+      <c r="F89" s="116"/>
       <c r="G89" s="68" t="s">
         <v>123</v>
       </c>
@@ -6522,7 +6547,7 @@
         <v>25</v>
       </c>
       <c r="J89" s="71">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K89" s="72"/>
       <c r="L89" s="6"/>
@@ -6531,16 +6556,13 @@
     </row>
     <row r="90" spans="1:14" ht="37.799999999999997">
       <c r="A90" s="11"/>
-      <c r="B90" s="110"/>
-      <c r="C90" s="87" t="str">
-        <f>master!C77</f>
-        <v>Changeログを作ってみましょう</v>
-      </c>
-      <c r="D90" s="112" t="s">
-        <v>174</v>
-      </c>
-      <c r="E90" s="113"/>
-      <c r="F90" s="114"/>
+      <c r="B90" s="121"/>
+      <c r="C90" s="88"/>
+      <c r="D90" s="114" t="s">
+        <v>189</v>
+      </c>
+      <c r="E90" s="115"/>
+      <c r="F90" s="116"/>
       <c r="G90" s="68" t="s">
         <v>123</v>
       </c>
@@ -6549,51 +6571,54 @@
         <v>25</v>
       </c>
       <c r="J90" s="71">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K90" s="72"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:14" ht="37.799999999999997">
+    <row r="91" spans="1:14" ht="25.2">
       <c r="A91" s="11"/>
-      <c r="B91" s="110"/>
-      <c r="C91" s="88"/>
-      <c r="D91" s="112" t="s">
-        <v>189</v>
-      </c>
-      <c r="E91" s="113"/>
-      <c r="F91" s="114"/>
+      <c r="B91" s="121"/>
+      <c r="C91" s="68" t="str">
+        <f>master!C78</f>
+        <v>チャット機能：Plan</v>
+      </c>
+      <c r="D91" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E91" s="115"/>
+      <c r="F91" s="116"/>
       <c r="G91" s="68" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H91" s="69"/>
       <c r="I91" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J91" s="71">
-        <v>6.9444444444444441E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K91" s="72"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:14" ht="25.2">
+    <row r="92" spans="1:14" ht="37.799999999999997">
       <c r="A92" s="11"/>
-      <c r="B92" s="110"/>
+      <c r="B92" s="121"/>
       <c r="C92" s="68" t="str">
-        <f>master!C78</f>
-        <v>チャット機能：Plan</v>
-      </c>
-      <c r="D92" s="112" t="s">
-        <v>141</v>
-      </c>
-      <c r="E92" s="113"/>
-      <c r="F92" s="114"/>
+        <f>master!C79</f>
+        <v>Planモードで機能追加してみましょう</v>
+      </c>
+      <c r="D92" s="114" t="s">
+        <v>174</v>
+      </c>
+      <c r="E92" s="115"/>
+      <c r="F92" s="116"/>
       <c r="G92" s="68" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H92" s="69"/>
       <c r="I92" s="70" t="s">
@@ -6607,27 +6632,27 @@
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
-    <row r="93" spans="1:14" ht="37.799999999999997">
+    <row r="93" spans="1:14" ht="25.2">
       <c r="A93" s="11"/>
-      <c r="B93" s="110"/>
+      <c r="B93" s="121"/>
       <c r="C93" s="68" t="str">
-        <f>master!C79</f>
-        <v>Planモードで機能追加してみましょう</v>
-      </c>
-      <c r="D93" s="112" t="s">
-        <v>174</v>
-      </c>
-      <c r="E93" s="113"/>
-      <c r="F93" s="114"/>
+        <f>master!C80</f>
+        <v>実行例</v>
+      </c>
+      <c r="D93" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E93" s="115"/>
+      <c r="F93" s="116"/>
       <c r="G93" s="68" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H93" s="69"/>
       <c r="I93" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J93" s="71">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K93" s="72"/>
       <c r="L93" s="6"/>
@@ -6636,16 +6661,16 @@
     </row>
     <row r="94" spans="1:14" ht="25.2">
       <c r="A94" s="11"/>
-      <c r="B94" s="110"/>
-      <c r="C94" s="68" t="str">
-        <f>master!C80</f>
-        <v>実行例</v>
-      </c>
-      <c r="D94" s="112" t="s">
+      <c r="B94" s="121"/>
+      <c r="C94" s="87" t="str">
+        <f>master!C81</f>
+        <v>実行結果</v>
+      </c>
+      <c r="D94" s="114" t="s">
         <v>141</v>
       </c>
-      <c r="E94" s="113"/>
-      <c r="F94" s="114"/>
+      <c r="E94" s="115"/>
+      <c r="F94" s="116"/>
       <c r="G94" s="68" t="s">
         <v>131</v>
       </c>
@@ -6661,161 +6686,153 @@
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
-    <row r="95" spans="1:14" ht="25.2">
+    <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="110"/>
-      <c r="C95" s="87" t="str">
-        <f>master!C81</f>
-        <v>実行結果</v>
-      </c>
-      <c r="D95" s="112" t="s">
-        <v>141</v>
-      </c>
-      <c r="E95" s="113"/>
-      <c r="F95" s="114"/>
+      <c r="B95" s="121"/>
+      <c r="C95" s="88"/>
+      <c r="D95" s="114" t="s">
+        <v>189</v>
+      </c>
+      <c r="E95" s="115"/>
+      <c r="F95" s="116"/>
       <c r="G95" s="68" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H95" s="69"/>
       <c r="I95" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J95" s="71">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K95" s="72"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
-    <row r="96" spans="1:14" ht="37.799999999999997">
+    <row r="96" spans="1:14" ht="25.2">
       <c r="A96" s="11"/>
-      <c r="B96" s="110"/>
-      <c r="C96" s="88"/>
-      <c r="D96" s="112" t="s">
-        <v>189</v>
-      </c>
-      <c r="E96" s="113"/>
-      <c r="F96" s="114"/>
+      <c r="B96" s="121"/>
+      <c r="C96" s="68" t="str">
+        <f>master!C82</f>
+        <v>Planモード＆Agentモードまとめ</v>
+      </c>
+      <c r="D96" s="114" t="s">
+        <v>141</v>
+      </c>
+      <c r="E96" s="115"/>
+      <c r="F96" s="116"/>
       <c r="G96" s="68" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H96" s="69"/>
       <c r="I96" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J96" s="71">
-        <v>6.9444444444444441E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K96" s="72"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
       <c r="N96" s="6"/>
     </row>
-    <row r="97" spans="1:14" ht="25.2">
+    <row r="97" spans="1:14" ht="113.4">
       <c r="A97" s="11"/>
-      <c r="B97" s="110"/>
+      <c r="B97" s="84" t="str">
+        <f>master!B83</f>
+        <v>プレゼン</v>
+      </c>
       <c r="C97" s="68" t="str">
-        <f>master!C82</f>
-        <v>Planモード＆Agentモードまとめ</v>
-      </c>
-      <c r="D97" s="112" t="s">
-        <v>141</v>
-      </c>
-      <c r="E97" s="113"/>
-      <c r="F97" s="114"/>
+        <f>master!C83</f>
+        <v>開発したゲームやアプリをプレゼン</v>
+      </c>
+      <c r="D97" s="114" t="s">
+        <v>188</v>
+      </c>
+      <c r="E97" s="115"/>
+      <c r="F97" s="116"/>
       <c r="G97" s="68" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H97" s="69"/>
       <c r="I97" s="70" t="s">
         <v>25</v>
       </c>
       <c r="J97" s="71">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K97" s="72"/>
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K97" s="72" t="s">
+        <v>185</v>
+      </c>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
-    <row r="98" spans="1:14" ht="113.4">
-      <c r="A98" s="11"/>
-      <c r="B98" s="84" t="str">
-        <f>master!B83</f>
-        <v>プレゼン</v>
-      </c>
-      <c r="C98" s="68" t="str">
-        <f>master!C83</f>
-        <v>開発したゲームやアプリをプレゼン</v>
-      </c>
-      <c r="D98" s="112" t="s">
-        <v>188</v>
-      </c>
-      <c r="E98" s="113"/>
-      <c r="F98" s="114"/>
-      <c r="G98" s="68" t="s">
-        <v>126</v>
-      </c>
-      <c r="H98" s="69"/>
-      <c r="I98" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="J98" s="71">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K98" s="72" t="s">
-        <v>185</v>
-      </c>
-      <c r="L98" s="6"/>
-      <c r="M98" s="6"/>
-      <c r="N98" s="6"/>
-    </row>
-    <row r="99" spans="1:14" ht="15" customHeight="1">
-      <c r="J99" s="46"/>
-    </row>
-    <row r="100" spans="1:14" ht="15" customHeight="1"/>
+    <row r="98" spans="1:14" ht="15" customHeight="1">
+      <c r="J98" s="46"/>
+    </row>
+    <row r="99" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B15:B25"/>
-    <mergeCell ref="B26:B34"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B62:B69"/>
+    <mergeCell ref="B70:B96"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D42:F42"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="B40:B53"/>
-    <mergeCell ref="B54:B61"/>
-    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B39:B52"/>
+    <mergeCell ref="B53:B60"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="D33:F33"/>
@@ -6827,60 +6844,41 @@
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D53:F53"/>
     <mergeCell ref="D54:F54"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B63:B70"/>
-    <mergeCell ref="B71:B97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="B14:B24"/>
+    <mergeCell ref="B25:B33"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6893,7 +6891,7 @@
           <x14:formula1>
             <xm:f>master!$C$48:$C$50</xm:f>
           </x14:formula1>
-          <xm:sqref>H13:H98</xm:sqref>
+          <xm:sqref>H12:H97</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
